--- a/data/CIM_Master_Data.xlsx
+++ b/data/CIM_Master_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\calvi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1285EB76-3F65-4B5D-B585-6361A6D25F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B6341E3-FFFB-4CC2-B62C-15DF6D800229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5017,7 +5017,7 @@
         <v>2022</v>
       </c>
       <c r="I36" s="8">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="J36" s="9">
         <v>4000</v>

--- a/data/CIM_Master_Data.xlsx
+++ b/data/CIM_Master_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\calvi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668E72A2-ED87-450B-B94A-213A270D1E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52531022-64FA-4245-A7BE-BD8712DC1F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2016,34 +2016,34 @@
     <xf numFmtId="169" fontId="7" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2368,23 +2368,23 @@
   <sheetData>
     <row r="1" spans="2:3" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="151" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="140"/>
+      <c r="C2" s="149"/>
     </row>
     <row r="3" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="139" t="s">
+      <c r="B3" s="148" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="140"/>
+      <c r="C3" s="149"/>
     </row>
     <row r="4" spans="2:3" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="141" t="s">
+      <c r="B5" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="140"/>
+      <c r="C5" s="149"/>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
@@ -4707,7 +4707,7 @@
         <v>2026</v>
       </c>
       <c r="I32" s="8">
-        <v>3200</v>
+        <v>32</v>
       </c>
       <c r="J32" s="50">
         <v>5906</v>
@@ -6418,76 +6418,76 @@
       </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A55" s="144" t="s">
+      <c r="A55" s="139" t="s">
         <v>181</v>
       </c>
-      <c r="B55" s="144"/>
-      <c r="C55" s="144"/>
-      <c r="D55" s="144"/>
-      <c r="E55" s="144"/>
-      <c r="F55" s="144"/>
-      <c r="G55" s="144"/>
-      <c r="H55" s="144"/>
-      <c r="I55" s="146">
+      <c r="B55" s="139"/>
+      <c r="C55" s="139"/>
+      <c r="D55" s="139"/>
+      <c r="E55" s="139"/>
+      <c r="F55" s="139"/>
+      <c r="G55" s="139"/>
+      <c r="H55" s="139"/>
+      <c r="I55" s="141">
         <v>1761</v>
       </c>
-      <c r="J55" s="147">
+      <c r="J55" s="142">
         <v>326774</v>
       </c>
-      <c r="K55" s="148"/>
-      <c r="L55" s="148"/>
-      <c r="M55" s="150">
+      <c r="K55" s="143"/>
+      <c r="L55" s="143"/>
+      <c r="M55" s="145">
         <v>17348.099999999999</v>
       </c>
-      <c r="N55" s="150">
+      <c r="N55" s="145">
         <v>3397.099999999999</v>
       </c>
-      <c r="O55" s="151">
+      <c r="O55" s="146">
         <v>0.19581971512730501</v>
       </c>
-      <c r="P55" s="150">
+      <c r="P55" s="145">
         <v>6339</v>
       </c>
-      <c r="Q55" s="148"/>
-      <c r="R55" s="148"/>
-      <c r="S55" s="152">
+      <c r="Q55" s="143"/>
+      <c r="R55" s="143"/>
+      <c r="S55" s="147">
         <v>11435</v>
       </c>
-      <c r="T55" s="144"/>
-      <c r="U55" s="144"/>
-      <c r="V55" s="144"/>
-      <c r="W55" s="144"/>
-      <c r="X55" s="144"/>
-      <c r="Y55" s="144"/>
-      <c r="Z55" s="148"/>
+      <c r="T55" s="139"/>
+      <c r="U55" s="139"/>
+      <c r="V55" s="139"/>
+      <c r="W55" s="139"/>
+      <c r="X55" s="139"/>
+      <c r="Y55" s="139"/>
+      <c r="Z55" s="143"/>
     </row>
     <row r="56" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="145"/>
-      <c r="B56" s="145"/>
-      <c r="C56" s="145"/>
-      <c r="D56" s="145"/>
-      <c r="E56" s="145"/>
-      <c r="F56" s="145"/>
-      <c r="G56" s="145"/>
-      <c r="H56" s="145"/>
-      <c r="I56" s="145"/>
-      <c r="J56" s="145"/>
-      <c r="K56" s="149"/>
-      <c r="L56" s="149"/>
-      <c r="M56" s="149"/>
-      <c r="N56" s="149"/>
-      <c r="O56" s="149"/>
-      <c r="P56" s="149"/>
-      <c r="Q56" s="149"/>
-      <c r="R56" s="149"/>
-      <c r="S56" s="149"/>
-      <c r="T56" s="145"/>
-      <c r="U56" s="145"/>
-      <c r="V56" s="145"/>
-      <c r="W56" s="145"/>
-      <c r="X56" s="145"/>
-      <c r="Y56" s="145"/>
-      <c r="Z56" s="149"/>
+      <c r="A56" s="140"/>
+      <c r="B56" s="140"/>
+      <c r="C56" s="140"/>
+      <c r="D56" s="140"/>
+      <c r="E56" s="140"/>
+      <c r="F56" s="140"/>
+      <c r="G56" s="140"/>
+      <c r="H56" s="140"/>
+      <c r="I56" s="140"/>
+      <c r="J56" s="140"/>
+      <c r="K56" s="144"/>
+      <c r="L56" s="144"/>
+      <c r="M56" s="144"/>
+      <c r="N56" s="144"/>
+      <c r="O56" s="144"/>
+      <c r="P56" s="144"/>
+      <c r="Q56" s="144"/>
+      <c r="R56" s="144"/>
+      <c r="S56" s="144"/>
+      <c r="T56" s="140"/>
+      <c r="U56" s="140"/>
+      <c r="V56" s="140"/>
+      <c r="W56" s="140"/>
+      <c r="X56" s="140"/>
+      <c r="Y56" s="140"/>
+      <c r="Z56" s="144"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:Z56" xr:uid="{00000000-0009-0000-0000-000001000000}">
@@ -6781,17 +6781,17 @@
     <row r="1" spans="2:10" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:10" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="143" t="s">
+      <c r="B3" s="152" t="s">
         <v>214</v>
       </c>
-      <c r="C3" s="140"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="140"/>
-      <c r="I3" s="140"/>
-      <c r="J3" s="140"/>
+      <c r="C3" s="149"/>
+      <c r="D3" s="149"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="149"/>
+      <c r="G3" s="149"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
     </row>
     <row r="4" spans="2:10" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">

--- a/data/CIM_Master_Data.xlsx
+++ b/data/CIM_Master_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\calvi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA70823-AA4A-4580-9C47-24F1B5D9345C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DED93E4-16A6-440C-8B3E-CF2216E43593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Acquisition Cost'!$B$3:$T$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Lease!$B$3:$I$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Locations!$A$2:$AP$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Locations!$A$2:$AP$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Selling Locations 6.9.26'!$A$5:$AX$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Site Info'!$B$3:$M$3</definedName>
   </definedNames>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="670">
   <si>
     <t>Unit ID</t>
   </si>
@@ -810,9 +810,6 @@
   </si>
   <si>
     <t>Westwood (Los Angeles) -- highest AWR location in the portfolio at $514/week; immature as of late 2024 acquisition with significant earnings upside in premium UCLA-area market.</t>
-  </si>
-  <si>
-    <t>TOTALS</t>
   </si>
   <si>
     <t>CIM Master Data — Phenix Salon Suites</t>
@@ -6562,77 +6559,77 @@
     <row r="1" spans="2:3" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="354" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C2" s="352"/>
     </row>
     <row r="3" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="351" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C3" s="352"/>
     </row>
     <row r="4" spans="2:3" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="353" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C5" s="352"/>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -6648,7 +6645,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A2:AQ57"/>
+  <dimension ref="A2:AQ54"/>
   <sheetFormatPr defaultColWidth="9.85546875" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="345" customWidth="1"/>
@@ -6760,10 +6757,10 @@
         <v>27</v>
       </c>
       <c r="AC2" s="81" t="s">
+        <v>668</v>
+      </c>
+      <c r="AD2" s="81" t="s">
         <v>669</v>
-      </c>
-      <c r="AD2" s="81" t="s">
-        <v>670</v>
       </c>
       <c r="AE2" s="81" t="s">
         <v>28</v>
@@ -6864,13 +6861,13 @@
         <v>297.35606971153845</v>
       </c>
       <c r="T3" s="350">
-        <v>1</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="U3" s="77">
-        <v>280.9203328104781</v>
+        <v>262.86276562499995</v>
       </c>
       <c r="V3" s="77">
-        <v>81.675350128122162</v>
+        <v>56.482100937499965</v>
       </c>
       <c r="W3" s="348">
         <v>0.29074203818213518</v>
@@ -6992,13 +6989,13 @@
         <v>229.4735198135198</v>
       </c>
       <c r="T4" s="350">
-        <v>0.91043600823240689</v>
+        <v>0.85227272727272729</v>
       </c>
       <c r="U4" s="77">
-        <v>478.01114589585171</v>
+        <v>453.43967515151513</v>
       </c>
       <c r="V4" s="77">
-        <v>-43.75259527211503</v>
+        <v>-86.189419393939417</v>
       </c>
       <c r="W4" s="348">
         <v>-9.1530491804991884E-2</v>
@@ -7120,13 +7117,13 @@
         <v>248.25245629370642</v>
       </c>
       <c r="T5" s="350">
-        <v>0.7354513131928857</v>
+        <v>0.83333333333333326</v>
       </c>
       <c r="U5" s="77">
-        <v>284.82104817592273</v>
+        <v>322.72819318181831</v>
       </c>
       <c r="V5" s="77">
-        <v>29.608645158037071</v>
+        <v>67.993198227272742</v>
       </c>
       <c r="W5" s="348">
         <v>0.1039552566345061</v>
@@ -7248,13 +7245,13 @@
         <v>270.83271367521365</v>
       </c>
       <c r="T6" s="350">
-        <v>0.80590348984171056</v>
+        <v>0.81451612903225801</v>
       </c>
       <c r="U6" s="77">
-        <v>703.68645386403728</v>
+        <v>718.24835666666661</v>
       </c>
       <c r="V6" s="77">
-        <v>293.73357531386318</v>
+        <v>289.73171466666656</v>
       </c>
       <c r="W6" s="348">
         <v>0.4174211023971437</v>
@@ -7376,13 +7373,13 @@
         <v>300.60475202429149</v>
       </c>
       <c r="T7" s="350">
-        <v>0.96396420615807976</v>
+        <v>0.94047619047619047</v>
       </c>
       <c r="U7" s="77">
-        <v>632.86253099693454</v>
+        <v>625.25788421052619</v>
       </c>
       <c r="V7" s="77">
-        <v>312.09183375522957</v>
+        <v>289.77119594736831</v>
       </c>
       <c r="W7" s="348">
         <v>0.49314316849126483</v>
@@ -7504,13 +7501,13 @@
         <v>361.50343750000008</v>
       </c>
       <c r="T8" s="350">
-        <v>0.548569248194407</v>
+        <v>0.78947368421052633</v>
       </c>
       <c r="U8" s="77">
-        <v>391.85990580383998</v>
+        <v>563.9453625000001</v>
       </c>
       <c r="V8" s="77">
-        <v>128.2124535337781</v>
+        <v>252.22696074999996</v>
       </c>
       <c r="W8" s="348">
         <v>0.32718951756692249</v>
@@ -7632,13 +7629,13 @@
         <v>257.58245562130185</v>
       </c>
       <c r="T9" s="350">
-        <v>0.96315253993550876</v>
+        <v>0.91077586206896555</v>
       </c>
       <c r="U9" s="77">
-        <v>374.1215241327194</v>
+        <v>348.25148000000007</v>
       </c>
       <c r="V9" s="77">
-        <v>159.8290524299133</v>
+        <v>114.40720000000005</v>
       </c>
       <c r="W9" s="348">
         <v>0.42721159334637487</v>
@@ -7760,13 +7757,13 @@
         <v>228.00289743589744</v>
       </c>
       <c r="T10" s="350">
-        <v>1</v>
+        <v>0.9170454545454545</v>
       </c>
       <c r="U10" s="77">
-        <v>424.10288757952861</v>
+        <v>355.68451999999996</v>
       </c>
       <c r="V10" s="77">
-        <v>159.82017272968309</v>
+        <v>60.142679999999956</v>
       </c>
       <c r="W10" s="348">
         <v>0.37684292517275852</v>
@@ -8026,13 +8023,13 @@
         <v>249.98862637362635</v>
       </c>
       <c r="T13" s="350">
-        <v>0.62550401119823462</v>
+        <v>0.7068965517241379</v>
       </c>
       <c r="U13" s="77">
-        <v>235.8042839343652</v>
+        <v>272.98757999999998</v>
       </c>
       <c r="V13" s="77">
-        <v>-11.82045963572258</v>
+        <v>-4.8539380000000065</v>
       </c>
       <c r="W13" s="348">
         <v>-5.0128265010710063E-2</v>
@@ -8154,13 +8151,13 @@
         <v>339.5060336538462</v>
       </c>
       <c r="T14" s="350">
-        <v>0.68540144053338914</v>
+        <v>0.83982683982683981</v>
       </c>
       <c r="U14" s="77">
-        <v>266.2064256693252</v>
+        <v>317.77764750000006</v>
       </c>
       <c r="V14" s="77">
-        <v>28.9352681161654</v>
+        <v>62.371539250000041</v>
       </c>
       <c r="W14" s="348">
         <v>0.1086948522877057</v>
@@ -8282,13 +8279,13 @@
         <v>398.35329487179484</v>
       </c>
       <c r="T15" s="350">
-        <v>0.66896517166667779</v>
+        <v>0.78091397849462363</v>
       </c>
       <c r="U15" s="77">
-        <v>332.5726313992954</v>
+        <v>393.57305533333329</v>
       </c>
       <c r="V15" s="77">
-        <v>37.545574775429259</v>
+        <v>73.099449733333287</v>
       </c>
       <c r="W15" s="348">
         <v>0.1128943612030151</v>
@@ -8410,13 +8407,13 @@
         <v>275.60710526315791</v>
       </c>
       <c r="T16" s="350">
-        <v>0.54351065226726525</v>
+        <v>0.75937500000000002</v>
       </c>
       <c r="U16" s="77">
-        <v>249.2595415249834</v>
+        <v>343.95766736842103</v>
       </c>
       <c r="V16" s="77">
-        <v>-53.967415216125232</v>
+        <v>37.40231315789471</v>
       </c>
       <c r="W16" s="348">
         <v>-0.21651093027753179</v>
@@ -8538,13 +8535,13 @@
         <v>285.01018665158364</v>
       </c>
       <c r="T17" s="350">
-        <v>0.8642873076119808</v>
+        <v>0.9358974358974359</v>
       </c>
       <c r="U17" s="77">
-        <v>499.558632958337</v>
+        <v>548.35959911764689</v>
       </c>
       <c r="V17" s="77">
-        <v>83.926999965964967</v>
+        <v>123.99320238235285</v>
       </c>
       <c r="W17" s="348">
         <v>0.16800230128935531</v>
@@ -8666,13 +8663,13 @@
         <v>323.08482371794867</v>
       </c>
       <c r="T18" s="350">
-        <v>0.85341980345434654</v>
+        <v>0.92592592592592582</v>
       </c>
       <c r="U18" s="77">
-        <v>387.12068940606139</v>
+        <v>420.01027083333327</v>
       </c>
       <c r="V18" s="77">
-        <v>80.722173243960697</v>
+        <v>106.96770758333331</v>
       </c>
       <c r="W18" s="348">
         <v>0.2085193983504432</v>
@@ -8794,13 +8791,13 @@
         <v>260.28130177514794</v>
       </c>
       <c r="T19" s="350">
-        <v>0.95818043285741394</v>
+        <v>0.87159090909090908</v>
       </c>
       <c r="U19" s="77">
-        <v>414.99569346493848</v>
+        <v>378.96957538461538</v>
       </c>
       <c r="V19" s="77">
-        <v>150.3891634649386</v>
+        <v>104.78847876923075</v>
       </c>
       <c r="W19" s="348">
         <v>0.36238728698432721</v>
@@ -8922,13 +8919,13 @@
         <v>277.92254273504273</v>
       </c>
       <c r="T20" s="350">
-        <v>0.73787656681161118</v>
+        <v>0.86956521739130443</v>
       </c>
       <c r="U20" s="77">
-        <v>245.26674788077241</v>
+        <v>289.03944444444443</v>
       </c>
       <c r="V20" s="77">
-        <v>45.149217949668312</v>
+        <v>70.98068111111111</v>
       </c>
       <c r="W20" s="348">
         <v>0.18408209975375861</v>
@@ -9050,13 +9047,13 @@
         <v>299.56252403846156</v>
       </c>
       <c r="T21" s="350">
-        <v>0.75992412527579056</v>
+        <v>0.87096774193548387</v>
       </c>
       <c r="U21" s="77">
-        <v>366.96339994108149</v>
+        <v>420.58578375000002</v>
       </c>
       <c r="V21" s="77">
-        <v>29.981049183506439</v>
+        <v>63.471967624999934</v>
       </c>
       <c r="W21" s="348">
         <v>8.1700379897069034E-2</v>
@@ -9178,13 +9175,13 @@
         <v>314.19451505016724</v>
       </c>
       <c r="T22" s="350">
-        <v>0.98796955873454162</v>
+        <v>0.90740740740740744</v>
       </c>
       <c r="U22" s="77">
-        <v>435.82212141286158</v>
+        <v>408.45286956521738</v>
       </c>
       <c r="V22" s="77">
-        <v>70.275332849068633</v>
+        <v>36.254240695652186</v>
       </c>
       <c r="W22" s="348">
         <v>0.1612477416732494</v>
@@ -9306,13 +9303,13 @@
         <v>289.79206730769232</v>
       </c>
       <c r="T23" s="350">
-        <v>1</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="U23" s="77">
-        <v>380.78029122654829</v>
+        <v>346.59131250000002</v>
       </c>
       <c r="V23" s="77">
-        <v>131.67918244072109</v>
+        <v>100.34152875000001</v>
       </c>
       <c r="W23" s="348">
         <v>0.34581407040937828</v>
@@ -9434,13 +9431,13 @@
         <v>420.14271761133602</v>
       </c>
       <c r="T24" s="350">
-        <v>0.84956633215818178</v>
+        <v>0.88804347826086949</v>
       </c>
       <c r="U24" s="77">
-        <v>853.79834534100814</v>
+        <v>895.74427394736836</v>
       </c>
       <c r="V24" s="77">
-        <v>356.16258287302981</v>
+        <v>363.47024476315789</v>
       </c>
       <c r="W24" s="348">
         <v>0.41715070638931501</v>
@@ -9562,13 +9559,13 @@
         <v>450.91667420814497</v>
       </c>
       <c r="T25" s="350">
-        <v>0.81444529248434094</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="U25" s="77">
-        <v>458.32420933917552</v>
+        <v>468.95334117647081</v>
       </c>
       <c r="V25" s="77">
-        <v>46.003627168838896</v>
+        <v>47.60591082352947</v>
       </c>
       <c r="W25" s="348">
         <v>0.1003735483123796</v>
@@ -9690,13 +9687,13 @@
         <v>355.54478021978025</v>
       </c>
       <c r="T26" s="350">
-        <v>0.60631227188861436</v>
+        <v>0.71951219512195119</v>
       </c>
       <c r="U26" s="77">
-        <v>459.59772048220759</v>
+        <v>554.64985714285717</v>
       </c>
       <c r="V26" s="77">
-        <v>27.921760649692491</v>
+        <v>76.878730000000004</v>
       </c>
       <c r="W26" s="348">
         <v>6.0752609086914343E-2</v>
@@ -9818,13 +9815,13 @@
         <v>476.43459615384626</v>
       </c>
       <c r="T27" s="350">
-        <v>0.86840827092389616</v>
+        <v>0.83333333333333326</v>
       </c>
       <c r="U27" s="77">
-        <v>580.89060037141803</v>
+        <v>569.81577700000014</v>
       </c>
       <c r="V27" s="77">
-        <v>49.219437848422153</v>
+        <v>12.373787899999996</v>
       </c>
       <c r="W27" s="348">
         <v>8.4730993782566849E-2</v>
@@ -9946,13 +9943,13 @@
         <v>261.40319397993312</v>
       </c>
       <c r="T28" s="350">
-        <v>0.97522316268362685</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="U28" s="77">
-        <v>331.40438443932561</v>
+        <v>312.63821999999999</v>
       </c>
       <c r="V28" s="77">
-        <v>78.128853293107923</v>
+        <v>60.67931999999999</v>
       </c>
       <c r="W28" s="348">
         <v>0.23575081369332929</v>
@@ -10074,13 +10071,13 @@
         <v>306.99210664335664</v>
       </c>
       <c r="T29" s="350">
-        <v>0.71227856597951467</v>
+        <v>0.82258064516129026</v>
       </c>
       <c r="U29" s="77">
-        <v>352.48620274898002</v>
+        <v>415.05332818181813</v>
       </c>
       <c r="V29" s="77">
-        <v>56.696265616775321</v>
+        <v>106.46253072727274</v>
       </c>
       <c r="W29" s="348">
         <v>0.16084676556021421</v>
@@ -10202,13 +10199,13 @@
         <v>236.86829670329672</v>
       </c>
       <c r="T30" s="350">
-        <v>0.98550976146985714</v>
+        <v>0.95227272727272727</v>
       </c>
       <c r="U30" s="77">
-        <v>267.05080525990991</v>
+        <v>258.66018000000003</v>
       </c>
       <c r="V30" s="77">
-        <v>72.742204048192932</v>
+        <v>55.143850000000029</v>
       </c>
       <c r="W30" s="348">
         <v>0.27239088074419338</v>
@@ -10333,13 +10330,13 @@
         <v>261.96634615384613</v>
       </c>
       <c r="T31" s="350">
-        <v>0.96059243781507841</v>
+        <v>0.92327586206896539</v>
       </c>
       <c r="U31" s="77">
-        <v>379.47747974476709</v>
+        <v>367.80074999999994</v>
       </c>
       <c r="V31" s="77">
-        <v>116.34020953242469</v>
+        <v>103.66692499999996</v>
       </c>
       <c r="W31" s="348">
         <v>0.3065800099934099</v>
@@ -10461,13 +10458,13 @@
         <v>224.94285256410257</v>
       </c>
       <c r="T32" s="350">
-        <v>0.98514347073507913</v>
+        <v>0.93653846153846143</v>
       </c>
       <c r="U32" s="77">
-        <v>299.60452832925051</v>
+        <v>280.72867999999994</v>
       </c>
       <c r="V32" s="77">
-        <v>39.531303057128127</v>
+        <v>20.956519999999962</v>
       </c>
       <c r="W32" s="348">
         <v>0.13194494515011199</v>
@@ -10589,13 +10586,13 @@
         <v>247.04104020979022</v>
       </c>
       <c r="T33" s="350">
-        <v>0.80542385429353902</v>
+        <v>0.85</v>
       </c>
       <c r="U33" s="77">
-        <v>310.39748496814889</v>
+        <v>333.99948636363638</v>
       </c>
       <c r="V33" s="77">
-        <v>48.887227725368099</v>
+        <v>63.702835454545493</v>
       </c>
       <c r="W33" s="348">
         <v>0.15749878814380411</v>
@@ -10717,13 +10714,13 @@
         <v>299.37726648351651</v>
       </c>
       <c r="T34" s="350">
-        <v>0.77769711192371915</v>
+        <v>0.79149048625792817</v>
       </c>
       <c r="U34" s="77">
-        <v>520.59633222238108</v>
+        <v>529.29900714285725</v>
       </c>
       <c r="V34" s="77">
-        <v>178.81982625076259</v>
+        <v>159.58184500000004</v>
       </c>
       <c r="W34" s="348">
         <v>0.34349036899164481</v>
@@ -10845,13 +10842,13 @@
         <v>376.85453846153848</v>
       </c>
       <c r="T35" s="350">
-        <v>0.83783783783783805</v>
+        <v>0.89189189189189189</v>
       </c>
       <c r="U35" s="77">
-        <v>607.48951599999998</v>
+        <v>646.68238800000006</v>
       </c>
       <c r="V35" s="77">
-        <v>182.53849799999998</v>
+        <v>213.8927956</v>
       </c>
       <c r="W35" s="348">
         <v>0.30048007939613558</v>
@@ -10973,13 +10970,13 @@
         <v>250.18626602564106</v>
       </c>
       <c r="T36" s="350">
-        <v>0.88172106660665261</v>
+        <v>0.9</v>
       </c>
       <c r="U36" s="77">
-        <v>344.12742207552378</v>
+        <v>351.26151750000002</v>
       </c>
       <c r="V36" s="77">
-        <v>163.35430470277069</v>
+        <v>128.57973025000001</v>
       </c>
       <c r="W36" s="348">
         <v>0.474691332988047</v>
@@ -11101,13 +11098,13 @@
         <v>283.72989583333333</v>
       </c>
       <c r="T37" s="350">
-        <v>0.73475619421338567</v>
+        <v>0.76995565410199562</v>
       </c>
       <c r="U37" s="77">
-        <v>444.46294028913269</v>
+        <v>472.12654666666663</v>
       </c>
       <c r="V37" s="77">
-        <v>39.703766716225239</v>
+        <v>110.05066566666662</v>
       </c>
       <c r="W37" s="348">
         <v>8.9329757595531106E-2</v>
@@ -11229,13 +11226,13 @@
         <v>305.17134615384617</v>
       </c>
       <c r="T38" s="350">
-        <v>0.90923882490876839</v>
+        <v>0.91249999999999998</v>
       </c>
       <c r="U38" s="77">
-        <v>692.57419588718426</v>
+        <v>698.23203999999998</v>
       </c>
       <c r="V38" s="77">
-        <v>258.02606586463151</v>
+        <v>266.30890399999993</v>
       </c>
       <c r="W38" s="348">
         <v>0.37256090018499938</v>
@@ -11357,13 +11354,13 @@
         <v>240.82234113712377</v>
       </c>
       <c r="T39" s="350">
-        <v>0.74230239946857601</v>
+        <v>0.79848484848484858</v>
       </c>
       <c r="U39" s="77">
-        <v>306.75731086868342</v>
+        <v>325.59180521739131</v>
       </c>
       <c r="V39" s="77">
-        <v>-46.09905302313372</v>
+        <v>-18.055150347826075</v>
       </c>
       <c r="W39" s="348">
         <v>-0.15027857980821779</v>
@@ -11485,13 +11482,13 @@
         <v>346.72228632478624</v>
       </c>
       <c r="T40" s="350">
-        <v>0.79694119845324363</v>
+        <v>0.87678571428571428</v>
       </c>
       <c r="U40" s="77">
-        <v>804.63590303568867</v>
+        <v>883.44838555555521</v>
       </c>
       <c r="V40" s="77">
-        <v>259.0786260063918</v>
+        <v>324.0959548888888</v>
       </c>
       <c r="W40" s="348">
         <v>0.32198243333283211</v>
@@ -11613,13 +11610,13 @@
         <v>318.46743006993006</v>
       </c>
       <c r="T41" s="350">
-        <v>1</v>
+        <v>0.97727272727272729</v>
       </c>
       <c r="U41" s="77">
-        <v>376.5556293473706</v>
+        <v>364.32673999999997</v>
       </c>
       <c r="V41" s="77">
-        <v>91.614149755116969</v>
+        <v>121.31479</v>
       </c>
       <c r="W41" s="348">
         <v>0.24329512724029259</v>
@@ -11741,13 +11738,13 @@
         <v>279.30067307692298</v>
       </c>
       <c r="T42" s="350">
-        <v>0.92297868783249548</v>
+        <v>0.89024390243902429</v>
       </c>
       <c r="U42" s="77">
-        <v>549.60522856918215</v>
+        <v>537.3744949999998</v>
       </c>
       <c r="V42" s="77">
-        <v>80.830352469316594</v>
+        <v>60.686353499999896</v>
       </c>
       <c r="W42" s="348">
         <v>0.14706983898196671</v>
@@ -11869,13 +11866,13 @@
         <v>369.93563275434246</v>
       </c>
       <c r="T43" s="350">
-        <v>0.82055464443204107</v>
+        <v>0.85555555555555562</v>
       </c>
       <c r="U43" s="77">
-        <v>647.1737202058307</v>
+        <v>673.28285161290319</v>
       </c>
       <c r="V43" s="77">
-        <v>135.60521315608241</v>
+        <v>139.53116812903227</v>
       </c>
       <c r="W43" s="348">
         <v>0.20953448652543211</v>
@@ -12000,13 +11997,13 @@
         <v>288.28824239713771</v>
       </c>
       <c r="T44" s="350">
-        <v>0.96860882271037874</v>
+        <v>0.94565217391304346</v>
       </c>
       <c r="U44" s="77">
-        <v>667.93857588632977</v>
+        <v>659.60349860465112</v>
       </c>
       <c r="V44" s="77">
-        <v>232.52974034935511</v>
+        <v>201.14603202325574</v>
       </c>
       <c r="W44" s="348">
         <v>0.34813042507807951</v>
@@ -12128,13 +12125,13 @@
         <v>319.08662721893484</v>
       </c>
       <c r="T45" s="350">
-        <v>1</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="U45" s="77">
-        <v>732.04782797790767</v>
+        <v>663.70018461538439</v>
       </c>
       <c r="V45" s="77">
-        <v>223.06638443930291</v>
+        <v>148.31753323076916</v>
       </c>
       <c r="W45" s="348">
         <v>0.30471558812689331</v>
@@ -12256,13 +12253,13 @@
         <v>253.63301975051974</v>
       </c>
       <c r="T46" s="350">
-        <v>0.78775828376551205</v>
+        <v>0.77419354838709675</v>
       </c>
       <c r="U46" s="77">
-        <v>644.16007580006601</v>
+        <v>633.06801729729727</v>
       </c>
       <c r="V46" s="77">
-        <v>114.1120072911406</v>
+        <v>60.343391108108051</v>
       </c>
       <c r="W46" s="348">
         <v>0.17714852499886791</v>
@@ -12456,13 +12453,13 @@
         <v>289.76781425891181</v>
       </c>
       <c r="T48" s="350">
-        <v>0.99861901902425942</v>
+        <v>0.92682926829268286</v>
       </c>
       <c r="U48" s="77">
-        <v>677.12030198288971</v>
+        <v>632.85290634146338</v>
       </c>
       <c r="V48" s="77">
-        <v>214.6660152567112</v>
+        <v>177.35499843902426</v>
       </c>
       <c r="W48" s="348">
         <v>0.31702788208842642</v>
@@ -12584,13 +12581,13 @@
         <v>304.09850732600734</v>
       </c>
       <c r="T49" s="350">
-        <v>0.75176749367196005</v>
+        <v>0.81666666666666665</v>
       </c>
       <c r="U49" s="77">
-        <v>356.63374138369642</v>
+        <v>395.32805952380954</v>
       </c>
       <c r="V49" s="77">
-        <v>49.15025563761148</v>
+        <v>120.45910266666664</v>
       </c>
       <c r="W49" s="348">
         <v>0.13781717749676281</v>
@@ -12784,13 +12781,13 @@
         <v>192.23014170040486</v>
       </c>
       <c r="T51" s="350">
-        <v>0.66808659521138025</v>
+        <v>0.74687499999999996</v>
       </c>
       <c r="U51" s="77">
-        <v>213.70149776039941</v>
+        <v>239.90321684210525</v>
       </c>
       <c r="V51" s="77">
-        <v>-32.476467932671348</v>
+        <v>-21.855814210526333</v>
       </c>
       <c r="W51" s="348">
         <v>-0.1519711760236877</v>
@@ -12912,13 +12909,13 @@
         <v>277.70612980769232</v>
       </c>
       <c r="T52" s="350">
-        <v>0.81023561194398241</v>
+        <v>0.89655172413793105</v>
       </c>
       <c r="U52" s="77">
-        <v>339.31115320619853</v>
+        <v>375.4586875</v>
       </c>
       <c r="V52" s="77">
-        <v>95.780772355320991</v>
+        <v>124.98182625</v>
       </c>
       <c r="W52" s="348">
         <v>0.28228005902628039</v>
@@ -13040,13 +13037,13 @@
         <v>228.90352357320097</v>
       </c>
       <c r="T53" s="350">
-        <v>0.92232461882481254</v>
+        <v>0.92647058823529405</v>
       </c>
       <c r="U53" s="77">
-        <v>373.26609186508239</v>
+        <v>380.8954632258064</v>
       </c>
       <c r="V53" s="77">
-        <v>108.83077641945749</v>
+        <v>113.33408825806437</v>
       </c>
       <c r="W53" s="348">
         <v>0.29156352208599368</v>
@@ -13168,13 +13165,13 @@
         <v>240.92704415954424</v>
       </c>
       <c r="T54" s="350">
-        <v>1</v>
+        <v>0.96551724137931028</v>
       </c>
       <c r="U54" s="77">
-        <v>364.2558658084223</v>
+        <v>350.7897762962964</v>
       </c>
       <c r="V54" s="77">
-        <v>180.72951839975801</v>
+        <v>152.09744440740738</v>
       </c>
       <c r="W54" s="348">
         <v>0.49616090052153439</v>
@@ -13237,35 +13234,8 @@
         <v>194</v>
       </c>
     </row>
-    <row r="55" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="T55" s="350"/>
-      <c r="X55" s="77"/>
-      <c r="AL55" s="347"/>
-      <c r="AM55" s="347"/>
-    </row>
-    <row r="56" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="A56" s="345" t="s">
-        <v>239</v>
-      </c>
-      <c r="J56" s="347">
-        <v>1779</v>
-      </c>
-      <c r="K56" s="347">
-        <v>326774</v>
-      </c>
-      <c r="T56" s="350"/>
-      <c r="X56" s="77"/>
-      <c r="AL56" s="347"/>
-      <c r="AM56" s="347"/>
-    </row>
-    <row r="57" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="T57" s="350"/>
-      <c r="X57" s="77"/>
-      <c r="AL57" s="347"/>
-      <c r="AM57" s="347"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:AP57" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A2:AP54" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13293,25 +13263,25 @@
         <v>38</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>263</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>39</v>
@@ -13322,19 +13292,19 @@
         <v>110</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="E3" s="7">
         <v>3950</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G3" s="8">
         <v>5</v>
@@ -13343,7 +13313,7 @@
         <v>181</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -13351,13 +13321,13 @@
         <v>52</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>270</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5" t="s">
@@ -13370,7 +13340,7 @@
         <v>267</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -13381,10 +13351,10 @@
         <v>94</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5" t="s">
@@ -13397,7 +13367,7 @@
         <v>133</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -13408,14 +13378,14 @@
         <v>82</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G6" s="8">
         <v>4</v>
@@ -13424,7 +13394,7 @@
         <v>124</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -13432,13 +13402,13 @@
         <v>44</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5" t="s">
@@ -13451,7 +13421,7 @@
         <v>296</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -13459,13 +13429,13 @@
         <v>58</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>280</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>281</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5" t="s">
@@ -13478,7 +13448,7 @@
         <v>308</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -13486,13 +13456,13 @@
         <v>65</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
@@ -13505,7 +13475,7 @@
         <v>368</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -13513,13 +13483,13 @@
         <v>99</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>286</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>287</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5" t="s">
@@ -13530,7 +13500,7 @@
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -13555,7 +13525,7 @@
     <row r="2" spans="2:10" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="355" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C3" s="352"/>
       <c r="D3" s="352"/>
@@ -13569,10 +13539,10 @@
     <row r="4" spans="2:10" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>290</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>291</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>9</v>
@@ -13581,19 +13551,19 @@
         <v>10</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>295</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -13826,7 +13796,7 @@
     </row>
     <row r="14" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="49" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C14" s="50">
         <v>51</v>
@@ -13874,7 +13844,7 @@
   <sheetData>
     <row r="1" spans="1:52" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="62" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -13980,25 +13950,25 @@
     </row>
     <row r="3" spans="1:52" s="58" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="68" t="s">
+        <v>298</v>
+      </c>
+      <c r="C3" s="69" t="s">
         <v>299</v>
       </c>
-      <c r="C3" s="69" t="s">
+      <c r="D3" s="69" t="s">
         <v>300</v>
       </c>
-      <c r="D3" s="69" t="s">
+      <c r="E3" s="69" t="s">
         <v>301</v>
       </c>
-      <c r="E3" s="69" t="s">
+      <c r="F3" s="70" t="s">
         <v>302</v>
-      </c>
-      <c r="F3" s="70" t="s">
-        <v>303</v>
       </c>
       <c r="G3" s="69" t="s">
         <v>32</v>
       </c>
       <c r="H3" s="70" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I3" s="70" t="s">
         <v>34</v>
@@ -14009,13 +13979,13 @@
         <v>7008</v>
       </c>
       <c r="C4" s="56" t="s">
+        <v>304</v>
+      </c>
+      <c r="D4" s="56" t="s">
         <v>305</v>
       </c>
-      <c r="D4" s="56" t="s">
+      <c r="E4" s="56" t="s">
         <v>306</v>
-      </c>
-      <c r="E4" s="56" t="s">
-        <v>307</v>
       </c>
       <c r="F4" s="60">
         <v>47848</v>
@@ -14035,13 +14005,13 @@
         <v>1501</v>
       </c>
       <c r="C5" s="56" t="s">
+        <v>307</v>
+      </c>
+      <c r="D5" s="56" t="s">
         <v>308</v>
       </c>
-      <c r="D5" s="56" t="s">
+      <c r="E5" s="56" t="s">
         <v>309</v>
-      </c>
-      <c r="E5" s="56" t="s">
-        <v>310</v>
       </c>
       <c r="F5" s="60">
         <v>47299</v>
@@ -14061,13 +14031,13 @@
         <v>2005</v>
       </c>
       <c r="C6" s="56" t="s">
+        <v>310</v>
+      </c>
+      <c r="D6" s="56" t="s">
         <v>311</v>
       </c>
-      <c r="D6" s="56" t="s">
-        <v>312</v>
-      </c>
       <c r="E6" s="56" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F6" s="60">
         <v>50222</v>
@@ -14087,13 +14057,13 @@
         <v>7002</v>
       </c>
       <c r="C7" s="56" t="s">
+        <v>312</v>
+      </c>
+      <c r="D7" s="56" t="s">
         <v>313</v>
       </c>
-      <c r="D7" s="56" t="s">
+      <c r="E7" s="56" t="s">
         <v>314</v>
-      </c>
-      <c r="E7" s="56" t="s">
-        <v>315</v>
       </c>
       <c r="F7" s="60">
         <v>47483</v>
@@ -14113,13 +14083,13 @@
         <v>2010</v>
       </c>
       <c r="C8" s="56" t="s">
+        <v>315</v>
+      </c>
+      <c r="D8" s="56" t="s">
         <v>316</v>
       </c>
-      <c r="D8" s="56" t="s">
+      <c r="E8" s="56" t="s">
         <v>317</v>
-      </c>
-      <c r="E8" s="56" t="s">
-        <v>318</v>
       </c>
       <c r="F8" s="60">
         <v>47695</v>
@@ -14139,13 +14109,13 @@
         <v>8007</v>
       </c>
       <c r="C9" s="56" t="s">
+        <v>318</v>
+      </c>
+      <c r="D9" s="56" t="s">
         <v>319</v>
       </c>
-      <c r="D9" s="56" t="s">
+      <c r="E9" s="56" t="s">
         <v>320</v>
-      </c>
-      <c r="E9" s="56" t="s">
-        <v>321</v>
       </c>
       <c r="F9" s="60">
         <v>46965</v>
@@ -14165,13 +14135,13 @@
         <v>9004</v>
       </c>
       <c r="C10" s="56" t="s">
+        <v>321</v>
+      </c>
+      <c r="D10" s="56" t="s">
         <v>322</v>
       </c>
-      <c r="D10" s="56" t="s">
+      <c r="E10" s="56" t="s">
         <v>323</v>
-      </c>
-      <c r="E10" s="56" t="s">
-        <v>324</v>
       </c>
       <c r="F10" s="60">
         <v>46843</v>
@@ -14191,13 +14161,13 @@
         <v>1504</v>
       </c>
       <c r="C11" s="56" t="s">
+        <v>324</v>
+      </c>
+      <c r="D11" s="56" t="s">
         <v>325</v>
       </c>
-      <c r="D11" s="56" t="s">
-        <v>326</v>
-      </c>
       <c r="E11" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F11" s="60">
         <v>48822</v>
@@ -14217,13 +14187,13 @@
         <v>2002</v>
       </c>
       <c r="C12" s="56" t="s">
+        <v>326</v>
+      </c>
+      <c r="D12" s="56" t="s">
         <v>327</v>
       </c>
-      <c r="D12" s="56" t="s">
-        <v>328</v>
-      </c>
       <c r="E12" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F12" s="60">
         <v>47452</v>
@@ -14243,13 +14213,13 @@
         <v>8008</v>
       </c>
       <c r="C13" s="56" t="s">
+        <v>328</v>
+      </c>
+      <c r="D13" s="56" t="s">
         <v>329</v>
       </c>
-      <c r="D13" s="56" t="s">
-        <v>330</v>
-      </c>
       <c r="E13" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F13" s="60">
         <v>48304</v>
@@ -14269,13 +14239,13 @@
         <v>1001</v>
       </c>
       <c r="C14" s="56" t="s">
+        <v>330</v>
+      </c>
+      <c r="D14" s="56" t="s">
         <v>331</v>
       </c>
-      <c r="D14" s="56" t="s">
+      <c r="E14" s="56" t="s">
         <v>332</v>
-      </c>
-      <c r="E14" s="56" t="s">
-        <v>333</v>
       </c>
       <c r="F14" s="60">
         <v>47938</v>
@@ -14295,13 +14265,13 @@
         <v>6501</v>
       </c>
       <c r="C15" s="56" t="s">
+        <v>333</v>
+      </c>
+      <c r="D15" s="56" t="s">
         <v>334</v>
       </c>
-      <c r="D15" s="56" t="s">
-        <v>335</v>
-      </c>
       <c r="E15" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F15" s="60">
         <v>49738</v>
@@ -14321,13 +14291,13 @@
         <v>9002</v>
       </c>
       <c r="C16" s="56" t="s">
+        <v>335</v>
+      </c>
+      <c r="D16" s="56" t="s">
         <v>336</v>
       </c>
-      <c r="D16" s="56" t="s">
-        <v>337</v>
-      </c>
       <c r="E16" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F16" s="60">
         <v>46599</v>
@@ -14347,13 +14317,13 @@
         <v>6003</v>
       </c>
       <c r="C17" s="56" t="s">
+        <v>337</v>
+      </c>
+      <c r="D17" s="56" t="s">
         <v>338</v>
       </c>
-      <c r="D17" s="56" t="s">
-        <v>339</v>
-      </c>
       <c r="E17" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F17" s="60">
         <v>47756</v>
@@ -14373,13 +14343,13 @@
         <v>1502</v>
       </c>
       <c r="C18" s="56" t="s">
+        <v>339</v>
+      </c>
+      <c r="D18" s="56" t="s">
         <v>340</v>
       </c>
-      <c r="D18" s="56" t="s">
+      <c r="E18" s="56" t="s">
         <v>341</v>
-      </c>
-      <c r="E18" s="56" t="s">
-        <v>342</v>
       </c>
       <c r="F18" s="60">
         <v>50282</v>
@@ -14399,13 +14369,13 @@
         <v>1503</v>
       </c>
       <c r="C19" s="56" t="s">
+        <v>342</v>
+      </c>
+      <c r="D19" s="56" t="s">
         <v>343</v>
       </c>
-      <c r="D19" s="56" t="s">
-        <v>344</v>
-      </c>
       <c r="E19" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F19" s="60">
         <v>48699</v>
@@ -14425,13 +14395,13 @@
         <v>6004</v>
       </c>
       <c r="C20" s="56" t="s">
+        <v>344</v>
+      </c>
+      <c r="D20" s="56" t="s">
         <v>345</v>
       </c>
-      <c r="D20" s="56" t="s">
-        <v>346</v>
-      </c>
       <c r="E20" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F20" s="60">
         <v>47330</v>
@@ -14451,13 +14421,13 @@
         <v>6002</v>
       </c>
       <c r="C21" s="56" t="s">
+        <v>346</v>
+      </c>
+      <c r="D21" s="56" t="s">
         <v>347</v>
       </c>
-      <c r="D21" s="56" t="s">
-        <v>348</v>
-      </c>
       <c r="E21" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F21" s="60">
         <v>48121</v>
@@ -14477,13 +14447,13 @@
         <v>5001</v>
       </c>
       <c r="C22" s="56" t="s">
+        <v>348</v>
+      </c>
+      <c r="D22" s="56" t="s">
         <v>349</v>
       </c>
-      <c r="D22" s="56" t="s">
-        <v>350</v>
-      </c>
       <c r="E22" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F22" s="60">
         <v>46691</v>
@@ -14503,13 +14473,13 @@
         <v>4000</v>
       </c>
       <c r="C23" s="56" t="s">
+        <v>350</v>
+      </c>
+      <c r="D23" s="56" t="s">
         <v>351</v>
       </c>
-      <c r="D23" s="56" t="s">
-        <v>352</v>
-      </c>
       <c r="E23" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F23" s="60">
         <v>48152</v>
@@ -14529,13 +14499,13 @@
         <v>1506</v>
       </c>
       <c r="C24" s="56" t="s">
+        <v>352</v>
+      </c>
+      <c r="D24" s="56" t="s">
         <v>353</v>
       </c>
-      <c r="D24" s="56" t="s">
-        <v>354</v>
-      </c>
       <c r="E24" s="56" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F24" s="60">
         <v>50982</v>
@@ -14555,13 +14525,13 @@
         <v>1002</v>
       </c>
       <c r="C25" s="56" t="s">
+        <v>354</v>
+      </c>
+      <c r="D25" s="56" t="s">
         <v>355</v>
       </c>
-      <c r="D25" s="56" t="s">
+      <c r="E25" s="56" t="s">
         <v>356</v>
-      </c>
-      <c r="E25" s="56" t="s">
-        <v>357</v>
       </c>
       <c r="F25" s="60">
         <v>47938</v>
@@ -14581,13 +14551,13 @@
         <v>8006</v>
       </c>
       <c r="C26" s="56" t="s">
+        <v>357</v>
+      </c>
+      <c r="D26" s="56" t="s">
         <v>358</v>
       </c>
-      <c r="D26" s="56" t="s">
-        <v>359</v>
-      </c>
       <c r="E26" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F26" s="60">
         <v>49400</v>
@@ -14607,13 +14577,13 @@
         <v>9003</v>
       </c>
       <c r="C27" s="56" t="s">
+        <v>359</v>
+      </c>
+      <c r="D27" s="56" t="s">
         <v>360</v>
       </c>
-      <c r="D27" s="56" t="s">
-        <v>361</v>
-      </c>
       <c r="E27" s="56" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F27" s="60">
         <v>46721</v>
@@ -14633,13 +14603,13 @@
         <v>6502</v>
       </c>
       <c r="C28" s="56" t="s">
+        <v>361</v>
+      </c>
+      <c r="D28" s="56" t="s">
         <v>362</v>
       </c>
-      <c r="D28" s="56" t="s">
-        <v>363</v>
-      </c>
       <c r="E28" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F28" s="60">
         <v>49979</v>
@@ -14659,13 +14629,13 @@
         <v>1510</v>
       </c>
       <c r="C29" s="56" t="s">
+        <v>363</v>
+      </c>
+      <c r="D29" s="56" t="s">
         <v>364</v>
       </c>
-      <c r="D29" s="56" t="s">
-        <v>365</v>
-      </c>
       <c r="E29" s="56" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F29" s="60">
         <v>46783</v>
@@ -14685,13 +14655,13 @@
         <v>7007</v>
       </c>
       <c r="C30" s="56" t="s">
+        <v>365</v>
+      </c>
+      <c r="D30" s="56" t="s">
         <v>366</v>
       </c>
-      <c r="D30" s="56" t="s">
-        <v>367</v>
-      </c>
       <c r="E30" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F30" s="60">
         <v>49003</v>
@@ -14711,13 +14681,13 @@
         <v>2006</v>
       </c>
       <c r="C31" s="56" t="s">
+        <v>367</v>
+      </c>
+      <c r="D31" s="56" t="s">
         <v>368</v>
       </c>
-      <c r="D31" s="56" t="s">
-        <v>369</v>
-      </c>
       <c r="E31" s="56" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F31" s="60">
         <v>46599</v>
@@ -14737,13 +14707,13 @@
         <v>7005</v>
       </c>
       <c r="C32" s="56" t="s">
+        <v>369</v>
+      </c>
+      <c r="D32" s="56" t="s">
         <v>370</v>
       </c>
-      <c r="D32" s="56" t="s">
-        <v>371</v>
-      </c>
       <c r="E32" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F32" s="60">
         <v>48610</v>
@@ -14763,13 +14733,13 @@
         <v>7004</v>
       </c>
       <c r="C33" s="56" t="s">
+        <v>371</v>
+      </c>
+      <c r="D33" s="56" t="s">
         <v>372</v>
       </c>
-      <c r="D33" s="56" t="s">
-        <v>373</v>
-      </c>
       <c r="E33" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F33" s="60">
         <v>47542</v>
@@ -14789,13 +14759,13 @@
         <v>5000</v>
       </c>
       <c r="C34" s="56" t="s">
+        <v>373</v>
+      </c>
+      <c r="D34" s="56" t="s">
         <v>374</v>
       </c>
-      <c r="D34" s="56" t="s">
-        <v>375</v>
-      </c>
       <c r="E34" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F34" s="60">
         <v>46507</v>
@@ -14815,13 +14785,13 @@
         <v>8003</v>
       </c>
       <c r="C35" s="56" t="s">
+        <v>375</v>
+      </c>
+      <c r="D35" s="56" t="s">
         <v>376</v>
       </c>
-      <c r="D35" s="56" t="s">
-        <v>377</v>
-      </c>
       <c r="E35" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F35" s="60">
         <v>47543</v>
@@ -14841,13 +14811,13 @@
         <v>2003</v>
       </c>
       <c r="C36" s="56" t="s">
+        <v>377</v>
+      </c>
+      <c r="D36" s="56" t="s">
         <v>378</v>
       </c>
-      <c r="D36" s="56" t="s">
-        <v>379</v>
-      </c>
       <c r="E36" s="56" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F36" s="60">
         <v>49795</v>
@@ -14867,13 +14837,13 @@
         <v>1505</v>
       </c>
       <c r="C37" s="56" t="s">
+        <v>379</v>
+      </c>
+      <c r="D37" s="56" t="s">
         <v>380</v>
       </c>
-      <c r="D37" s="56" t="s">
-        <v>381</v>
-      </c>
       <c r="E37" s="56" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F37" s="60">
         <v>48791</v>
@@ -14893,13 +14863,13 @@
         <v>2004</v>
       </c>
       <c r="C38" s="56" t="s">
+        <v>381</v>
+      </c>
+      <c r="D38" s="56" t="s">
         <v>382</v>
       </c>
-      <c r="D38" s="56" t="s">
-        <v>383</v>
-      </c>
       <c r="E38" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F38" s="60">
         <v>48883</v>
@@ -14919,13 +14889,13 @@
         <v>7006</v>
       </c>
       <c r="C39" s="56" t="s">
+        <v>383</v>
+      </c>
+      <c r="D39" s="56" t="s">
         <v>384</v>
       </c>
-      <c r="D39" s="56" t="s">
+      <c r="E39" s="56" t="s">
         <v>385</v>
-      </c>
-      <c r="E39" s="56" t="s">
-        <v>386</v>
       </c>
       <c r="F39" s="60">
         <v>46507</v>
@@ -14945,13 +14915,13 @@
         <v>7009</v>
       </c>
       <c r="C40" s="56" t="s">
+        <v>386</v>
+      </c>
+      <c r="D40" s="56" t="s">
         <v>387</v>
       </c>
-      <c r="D40" s="56" t="s">
+      <c r="E40" s="56" t="s">
         <v>388</v>
-      </c>
-      <c r="E40" s="56" t="s">
-        <v>389</v>
       </c>
       <c r="F40" s="60">
         <v>47238</v>
@@ -14971,13 +14941,13 @@
         <v>3500</v>
       </c>
       <c r="C41" s="56" t="s">
+        <v>389</v>
+      </c>
+      <c r="D41" s="56" t="s">
         <v>390</v>
       </c>
-      <c r="D41" s="56" t="s">
-        <v>391</v>
-      </c>
       <c r="E41" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F41" s="60">
         <v>49552</v>
@@ -14997,13 +14967,13 @@
         <v>9001</v>
       </c>
       <c r="C42" s="56" t="s">
+        <v>391</v>
+      </c>
+      <c r="D42" s="56" t="s">
         <v>392</v>
       </c>
-      <c r="D42" s="56" t="s">
-        <v>393</v>
-      </c>
       <c r="E42" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F42" s="60">
         <v>46630</v>
@@ -15023,13 +14993,13 @@
         <v>8002</v>
       </c>
       <c r="C43" s="56" t="s">
+        <v>393</v>
+      </c>
+      <c r="D43" s="56" t="s">
         <v>394</v>
       </c>
-      <c r="D43" s="56" t="s">
-        <v>395</v>
-      </c>
       <c r="E43" s="56" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F43" s="60">
         <v>46942</v>
@@ -15049,13 +15019,13 @@
         <v>7003</v>
       </c>
       <c r="C44" s="56" t="s">
+        <v>395</v>
+      </c>
+      <c r="D44" s="56" t="s">
         <v>396</v>
       </c>
-      <c r="D44" s="56" t="s">
-        <v>397</v>
-      </c>
       <c r="E44" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F44" s="60">
         <v>48365</v>
@@ -15075,13 +15045,13 @@
         <v>8004</v>
       </c>
       <c r="C45" s="56" t="s">
+        <v>397</v>
+      </c>
+      <c r="D45" s="56" t="s">
         <v>398</v>
       </c>
-      <c r="D45" s="56" t="s">
-        <v>399</v>
-      </c>
       <c r="E45" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F45" s="60">
         <v>47998</v>
@@ -15101,13 +15071,13 @@
         <v>6001</v>
       </c>
       <c r="C46" s="56" t="s">
+        <v>399</v>
+      </c>
+      <c r="D46" s="56" t="s">
         <v>400</v>
       </c>
-      <c r="D46" s="56" t="s">
-        <v>401</v>
-      </c>
       <c r="E46" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F46" s="60">
         <v>49460</v>
@@ -15127,13 +15097,13 @@
         <v>1003</v>
       </c>
       <c r="C47" s="56" t="s">
+        <v>401</v>
+      </c>
+      <c r="D47" s="56" t="s">
         <v>402</v>
       </c>
-      <c r="D47" s="56" t="s">
-        <v>403</v>
-      </c>
       <c r="E47" s="56" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F47" s="60">
         <v>46752</v>
@@ -15153,13 +15123,13 @@
         <v>2008</v>
       </c>
       <c r="C48" s="56" t="s">
+        <v>403</v>
+      </c>
+      <c r="D48" s="56" t="s">
         <v>404</v>
       </c>
-      <c r="D48" s="56" t="s">
+      <c r="E48" s="56" t="s">
         <v>405</v>
-      </c>
-      <c r="E48" s="56" t="s">
-        <v>406</v>
       </c>
       <c r="F48" s="60">
         <v>47208</v>
@@ -15179,13 +15149,13 @@
         <v>2009</v>
       </c>
       <c r="C49" s="56" t="s">
+        <v>406</v>
+      </c>
+      <c r="D49" s="56" t="s">
         <v>407</v>
       </c>
-      <c r="D49" s="56" t="s">
-        <v>408</v>
-      </c>
       <c r="E49" s="56" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F49" s="60">
         <v>46752</v>
@@ -15205,13 +15175,13 @@
         <v>8001</v>
       </c>
       <c r="C50" s="56" t="s">
+        <v>408</v>
+      </c>
+      <c r="D50" s="56" t="s">
         <v>409</v>
       </c>
-      <c r="D50" s="56" t="s">
-        <v>410</v>
-      </c>
       <c r="E50" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F50" s="60">
         <v>47787</v>
@@ -15231,13 +15201,13 @@
         <v>8005</v>
       </c>
       <c r="C51" s="56" t="s">
+        <v>410</v>
+      </c>
+      <c r="D51" s="56" t="s">
         <v>411</v>
       </c>
-      <c r="D51" s="56" t="s">
-        <v>412</v>
-      </c>
       <c r="E51" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F51" s="60">
         <v>48456</v>
@@ -15257,13 +15227,13 @@
         <v>7001</v>
       </c>
       <c r="C52" s="56" t="s">
+        <v>412</v>
+      </c>
+      <c r="D52" s="56" t="s">
         <v>413</v>
       </c>
-      <c r="D52" s="56" t="s">
-        <v>414</v>
-      </c>
       <c r="E52" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F52" s="60">
         <v>47299</v>
@@ -15283,13 +15253,13 @@
         <v>2011</v>
       </c>
       <c r="C53" s="56" t="s">
+        <v>414</v>
+      </c>
+      <c r="D53" s="56" t="s">
         <v>415</v>
       </c>
-      <c r="D53" s="56" t="s">
-        <v>416</v>
-      </c>
       <c r="E53" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F53" s="60">
         <v>48213</v>
@@ -15309,13 +15279,13 @@
         <v>2012</v>
       </c>
       <c r="C54" s="56" t="s">
+        <v>416</v>
+      </c>
+      <c r="D54" s="56" t="s">
         <v>417</v>
       </c>
-      <c r="D54" s="56" t="s">
+      <c r="E54" s="56" t="s">
         <v>418</v>
-      </c>
-      <c r="E54" s="56" t="s">
-        <v>419</v>
       </c>
       <c r="F54" s="60">
         <v>46477</v>
@@ -15335,13 +15305,13 @@
         <v>2007</v>
       </c>
       <c r="C55" s="56" t="s">
+        <v>419</v>
+      </c>
+      <c r="D55" s="56" t="s">
         <v>420</v>
       </c>
-      <c r="D55" s="56" t="s">
-        <v>421</v>
-      </c>
       <c r="E55" s="56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F55" s="60">
         <v>49217</v>
@@ -15392,7 +15362,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="62" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -15400,45 +15370,45 @@
     </row>
     <row r="3" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="71" t="s">
+        <v>422</v>
+      </c>
+      <c r="C3" s="72" t="s">
         <v>423</v>
       </c>
-      <c r="C3" s="72" t="s">
+      <c r="D3" s="71" t="s">
         <v>424</v>
       </c>
-      <c r="D3" s="71" t="s">
+      <c r="E3" s="72" t="s">
         <v>425</v>
       </c>
-      <c r="E3" s="72" t="s">
+      <c r="F3" s="71" t="s">
         <v>426</v>
-      </c>
-      <c r="F3" s="71" t="s">
-        <v>427</v>
       </c>
       <c r="G3" s="71" t="s">
         <v>1</v>
       </c>
       <c r="H3" s="71" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I3" s="71" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="J3" s="71" t="s">
         <v>4</v>
       </c>
       <c r="K3" s="74" t="s">
+        <v>428</v>
+      </c>
+      <c r="L3" s="74" t="s">
         <v>429</v>
       </c>
-      <c r="L3" s="74" t="s">
+      <c r="M3" s="72" t="s">
         <v>430</v>
-      </c>
-      <c r="M3" s="72" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B4" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C4" s="65">
         <v>2008</v>
@@ -15450,13 +15420,13 @@
         <v>41791</v>
       </c>
       <c r="F4" s="64" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G4" s="64" t="s">
         <v>209</v>
       </c>
       <c r="H4" s="64" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I4" s="64" t="s">
         <v>209</v>
@@ -15476,7 +15446,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B5" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C5" s="65">
         <v>1501</v>
@@ -15488,13 +15458,13 @@
         <v>44228</v>
       </c>
       <c r="F5" s="64" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G5" s="64" t="s">
         <v>56</v>
       </c>
       <c r="H5" s="64" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I5" s="64" t="s">
         <v>206</v>
@@ -15514,7 +15484,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C6" s="65">
         <v>1502</v>
@@ -15526,13 +15496,13 @@
         <v>44682</v>
       </c>
       <c r="F6" s="64" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G6" s="64" t="s">
         <v>114</v>
       </c>
       <c r="H6" s="64" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I6" s="64" t="s">
         <v>206</v>
@@ -15552,7 +15522,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B7" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C7" s="65">
         <v>1503</v>
@@ -15564,13 +15534,13 @@
         <v>45078</v>
       </c>
       <c r="F7" s="64" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G7" s="64" t="s">
         <v>117</v>
       </c>
       <c r="H7" s="64" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I7" s="64" t="s">
         <v>206</v>
@@ -15590,7 +15560,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B8" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C8" s="65">
         <v>1504</v>
@@ -15602,13 +15572,13 @@
         <v>45108</v>
       </c>
       <c r="F8" s="64" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G8" s="64" t="s">
         <v>85</v>
       </c>
       <c r="H8" s="64" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I8" s="64" t="s">
         <v>206</v>
@@ -15628,7 +15598,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B9" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C9" s="65">
         <v>1505</v>
@@ -15640,13 +15610,13 @@
         <v>45170</v>
       </c>
       <c r="F9" s="64" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G9" s="64" t="s">
         <v>175</v>
       </c>
       <c r="H9" s="64" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I9" s="64" t="s">
         <v>175</v>
@@ -15666,7 +15636,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B10" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C10" s="65">
         <v>1506</v>
@@ -15678,16 +15648,16 @@
         <v>45566</v>
       </c>
       <c r="F10" s="64" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G10" s="64" t="s">
         <v>134</v>
       </c>
       <c r="H10" s="64" t="s">
+        <v>439</v>
+      </c>
+      <c r="I10" s="64" t="s">
         <v>440</v>
-      </c>
-      <c r="I10" s="64" t="s">
-        <v>441</v>
       </c>
       <c r="J10" s="64" t="s">
         <v>57</v>
@@ -15704,7 +15674,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B11" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C11" s="65">
         <v>2009</v>
@@ -15716,13 +15686,13 @@
         <v>41183</v>
       </c>
       <c r="F11" s="64" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G11" s="64" t="s">
         <v>212</v>
       </c>
       <c r="H11" s="64" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I11" s="64" t="s">
         <v>212</v>
@@ -15742,7 +15712,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B12" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C12" s="59">
         <v>5001</v>
@@ -15754,16 +15724,16 @@
         <v>43327</v>
       </c>
       <c r="F12" s="55" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G12" s="55" t="s">
         <v>126</v>
       </c>
       <c r="H12" s="55" t="s">
+        <v>443</v>
+      </c>
+      <c r="I12" s="55" t="s">
         <v>444</v>
-      </c>
-      <c r="I12" s="55" t="s">
-        <v>445</v>
       </c>
       <c r="J12" s="55" t="s">
         <v>127</v>
@@ -15780,7 +15750,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B13" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C13" s="59">
         <v>6004</v>
@@ -15792,13 +15762,13 @@
         <v>43889</v>
       </c>
       <c r="F13" s="55" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G13" s="55" t="s">
         <v>120</v>
       </c>
       <c r="H13" s="55" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I13" s="55" t="s">
         <v>120</v>
@@ -15818,7 +15788,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B14" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C14" s="59">
         <v>8006</v>
@@ -15830,13 +15800,13 @@
         <v>42095</v>
       </c>
       <c r="F14" s="55" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G14" s="55" t="s">
         <v>137</v>
       </c>
       <c r="H14" s="55" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I14" s="55" t="s">
         <v>137</v>
@@ -15856,7 +15826,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B15" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C15" s="59">
         <v>7008</v>
@@ -15868,13 +15838,13 @@
         <v>42278</v>
       </c>
       <c r="F15" s="55" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G15" s="55" t="s">
         <v>50</v>
       </c>
       <c r="H15" s="55" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I15" s="55" t="s">
         <v>50</v>
@@ -15894,7 +15864,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B16" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C16" s="65">
         <v>2010</v>
@@ -15906,13 +15876,13 @@
         <v>41640</v>
       </c>
       <c r="F16" s="64" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G16" s="64" t="s">
         <v>75</v>
       </c>
       <c r="H16" s="64" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I16" s="64" t="s">
         <v>75</v>
@@ -15932,7 +15902,7 @@
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B17" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C17" s="65">
         <v>2011</v>
@@ -15944,13 +15914,13 @@
         <v>42795</v>
       </c>
       <c r="F17" s="64" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G17" s="64" t="s">
         <v>225</v>
       </c>
       <c r="H17" s="64" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I17" s="64" t="s">
         <v>225</v>
@@ -15970,7 +15940,7 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B18" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C18" s="59">
         <v>3500</v>
@@ -15982,16 +15952,16 @@
         <v>43617</v>
       </c>
       <c r="F18" s="55" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G18" s="55" t="s">
         <v>188</v>
       </c>
       <c r="H18" s="55" t="s">
+        <v>454</v>
+      </c>
+      <c r="I18" s="55" t="s">
         <v>455</v>
-      </c>
-      <c r="I18" s="55" t="s">
-        <v>456</v>
       </c>
       <c r="J18" s="55" t="s">
         <v>189</v>
@@ -16008,7 +15978,7 @@
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B19" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C19" s="59">
         <v>8007</v>
@@ -16020,16 +15990,16 @@
         <v>43259</v>
       </c>
       <c r="F19" s="55" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G19" s="55" t="s">
+        <v>456</v>
+      </c>
+      <c r="H19" s="55" t="s">
         <v>457</v>
       </c>
-      <c r="H19" s="55" t="s">
+      <c r="I19" s="55" t="s">
         <v>458</v>
-      </c>
-      <c r="I19" s="55" t="s">
-        <v>459</v>
       </c>
       <c r="J19" s="55" t="s">
         <v>43</v>
@@ -16046,7 +16016,7 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B20" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C20" s="59">
         <v>8008</v>
@@ -16058,16 +16028,16 @@
         <v>44641</v>
       </c>
       <c r="F20" s="55" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G20" s="55" t="s">
+        <v>459</v>
+      </c>
+      <c r="H20" s="55" t="s">
         <v>460</v>
       </c>
-      <c r="H20" s="55" t="s">
-        <v>461</v>
-      </c>
       <c r="I20" s="55" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J20" s="55" t="s">
         <v>43</v>
@@ -16084,7 +16054,7 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B21" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C21" s="59">
         <v>7009</v>
@@ -16096,13 +16066,13 @@
         <v>43344</v>
       </c>
       <c r="F21" s="55" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G21" s="55" t="s">
         <v>185</v>
       </c>
       <c r="H21" s="55" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I21" s="55" t="s">
         <v>185</v>
@@ -16122,7 +16092,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B22" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C22" s="59">
         <v>6501</v>
@@ -16134,13 +16104,13 @@
         <v>42856</v>
       </c>
       <c r="F22" s="55" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G22" s="55" t="s">
         <v>97</v>
       </c>
       <c r="H22" s="55" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I22" s="55" t="s">
         <v>97</v>
@@ -16160,7 +16130,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B23" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C23" s="65">
         <v>1510</v>
@@ -16172,13 +16142,13 @@
         <v>41282</v>
       </c>
       <c r="F23" s="64" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G23" s="64" t="s">
+        <v>464</v>
+      </c>
+      <c r="H23" s="64" t="s">
         <v>465</v>
-      </c>
-      <c r="H23" s="64" t="s">
-        <v>466</v>
       </c>
       <c r="I23" s="64" t="s">
         <v>146</v>
@@ -16198,7 +16168,7 @@
     </row>
     <row r="24" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C24" s="59">
         <v>2012</v>
@@ -16210,13 +16180,13 @@
         <v>42094</v>
       </c>
       <c r="F24" s="55" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G24" s="55" t="s">
         <v>234</v>
       </c>
       <c r="H24" s="55" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="I24" s="55" t="s">
         <v>234</v>
@@ -16236,7 +16206,7 @@
     </row>
     <row r="25" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C25" s="59">
         <v>6502</v>
@@ -16248,13 +16218,13 @@
         <v>42795</v>
       </c>
       <c r="F25" s="55" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G25" s="55" t="s">
         <v>143</v>
       </c>
       <c r="H25" s="55" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="I25" s="55" t="s">
         <v>143</v>
@@ -16274,7 +16244,7 @@
     </row>
     <row r="26" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C26" s="65">
         <v>1001</v>
@@ -16286,13 +16256,13 @@
         <v>43916</v>
       </c>
       <c r="F26" s="64" t="s">
+        <v>468</v>
+      </c>
+      <c r="G26" s="64" t="s">
         <v>469</v>
       </c>
-      <c r="G26" s="64" t="s">
+      <c r="H26" s="64" t="s">
         <v>470</v>
-      </c>
-      <c r="H26" s="64" t="s">
-        <v>471</v>
       </c>
       <c r="I26" s="64" t="s">
         <v>91</v>
@@ -16312,7 +16282,7 @@
     </row>
     <row r="27" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C27" s="65">
         <v>1002</v>
@@ -16324,13 +16294,13 @@
         <v>43815</v>
       </c>
       <c r="F27" s="64" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G27" s="64" t="s">
         <v>137</v>
       </c>
       <c r="H27" s="64" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I27" s="64" t="s">
         <v>149</v>
@@ -16350,7 +16320,7 @@
     </row>
     <row r="28" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C28" s="65">
         <v>2002</v>
@@ -16362,13 +16332,13 @@
         <v>44239</v>
       </c>
       <c r="F28" s="64" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G28" s="64" t="s">
         <v>88</v>
       </c>
       <c r="H28" s="64" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I28" s="64" t="s">
         <v>88</v>
@@ -16388,7 +16358,7 @@
     </row>
     <row r="29" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B29" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C29" s="65">
         <v>2003</v>
@@ -16400,13 +16370,13 @@
         <v>44841</v>
       </c>
       <c r="F29" s="64" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G29" s="64" t="s">
         <v>172</v>
       </c>
       <c r="H29" s="64" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I29" s="64" t="s">
         <v>69</v>
@@ -16426,7 +16396,7 @@
     </row>
     <row r="30" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B30" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C30" s="65">
         <v>2004</v>
@@ -16438,16 +16408,16 @@
         <v>45226</v>
       </c>
       <c r="F30" s="64" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G30" s="64" t="s">
+        <v>475</v>
+      </c>
+      <c r="H30" s="64" t="s">
         <v>476</v>
       </c>
-      <c r="H30" s="64" t="s">
+      <c r="I30" s="64" t="s">
         <v>477</v>
-      </c>
-      <c r="I30" s="64" t="s">
-        <v>478</v>
       </c>
       <c r="J30" s="64" t="s">
         <v>64</v>
@@ -16464,7 +16434,7 @@
     </row>
     <row r="31" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B31" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C31" s="65">
         <v>2005</v>
@@ -16476,16 +16446,16 @@
         <v>45392</v>
       </c>
       <c r="F31" s="64" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G31" s="64" t="s">
         <v>63</v>
       </c>
       <c r="H31" s="64" t="s">
+        <v>478</v>
+      </c>
+      <c r="I31" s="64" t="s">
         <v>479</v>
-      </c>
-      <c r="I31" s="64" t="s">
-        <v>480</v>
       </c>
       <c r="J31" s="64" t="s">
         <v>64</v>
@@ -16502,7 +16472,7 @@
     </row>
     <row r="32" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B32" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C32" s="65">
         <v>2006</v>
@@ -16514,13 +16484,13 @@
         <v>41699</v>
       </c>
       <c r="F32" s="64" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G32" s="64" t="s">
         <v>155</v>
       </c>
       <c r="H32" s="64" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I32" s="64" t="s">
         <v>155</v>
@@ -16540,7 +16510,7 @@
     </row>
     <row r="33" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B33" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C33" s="59">
         <v>7001</v>
@@ -16552,16 +16522,16 @@
         <v>41852</v>
       </c>
       <c r="F33" s="55" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G33" s="55" t="s">
         <v>222</v>
       </c>
       <c r="H33" s="55" t="s">
+        <v>481</v>
+      </c>
+      <c r="I33" s="55" t="s">
         <v>482</v>
-      </c>
-      <c r="I33" s="55" t="s">
-        <v>483</v>
       </c>
       <c r="J33" s="55" t="s">
         <v>51</v>
@@ -16578,7 +16548,7 @@
     </row>
     <row r="34" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B34" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C34" s="59">
         <v>7002</v>
@@ -16590,13 +16560,13 @@
         <v>41913</v>
       </c>
       <c r="F34" s="55" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G34" s="55" t="s">
         <v>72</v>
       </c>
       <c r="H34" s="55" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I34" s="55" t="s">
         <v>72</v>
@@ -16616,7 +16586,7 @@
     </row>
     <row r="35" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B35" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C35" s="59">
         <v>7003</v>
@@ -16628,13 +16598,13 @@
         <v>40940</v>
       </c>
       <c r="F35" s="55" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G35" s="55" t="s">
         <v>196</v>
       </c>
       <c r="H35" s="55" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I35" s="55" t="s">
         <v>196</v>
@@ -16654,7 +16624,7 @@
     </row>
     <row r="36" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B36" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C36" s="59">
         <v>7004</v>
@@ -16666,13 +16636,13 @@
         <v>42036</v>
       </c>
       <c r="F36" s="55" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G36" s="55" t="s">
         <v>163</v>
       </c>
       <c r="H36" s="55" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I36" s="55" t="s">
         <v>163</v>
@@ -16692,7 +16662,7 @@
     </row>
     <row r="37" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B37" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C37" s="59">
         <v>7006</v>
@@ -16704,16 +16674,16 @@
         <v>42644</v>
       </c>
       <c r="F37" s="55" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G37" s="55" t="s">
         <v>182</v>
       </c>
       <c r="H37" s="55" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I37" s="55" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J37" s="55" t="s">
         <v>51</v>
@@ -16730,7 +16700,7 @@
     </row>
     <row r="38" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B38" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C38" s="59">
         <v>6003</v>
@@ -16742,13 +16712,13 @@
         <v>42491</v>
       </c>
       <c r="F38" s="55" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G38" s="55" t="s">
         <v>108</v>
       </c>
       <c r="H38" s="55" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I38" s="55" t="s">
         <v>108</v>
@@ -16768,7 +16738,7 @@
     </row>
     <row r="39" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B39" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C39" s="59">
         <v>9001</v>
@@ -16780,13 +16750,13 @@
         <v>42767</v>
       </c>
       <c r="F39" s="55" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G39" s="55" t="s">
         <v>193</v>
       </c>
       <c r="H39" s="55" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I39" s="55" t="s">
         <v>193</v>
@@ -16806,7 +16776,7 @@
     </row>
     <row r="40" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B40" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C40" s="59">
         <v>9002</v>
@@ -16818,13 +16788,13 @@
         <v>42979</v>
       </c>
       <c r="F40" s="55" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G40" s="55" t="s">
         <v>104</v>
       </c>
       <c r="H40" s="55" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I40" s="55" t="s">
         <v>104</v>
@@ -16844,7 +16814,7 @@
     </row>
     <row r="41" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B41" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C41" s="59">
         <v>9003</v>
@@ -16856,13 +16826,13 @@
         <v>43009</v>
       </c>
       <c r="F41" s="55" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G41" s="55" t="s">
         <v>140</v>
       </c>
       <c r="H41" s="55" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="I41" s="55" t="s">
         <v>140</v>
@@ -16882,7 +16852,7 @@
     </row>
     <row r="42" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B42" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C42" s="59">
         <v>9004</v>
@@ -16894,13 +16864,13 @@
         <v>43009</v>
       </c>
       <c r="F42" s="55" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G42" s="55" t="s">
         <v>79</v>
       </c>
       <c r="H42" s="55" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I42" s="55" t="s">
         <v>79</v>
@@ -16920,7 +16890,7 @@
     </row>
     <row r="43" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B43" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C43" s="59">
         <v>7005</v>
@@ -16932,13 +16902,13 @@
         <v>43040</v>
       </c>
       <c r="F43" s="55" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G43" s="55" t="s">
+        <v>493</v>
+      </c>
+      <c r="H43" s="55" t="s">
         <v>494</v>
-      </c>
-      <c r="H43" s="55" t="s">
-        <v>495</v>
       </c>
       <c r="I43" s="55" t="s">
         <v>159</v>
@@ -16958,7 +16928,7 @@
     </row>
     <row r="44" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B44" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C44" s="59">
         <v>8001</v>
@@ -16970,13 +16940,13 @@
         <v>42248</v>
       </c>
       <c r="F44" s="55" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G44" s="55" t="s">
         <v>216</v>
       </c>
       <c r="H44" s="55" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I44" s="55" t="s">
         <v>216</v>
@@ -16996,7 +16966,7 @@
     </row>
     <row r="45" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B45" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C45" s="59">
         <v>8002</v>
@@ -17008,16 +16978,16 @@
         <v>43122</v>
       </c>
       <c r="F45" s="55" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G45" s="55" t="s">
+        <v>496</v>
+      </c>
+      <c r="H45" s="55" t="s">
         <v>497</v>
       </c>
-      <c r="H45" s="55" t="s">
+      <c r="I45" s="55" t="s">
         <v>498</v>
-      </c>
-      <c r="I45" s="55" t="s">
-        <v>499</v>
       </c>
       <c r="J45" s="55" t="s">
         <v>43</v>
@@ -17034,7 +17004,7 @@
     </row>
     <row r="46" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B46" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C46" s="59">
         <v>8003</v>
@@ -17046,13 +17016,13 @@
         <v>42309</v>
       </c>
       <c r="F46" s="55" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G46" s="55" t="s">
         <v>169</v>
       </c>
       <c r="H46" s="55" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I46" s="55" t="s">
         <v>169</v>
@@ -17072,7 +17042,7 @@
     </row>
     <row r="47" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B47" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C47" s="59">
         <v>8004</v>
@@ -17084,16 +17054,16 @@
         <v>44519</v>
       </c>
       <c r="F47" s="55" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G47" s="55" t="s">
+        <v>500</v>
+      </c>
+      <c r="H47" s="55" t="s">
         <v>501</v>
       </c>
-      <c r="H47" s="55" t="s">
-        <v>502</v>
-      </c>
       <c r="I47" s="55" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="J47" s="55" t="s">
         <v>43</v>
@@ -17110,7 +17080,7 @@
     </row>
     <row r="48" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B48" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C48" s="59">
         <v>8005</v>
@@ -17122,13 +17092,13 @@
         <v>45145</v>
       </c>
       <c r="F48" s="55" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G48" s="55" t="s">
         <v>219</v>
       </c>
       <c r="H48" s="55" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="I48" s="55" t="s">
         <v>219</v>
@@ -17148,7 +17118,7 @@
     </row>
     <row r="49" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B49" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C49" s="59">
         <v>4000</v>
@@ -17160,13 +17130,13 @@
         <v>42675</v>
       </c>
       <c r="F49" s="55" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G49" s="55" t="s">
         <v>130</v>
       </c>
       <c r="H49" s="55" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="I49" s="55" t="s">
         <v>130</v>
@@ -17186,7 +17156,7 @@
     </row>
     <row r="50" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B50" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C50" s="59">
         <v>5000</v>
@@ -17198,16 +17168,16 @@
         <v>42884</v>
       </c>
       <c r="F50" s="55" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G50" s="55" t="s">
         <v>166</v>
       </c>
       <c r="H50" s="55" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="I50" s="55" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="J50" s="55" t="s">
         <v>127</v>
@@ -17224,7 +17194,7 @@
     </row>
     <row r="51" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B51" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C51" s="59">
         <v>6001</v>
@@ -17236,13 +17206,13 @@
         <v>42095</v>
       </c>
       <c r="F51" s="55" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G51" s="55" t="s">
         <v>202</v>
       </c>
       <c r="H51" s="55" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="I51" s="55" t="s">
         <v>202</v>
@@ -17262,7 +17232,7 @@
     </row>
     <row r="52" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B52" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C52" s="59">
         <v>6002</v>
@@ -17274,13 +17244,13 @@
         <v>42401</v>
       </c>
       <c r="F52" s="55" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G52" s="55" t="s">
         <v>123</v>
       </c>
       <c r="H52" s="55" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="I52" s="55" t="s">
         <v>123</v>
@@ -17300,7 +17270,7 @@
     </row>
     <row r="53" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B53" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C53" s="65">
         <v>1003</v>
@@ -17312,13 +17282,13 @@
         <v>41153</v>
       </c>
       <c r="F53" s="64" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G53" s="64" t="s">
+        <v>508</v>
+      </c>
+      <c r="H53" s="64" t="s">
         <v>509</v>
-      </c>
-      <c r="H53" s="64" t="s">
-        <v>510</v>
       </c>
       <c r="I53" s="64" t="s">
         <v>206</v>
@@ -17338,7 +17308,7 @@
     </row>
     <row r="54" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B54" s="55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C54" s="59">
         <v>7007</v>
@@ -17350,13 +17320,13 @@
         <v>42868</v>
       </c>
       <c r="F54" s="55" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G54" s="55" t="s">
+        <v>510</v>
+      </c>
+      <c r="H54" s="55" t="s">
         <v>511</v>
-      </c>
-      <c r="H54" s="55" t="s">
-        <v>512</v>
       </c>
       <c r="I54" s="55" t="s">
         <v>159</v>
@@ -17376,7 +17346,7 @@
     </row>
     <row r="55" spans="2:13" s="55" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B55" s="64" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C55" s="65">
         <v>2007</v>
@@ -17388,13 +17358,13 @@
         <v>41518</v>
       </c>
       <c r="F55" s="64" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G55" s="64" t="s">
         <v>237</v>
       </c>
       <c r="H55" s="64" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="I55" s="64" t="s">
         <v>76</v>
@@ -17493,7 +17463,7 @@
   <sheetData>
     <row r="1" spans="1:70" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="62" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="2" spans="1:70" x14ac:dyDescent="0.2">
@@ -17501,58 +17471,58 @@
     </row>
     <row r="3" spans="1:70" x14ac:dyDescent="0.2">
       <c r="H3" s="127" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I3" s="131" t="s">
         <v>152</v>
       </c>
       <c r="O3" s="127" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P3" s="131" t="s">
         <v>120</v>
       </c>
       <c r="V3" s="127" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W3" s="131" t="s">
         <v>50</v>
       </c>
       <c r="AC3" s="127" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AD3" s="131" t="s">
         <v>225</v>
       </c>
       <c r="AJ3" s="129" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AK3" s="128" t="s">
         <v>225</v>
       </c>
       <c r="AQ3" s="127" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AR3" s="131" t="s">
         <v>75</v>
       </c>
       <c r="AX3" s="127" t="s">
+        <v>514</v>
+      </c>
+      <c r="AY3" s="131" t="s">
         <v>515</v>
       </c>
-      <c r="AY3" s="131" t="s">
+      <c r="BE3" s="127" t="s">
+        <v>514</v>
+      </c>
+      <c r="BF3" s="131" t="s">
+        <v>515</v>
+      </c>
+      <c r="BL3" s="127" t="s">
+        <v>514</v>
+      </c>
+      <c r="BM3" s="131" t="s">
         <v>516</v>
-      </c>
-      <c r="BE3" s="127" t="s">
-        <v>515</v>
-      </c>
-      <c r="BF3" s="131" t="s">
-        <v>516</v>
-      </c>
-      <c r="BL3" s="127" t="s">
-        <v>515</v>
-      </c>
-      <c r="BM3" s="131" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="4" spans="1:70" x14ac:dyDescent="0.2">
@@ -17560,116 +17530,116 @@
         <v>7</v>
       </c>
       <c r="I4" s="131" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="O4" s="127" t="s">
         <v>7</v>
       </c>
       <c r="P4" s="131" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="V4" s="127" t="s">
         <v>7</v>
       </c>
       <c r="W4" s="131" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AC4" s="127" t="s">
         <v>7</v>
       </c>
       <c r="AD4" s="131" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AJ4" s="129" t="s">
         <v>7</v>
       </c>
       <c r="AK4" s="128" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AQ4" s="127" t="s">
         <v>7</v>
       </c>
       <c r="AR4" s="131" t="s">
+        <v>518</v>
+      </c>
+      <c r="AS4" s="77" t="s">
         <v>519</v>
-      </c>
-      <c r="AS4" s="77" t="s">
-        <v>520</v>
       </c>
       <c r="AX4" s="127" t="s">
         <v>7</v>
       </c>
       <c r="AY4" s="131" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AZ4" s="77"/>
       <c r="BE4" s="127" t="s">
         <v>7</v>
       </c>
       <c r="BF4" s="131" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="BG4" s="77" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="BL4" s="127" t="s">
         <v>7</v>
       </c>
       <c r="BM4" s="131" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="BN4" s="77"/>
     </row>
     <row r="5" spans="1:70" x14ac:dyDescent="0.2">
       <c r="H5" s="127" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="I5" s="131">
         <v>7007</v>
       </c>
       <c r="O5" s="127" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P5" s="131">
         <v>6004</v>
       </c>
       <c r="V5" s="127" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="W5" s="131">
         <v>7008</v>
       </c>
       <c r="AC5" s="127" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AD5" s="131">
         <v>2011</v>
       </c>
       <c r="AJ5" s="129" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AK5" s="128">
         <v>2011</v>
       </c>
       <c r="AQ5" s="127" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AR5" s="131">
         <v>2010</v>
       </c>
       <c r="AX5" s="127" t="s">
+        <v>521</v>
+      </c>
+      <c r="AY5" s="131" t="s">
         <v>522</v>
       </c>
-      <c r="AY5" s="131" t="s">
-        <v>523</v>
-      </c>
       <c r="BE5" s="127" t="s">
+        <v>521</v>
+      </c>
+      <c r="BF5" s="131" t="s">
         <v>522</v>
       </c>
-      <c r="BF5" s="131" t="s">
-        <v>523</v>
-      </c>
       <c r="BL5" s="127" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="BM5" s="131">
         <v>7009</v>
@@ -17677,55 +17647,55 @@
     </row>
     <row r="6" spans="1:70" x14ac:dyDescent="0.2">
       <c r="H6" s="127" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I6" s="140">
         <v>0.06</v>
       </c>
       <c r="O6" s="127" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P6" s="140">
         <v>0.06</v>
       </c>
       <c r="V6" s="127" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="W6" s="140">
         <v>0.06</v>
       </c>
       <c r="AC6" s="127" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AD6" s="140">
         <v>0.05</v>
       </c>
       <c r="AJ6" s="129" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AK6" s="142">
         <v>0.05</v>
       </c>
       <c r="AQ6" s="127" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AR6" s="140">
         <v>0.06</v>
       </c>
       <c r="AX6" s="127" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AY6" s="141">
         <v>6.5068590400172863E-2</v>
       </c>
       <c r="BE6" s="127" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="BF6" s="140">
         <v>0</v>
       </c>
       <c r="BL6" s="127" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="BM6" s="140">
         <v>7.4999999999999997E-2</v>
@@ -17733,55 +17703,55 @@
     </row>
     <row r="7" spans="1:70" x14ac:dyDescent="0.2">
       <c r="H7" s="127" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I7" s="139">
         <v>176700</v>
       </c>
       <c r="O7" s="127" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P7" s="139">
         <v>125000</v>
       </c>
       <c r="V7" s="127" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="W7" s="139">
         <v>214500</v>
       </c>
       <c r="AC7" s="127" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AD7" s="139">
         <v>1175000</v>
       </c>
       <c r="AJ7" s="129" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AK7" s="138">
         <v>1175000</v>
       </c>
       <c r="AQ7" s="127" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AR7" s="136">
         <v>267285.5</v>
       </c>
       <c r="AX7" s="127" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AY7" s="136">
         <v>280707.05</v>
       </c>
       <c r="BE7" s="127" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="BF7" s="136">
         <v>128523.18</v>
       </c>
       <c r="BL7" s="127" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="BM7" s="136">
         <v>425000</v>
@@ -17789,63 +17759,63 @@
     </row>
     <row r="8" spans="1:70" x14ac:dyDescent="0.2">
       <c r="H8" s="127" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="I8" s="136">
         <f>PMT(I6/12,I9,-I7)</f>
         <v>2928.429290776538</v>
       </c>
       <c r="O8" s="127" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="P8" s="136">
         <f>PMT(P6/12,P9,-P7)</f>
         <v>10758.303713385081</v>
       </c>
       <c r="V8" s="127" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="W8" s="136">
         <f>PMT(W6/12,W9,-W7)</f>
         <v>2575.2332958335392</v>
       </c>
       <c r="AC8" s="127" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AD8" s="136">
         <f>PMT(AD6/12,AD9,-AD7)</f>
         <v>27059.419945509657</v>
       </c>
       <c r="AJ8" s="129" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AK8" s="137">
         <f>PMT(AK6/12,AK9,-AK7)/2</f>
         <v>13529.709972754828</v>
       </c>
       <c r="AQ8" s="127" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AR8" s="136">
         <f>PMT(AR6/12,AR9,-AR7)</f>
         <v>6782.4787835382895</v>
       </c>
       <c r="AX8" s="127" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AY8" s="136">
         <f>PMT(AY6/12,AY9,-AY7)</f>
         <v>7654.2093662030939</v>
       </c>
       <c r="BE8" s="127" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="BF8" s="136">
         <f>+BF7/3</f>
         <v>42841.06</v>
       </c>
       <c r="BL8" s="127" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="BM8" s="135">
         <f>PMT(BM6/12,BM9,-BM7)</f>
@@ -17854,55 +17824,55 @@
     </row>
     <row r="9" spans="1:70" x14ac:dyDescent="0.2">
       <c r="H9" s="127" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I9" s="131">
         <v>72</v>
       </c>
       <c r="O9" s="127" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="P9" s="131">
         <v>12</v>
       </c>
       <c r="V9" s="127" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="W9" s="131">
         <v>108</v>
       </c>
       <c r="AC9" s="127" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AD9" s="131">
         <v>48</v>
       </c>
       <c r="AJ9" s="129" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AK9" s="128">
         <v>48</v>
       </c>
       <c r="AQ9" s="127" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AR9" s="131">
         <v>44</v>
       </c>
       <c r="AX9" s="127" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AY9" s="131">
         <v>41</v>
       </c>
       <c r="BE9" s="127" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="BF9" s="131">
         <v>3</v>
       </c>
       <c r="BL9" s="127" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="BM9" s="131">
         <v>60</v>
@@ -17910,55 +17880,55 @@
     </row>
     <row r="10" spans="1:70" x14ac:dyDescent="0.2">
       <c r="H10" s="127" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I10" s="133">
         <v>45458</v>
       </c>
       <c r="O10" s="127" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="P10" s="133">
         <v>45717</v>
       </c>
       <c r="V10" s="127" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="W10" s="133">
         <v>45778</v>
       </c>
       <c r="AC10" s="127" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AD10" s="133">
         <v>45870</v>
       </c>
       <c r="AJ10" s="129" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AK10" s="134">
         <v>45870</v>
       </c>
       <c r="AQ10" s="127" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AR10" s="133">
         <v>45802</v>
       </c>
       <c r="AX10" s="127" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AY10" s="133">
         <v>45992</v>
       </c>
       <c r="BE10" s="127" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="BF10" s="133">
         <v>46006</v>
       </c>
       <c r="BL10" s="127" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="BM10" s="133">
         <v>46006</v>
@@ -17967,7 +17937,7 @@
     <row r="11" spans="1:70" x14ac:dyDescent="0.2">
       <c r="F11" s="132"/>
       <c r="H11" s="127" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="N11" s="130">
         <f>+I7</f>
@@ -17996,28 +17966,28 @@
         <v>1175000</v>
       </c>
       <c r="AQ11" s="127" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AW11" s="77">
         <f>+AR7</f>
         <v>267285.5</v>
       </c>
       <c r="AX11" s="127" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="BD11" s="77">
         <f>+AY7</f>
         <v>280707.05</v>
       </c>
       <c r="BE11" s="127" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="BK11" s="77">
         <f>+BF7</f>
         <v>128523.18</v>
       </c>
       <c r="BL11" s="127" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="BR11" s="77">
         <f>+BM7</f>
@@ -18026,188 +17996,188 @@
     </row>
     <row r="12" spans="1:70" s="116" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="119" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C12" s="118" t="s">
+        <v>529</v>
+      </c>
+      <c r="D12" s="118" t="s">
         <v>530</v>
       </c>
-      <c r="D12" s="118" t="s">
+      <c r="E12" s="118" t="s">
+        <v>525</v>
+      </c>
+      <c r="F12" s="118" t="s">
         <v>531</v>
-      </c>
-      <c r="E12" s="118" t="s">
-        <v>526</v>
-      </c>
-      <c r="F12" s="118" t="s">
-        <v>532</v>
       </c>
       <c r="H12" s="121"/>
       <c r="I12" s="120" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="J12" s="119" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="K12" s="118" t="s">
+        <v>529</v>
+      </c>
+      <c r="L12" s="118" t="s">
         <v>530</v>
       </c>
-      <c r="L12" s="118" t="s">
+      <c r="M12" s="118" t="s">
+        <v>525</v>
+      </c>
+      <c r="N12" s="118" t="s">
         <v>531</v>
       </c>
-      <c r="M12" s="118" t="s">
-        <v>526</v>
-      </c>
-      <c r="N12" s="118" t="s">
+      <c r="P12" s="120" t="s">
         <v>532</v>
       </c>
-      <c r="P12" s="120" t="s">
-        <v>533</v>
-      </c>
       <c r="Q12" s="119" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="R12" s="118" t="s">
+        <v>529</v>
+      </c>
+      <c r="S12" s="118" t="s">
         <v>530</v>
       </c>
-      <c r="S12" s="118" t="s">
+      <c r="T12" s="118" t="s">
+        <v>525</v>
+      </c>
+      <c r="U12" s="118" t="s">
         <v>531</v>
       </c>
-      <c r="T12" s="118" t="s">
-        <v>526</v>
-      </c>
-      <c r="U12" s="118" t="s">
+      <c r="W12" s="120" t="s">
         <v>532</v>
       </c>
-      <c r="W12" s="120" t="s">
-        <v>533</v>
-      </c>
       <c r="X12" s="119" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y12" s="118" t="s">
+        <v>529</v>
+      </c>
+      <c r="Z12" s="118" t="s">
         <v>530</v>
       </c>
-      <c r="Z12" s="118" t="s">
+      <c r="AA12" s="118" t="s">
+        <v>525</v>
+      </c>
+      <c r="AB12" s="118" t="s">
         <v>531</v>
-      </c>
-      <c r="AA12" s="118" t="s">
-        <v>526</v>
-      </c>
-      <c r="AB12" s="118" t="s">
-        <v>532</v>
       </c>
       <c r="AC12" s="121"/>
       <c r="AD12" s="120" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AE12" s="119" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AF12" s="118" t="s">
+        <v>529</v>
+      </c>
+      <c r="AG12" s="118" t="s">
         <v>530</v>
       </c>
-      <c r="AG12" s="118" t="s">
+      <c r="AH12" s="118" t="s">
+        <v>525</v>
+      </c>
+      <c r="AI12" s="118" t="s">
         <v>531</v>
-      </c>
-      <c r="AH12" s="118" t="s">
-        <v>526</v>
-      </c>
-      <c r="AI12" s="118" t="s">
-        <v>532</v>
       </c>
       <c r="AJ12" s="126"/>
       <c r="AK12" s="125" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AL12" s="124" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AM12" s="123" t="s">
+        <v>529</v>
+      </c>
+      <c r="AN12" s="123" t="s">
         <v>530</v>
       </c>
-      <c r="AN12" s="123" t="s">
+      <c r="AO12" s="123" t="s">
+        <v>525</v>
+      </c>
+      <c r="AP12" s="122" t="s">
         <v>531</v>
-      </c>
-      <c r="AO12" s="123" t="s">
-        <v>526</v>
-      </c>
-      <c r="AP12" s="122" t="s">
-        <v>532</v>
       </c>
       <c r="AQ12" s="121"/>
       <c r="AR12" s="120" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AS12" s="119" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AT12" s="118" t="s">
+        <v>529</v>
+      </c>
+      <c r="AU12" s="118" t="s">
         <v>530</v>
       </c>
-      <c r="AU12" s="118" t="s">
+      <c r="AV12" s="118" t="s">
+        <v>525</v>
+      </c>
+      <c r="AW12" s="117" t="s">
         <v>531</v>
-      </c>
-      <c r="AV12" s="118" t="s">
-        <v>526</v>
-      </c>
-      <c r="AW12" s="117" t="s">
-        <v>532</v>
       </c>
       <c r="AX12" s="121"/>
       <c r="AY12" s="120" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AZ12" s="119" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="BA12" s="118" t="s">
+        <v>529</v>
+      </c>
+      <c r="BB12" s="118" t="s">
         <v>530</v>
       </c>
-      <c r="BB12" s="118" t="s">
+      <c r="BC12" s="118" t="s">
+        <v>525</v>
+      </c>
+      <c r="BD12" s="117" t="s">
         <v>531</v>
-      </c>
-      <c r="BC12" s="118" t="s">
-        <v>526</v>
-      </c>
-      <c r="BD12" s="117" t="s">
-        <v>532</v>
       </c>
       <c r="BE12" s="121"/>
       <c r="BF12" s="120" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="BG12" s="119" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="BH12" s="118" t="s">
+        <v>529</v>
+      </c>
+      <c r="BI12" s="118" t="s">
         <v>530</v>
       </c>
-      <c r="BI12" s="118" t="s">
+      <c r="BJ12" s="118" t="s">
+        <v>525</v>
+      </c>
+      <c r="BK12" s="117" t="s">
         <v>531</v>
-      </c>
-      <c r="BJ12" s="118" t="s">
-        <v>526</v>
-      </c>
-      <c r="BK12" s="117" t="s">
-        <v>532</v>
       </c>
       <c r="BL12" s="121"/>
       <c r="BM12" s="120" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="BN12" s="119" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="BO12" s="118" t="s">
+        <v>529</v>
+      </c>
+      <c r="BP12" s="118" t="s">
         <v>530</v>
       </c>
-      <c r="BP12" s="118" t="s">
+      <c r="BQ12" s="118" t="s">
+        <v>525</v>
+      </c>
+      <c r="BR12" s="117" t="s">
         <v>531</v>
-      </c>
-      <c r="BQ12" s="118" t="s">
-        <v>526</v>
-      </c>
-      <c r="BR12" s="117" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="13" spans="1:70" x14ac:dyDescent="0.2">
@@ -32099,22 +32069,22 @@
     </row>
     <row r="3" spans="2:21" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="176" t="s">
+        <v>533</v>
+      </c>
+      <c r="C3" s="176" t="s">
         <v>534</v>
-      </c>
-      <c r="C3" s="176" t="s">
-        <v>535</v>
       </c>
       <c r="D3" s="176" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="176" t="s">
+        <v>535</v>
+      </c>
+      <c r="F3" s="176" t="s">
         <v>536</v>
       </c>
-      <c r="F3" s="176" t="s">
+      <c r="G3" s="176" t="s">
         <v>537</v>
-      </c>
-      <c r="G3" s="176" t="s">
-        <v>538</v>
       </c>
       <c r="H3" s="176" t="s">
         <v>29</v>
@@ -32123,37 +32093,37 @@
         <v>8</v>
       </c>
       <c r="J3" s="176" t="s">
+        <v>538</v>
+      </c>
+      <c r="K3" s="176" t="s">
         <v>539</v>
       </c>
-      <c r="K3" s="176" t="s">
-        <v>540</v>
-      </c>
       <c r="L3" s="176" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M3" s="176" t="s">
         <v>4</v>
       </c>
       <c r="N3" s="176" t="s">
+        <v>540</v>
+      </c>
+      <c r="O3" s="176" t="s">
         <v>541</v>
       </c>
-      <c r="O3" s="176" t="s">
+      <c r="P3" s="176" t="s">
         <v>542</v>
       </c>
-      <c r="P3" s="176" t="s">
+      <c r="Q3" s="176" t="s">
         <v>543</v>
       </c>
-      <c r="Q3" s="176" t="s">
+      <c r="R3" s="176" t="s">
         <v>544</v>
       </c>
-      <c r="R3" s="176" t="s">
+      <c r="S3" s="176" t="s">
         <v>545</v>
       </c>
-      <c r="S3" s="176" t="s">
+      <c r="T3" s="176" t="s">
         <v>546</v>
-      </c>
-      <c r="T3" s="176" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
@@ -32185,10 +32155,10 @@
         <v>7.021917808219178</v>
       </c>
       <c r="K4" s="167" t="s">
+        <v>547</v>
+      </c>
+      <c r="L4" s="166" t="s">
         <v>548</v>
-      </c>
-      <c r="L4" s="166" t="s">
-        <v>549</v>
       </c>
       <c r="M4" s="166" t="s">
         <v>131</v>
@@ -32237,7 +32207,7 @@
         <v>7.021917808219178</v>
       </c>
       <c r="K5" s="167" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L5" s="166" t="s">
         <v>93</v>
@@ -32265,7 +32235,7 @@
         <v>196</v>
       </c>
       <c r="C6" s="169" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D6" s="169" t="s">
         <v>45</v>
@@ -32289,10 +32259,10 @@
         <v>2.9369863013698629</v>
       </c>
       <c r="K6" s="167" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L6" s="166" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M6" s="166" t="s">
         <v>51</v>
@@ -32321,7 +32291,7 @@
         <v>222</v>
       </c>
       <c r="C7" s="169" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D7" s="169" t="s">
         <v>45</v>
@@ -32345,10 +32315,10 @@
         <v>2.9369863013698629</v>
       </c>
       <c r="K7" s="167" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L7" s="166" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M7" s="166" t="s">
         <v>51</v>
@@ -32371,7 +32341,7 @@
         <v>72</v>
       </c>
       <c r="C8" s="169" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D8" s="169" t="s">
         <v>45</v>
@@ -32395,10 +32365,10 @@
         <v>2.9369863013698629</v>
       </c>
       <c r="K8" s="167" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L8" s="166" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M8" s="166" t="s">
         <v>51</v>
@@ -32421,7 +32391,7 @@
         <v>163</v>
       </c>
       <c r="C9" s="169" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D9" s="169" t="s">
         <v>45</v>
@@ -32445,10 +32415,10 @@
         <v>2.9369863013698629</v>
       </c>
       <c r="K9" s="167" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L9" s="166" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M9" s="166" t="s">
         <v>51</v>
@@ -32471,7 +32441,7 @@
         <v>182</v>
       </c>
       <c r="C10" s="169" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D10" s="169" t="s">
         <v>45</v>
@@ -32495,10 +32465,10 @@
         <v>2.9369863013698629</v>
       </c>
       <c r="K10" s="167" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L10" s="166" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M10" s="166" t="s">
         <v>51</v>
@@ -32531,7 +32501,7 @@
         <v>159</v>
       </c>
       <c r="C11" s="169" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D11" s="169" t="s">
         <v>45</v>
@@ -32555,10 +32525,10 @@
         <v>2.7863013698630139</v>
       </c>
       <c r="K11" s="167" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L11" s="166" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M11" s="166" t="s">
         <v>51</v>
@@ -32583,7 +32553,7 @@
         <v>152</v>
       </c>
       <c r="C12" s="169" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D12" s="169" t="s">
         <v>45</v>
@@ -32607,10 +32577,10 @@
         <v>2.1863013698630138</v>
       </c>
       <c r="K12" s="167" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L12" s="166" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M12" s="166" t="s">
         <v>51</v>
@@ -32639,7 +32609,7 @@
         <v>50</v>
       </c>
       <c r="C13" s="169" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D13" s="169" t="s">
         <v>45</v>
@@ -32663,10 +32633,10 @@
         <v>0.52054794520547942</v>
       </c>
       <c r="K13" s="167" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L13" s="166" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M13" s="166" t="s">
         <v>51</v>
@@ -32695,7 +32665,7 @@
         <v>188</v>
       </c>
       <c r="C14" s="169" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D14" s="169" t="s">
         <v>45</v>
@@ -32719,10 +32689,10 @@
         <v>0.18356164383561641</v>
       </c>
       <c r="K14" s="167" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L14" s="166" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M14" s="166" t="s">
         <v>189</v>
@@ -32751,7 +32721,7 @@
         <v>193</v>
       </c>
       <c r="C15" s="169" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D15" s="169" t="s">
         <v>45</v>
@@ -32775,7 +32745,7 @@
         <v>1.7287671232876709</v>
       </c>
       <c r="K15" s="167" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L15" s="166" t="s">
         <v>93</v>
@@ -32807,7 +32777,7 @@
         <v>104</v>
       </c>
       <c r="C16" s="169" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D16" s="169" t="s">
         <v>45</v>
@@ -32831,7 +32801,7 @@
         <v>1.7287671232876709</v>
       </c>
       <c r="K16" s="167" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L16" s="166" t="s">
         <v>93</v>
@@ -32857,7 +32827,7 @@
         <v>202</v>
       </c>
       <c r="C17" s="169" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D17" s="169" t="s">
         <v>45</v>
@@ -32881,7 +32851,7 @@
         <v>3.0520547945205481</v>
       </c>
       <c r="K17" s="167" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L17" s="166" t="s">
         <v>93</v>
@@ -32913,7 +32883,7 @@
         <v>123</v>
       </c>
       <c r="C18" s="169" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D18" s="169" t="s">
         <v>45</v>
@@ -32937,7 +32907,7 @@
         <v>3.0520547945205481</v>
       </c>
       <c r="K18" s="167" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L18" s="166" t="s">
         <v>93</v>
@@ -32963,7 +32933,7 @@
         <v>108</v>
       </c>
       <c r="C19" s="169" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D19" s="169" t="s">
         <v>45</v>
@@ -32987,7 +32957,7 @@
         <v>1.693150684931507</v>
       </c>
       <c r="K19" s="167" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L19" s="166" t="s">
         <v>93</v>
@@ -33019,7 +32989,7 @@
         <v>120</v>
       </c>
       <c r="C20" s="169" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D20" s="169" t="s">
         <v>45</v>
@@ -33043,7 +33013,7 @@
         <v>0.69041095890410964</v>
       </c>
       <c r="K20" s="167" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L20" s="166" t="s">
         <v>93</v>
@@ -33075,7 +33045,7 @@
         <v>126</v>
       </c>
       <c r="C21" s="169" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D21" s="169" t="s">
         <v>45</v>
@@ -33099,7 +33069,7 @@
         <v>0.73424657534246573</v>
       </c>
       <c r="K21" s="167" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L21" s="166" t="s">
         <v>93</v>
@@ -33131,7 +33101,7 @@
         <v>140</v>
       </c>
       <c r="C22" s="169" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D22" s="169" t="s">
         <v>45</v>
@@ -33155,7 +33125,7 @@
         <v>1.7287671232876709</v>
       </c>
       <c r="K22" s="167" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L22" s="166" t="s">
         <v>93</v>
@@ -33181,7 +33151,7 @@
         <v>79</v>
       </c>
       <c r="C23" s="169" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D23" s="169" t="s">
         <v>45</v>
@@ -33205,7 +33175,7 @@
         <v>1.7287671232876709</v>
       </c>
       <c r="K23" s="167" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L23" s="166" t="s">
         <v>93</v>
@@ -33231,7 +33201,7 @@
         <v>216</v>
       </c>
       <c r="C24" s="153" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D24" s="153" t="s">
         <v>45</v>
@@ -33255,10 +33225,10 @@
         <v>1.76986301369863</v>
       </c>
       <c r="K24" s="151" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L24" s="144" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M24" s="144" t="s">
         <v>43</v>
@@ -33287,7 +33257,7 @@
         <v>169</v>
       </c>
       <c r="C25" s="153" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D25" s="153" t="s">
         <v>45</v>
@@ -33311,10 +33281,10 @@
         <v>1.76986301369863</v>
       </c>
       <c r="K25" s="151" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L25" s="144" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M25" s="144" t="s">
         <v>43</v>
@@ -33337,7 +33307,7 @@
         <v>199</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D26" s="153" t="s">
         <v>45</v>
@@ -33361,10 +33331,10 @@
         <v>1.76986301369863</v>
       </c>
       <c r="K26" s="151" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L26" s="144" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M26" s="144" t="s">
         <v>43</v>
@@ -33387,7 +33357,7 @@
         <v>42</v>
       </c>
       <c r="C27" s="153" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D27" s="153" t="s">
         <v>45</v>
@@ -33411,10 +33381,10 @@
         <v>1.76986301369863</v>
       </c>
       <c r="K27" s="151" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L27" s="144" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M27" s="144" t="s">
         <v>43</v>
@@ -33437,7 +33407,7 @@
         <v>219</v>
       </c>
       <c r="C28" s="153" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D28" s="153" t="s">
         <v>45</v>
@@ -33461,10 +33431,10 @@
         <v>1.76986301369863</v>
       </c>
       <c r="K28" s="151" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L28" s="144" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M28" s="144" t="s">
         <v>43</v>
@@ -33487,7 +33457,7 @@
         <v>137</v>
       </c>
       <c r="C29" s="153" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D29" s="153" t="s">
         <v>59</v>
@@ -33511,10 +33481,10 @@
         <v>0.60273972602739723</v>
       </c>
       <c r="K29" s="151" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L29" s="144" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M29" s="144" t="s">
         <v>43</v>
@@ -33539,7 +33509,7 @@
         <v>155</v>
       </c>
       <c r="C30" s="153" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D30" s="153" t="s">
         <v>45</v>
@@ -33563,10 +33533,10 @@
         <v>3.2712328767123289</v>
       </c>
       <c r="K30" s="151" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L30" s="144" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M30" s="144" t="s">
         <v>64</v>
@@ -33591,7 +33561,7 @@
         <v>237</v>
       </c>
       <c r="C31" s="153" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D31" s="153" t="s">
         <v>45</v>
@@ -33615,10 +33585,10 @@
         <v>1.1589041095890411</v>
       </c>
       <c r="K31" s="151" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L31" s="144" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M31" s="144" t="s">
         <v>64</v>
@@ -33643,7 +33613,7 @@
         <v>209</v>
       </c>
       <c r="C32" s="144" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D32" s="144" t="s">
         <v>45</v>
@@ -33667,10 +33637,10 @@
         <v>0.76712328767123283</v>
       </c>
       <c r="K32" s="151" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L32" s="144" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M32" s="144" t="s">
         <v>64</v>
@@ -33692,10 +33662,10 @@
     </row>
     <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B33" s="153" t="s">
+        <v>567</v>
+      </c>
+      <c r="C33" s="153" t="s">
         <v>568</v>
-      </c>
-      <c r="C33" s="153" t="s">
-        <v>569</v>
       </c>
       <c r="D33" s="153" t="s">
         <v>45</v>
@@ -33719,10 +33689,10 @@
         <v>0.73424657534246573</v>
       </c>
       <c r="K33" s="151" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L33" s="144" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M33" s="144" t="s">
         <v>64</v>
@@ -33751,7 +33721,7 @@
         <v>75</v>
       </c>
       <c r="C34" s="153" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D34" s="153" t="s">
         <v>45</v>
@@ -33775,10 +33745,10 @@
         <v>0.41095890410958902</v>
       </c>
       <c r="K34" s="151" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L34" s="144" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M34" s="144" t="s">
         <v>64</v>
@@ -33807,7 +33777,7 @@
         <v>225</v>
       </c>
       <c r="C35" s="153" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D35" s="153" t="s">
         <v>45</v>
@@ -33831,10 +33801,10 @@
         <v>0.26849315068493151</v>
       </c>
       <c r="K35" s="151" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L35" s="144" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M35" s="144" t="s">
         <v>64</v>
@@ -33863,7 +33833,7 @@
         <v>206</v>
       </c>
       <c r="C36" s="153" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D36" s="153" t="s">
         <v>45</v>
@@ -33887,10 +33857,10 @@
         <v>1.0602739726027399</v>
       </c>
       <c r="K36" s="151" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L36" s="144" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M36" s="144" t="s">
         <v>57</v>
@@ -33919,7 +33889,7 @@
         <v>56</v>
       </c>
       <c r="C37" s="153" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D37" s="153" t="s">
         <v>59</v>
@@ -33943,10 +33913,10 @@
         <v>0.73698630136986298</v>
       </c>
       <c r="K37" s="151" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L37" s="144" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M37" s="144" t="s">
         <v>57</v>
@@ -33975,7 +33945,7 @@
         <v>114</v>
       </c>
       <c r="C38" s="153" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D38" s="153" t="s">
         <v>59</v>
@@ -33999,10 +33969,10 @@
         <v>0.73698630136986298</v>
       </c>
       <c r="K38" s="151" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L38" s="144" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M38" s="144" t="s">
         <v>57</v>
@@ -34025,7 +33995,7 @@
         <v>117</v>
       </c>
       <c r="C39" s="153" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D39" s="153" t="s">
         <v>59</v>
@@ -34049,10 +34019,10 @@
         <v>0.73698630136986298</v>
       </c>
       <c r="K39" s="151" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L39" s="144" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M39" s="144" t="s">
         <v>57</v>
@@ -34075,7 +34045,7 @@
         <v>85</v>
       </c>
       <c r="C40" s="153" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D40" s="153" t="s">
         <v>59</v>
@@ -34099,10 +34069,10 @@
         <v>0.73698630136986298</v>
       </c>
       <c r="K40" s="151" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L40" s="144" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M40" s="144" t="s">
         <v>57</v>
@@ -34125,7 +34095,7 @@
         <v>175</v>
       </c>
       <c r="C41" s="153" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D41" s="153" t="s">
         <v>59</v>
@@ -34149,10 +34119,10 @@
         <v>0.73698630136986298</v>
       </c>
       <c r="K41" s="151" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L41" s="144" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M41" s="144" t="s">
         <v>57</v>
@@ -34175,7 +34145,7 @@
         <v>134</v>
       </c>
       <c r="C42" s="153" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D42" s="153" t="s">
         <v>59</v>
@@ -34199,10 +34169,10 @@
         <v>0.73698630136986298</v>
       </c>
       <c r="K42" s="151" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L42" s="144" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M42" s="144" t="s">
         <v>57</v>
@@ -34242,7 +34212,7 @@
     </row>
     <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B44" s="148" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C44" s="147"/>
       <c r="D44" s="147"/>
@@ -34343,7 +34313,7 @@
   <sheetData>
     <row r="1" spans="1:57" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="344" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="2" spans="1:57" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -34361,7 +34331,7 @@
     </row>
     <row r="3" spans="1:57" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="V3" s="343" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="W3" s="342"/>
       <c r="X3" s="342"/>
@@ -34405,15 +34375,15 @@
     </row>
     <row r="4" spans="1:57" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="336" t="s">
+        <v>576</v>
+      </c>
+      <c r="S4" s="356" t="s">
         <v>577</v>
-      </c>
-      <c r="S4" s="356" t="s">
-        <v>578</v>
       </c>
       <c r="T4" s="357"/>
       <c r="U4" s="358"/>
       <c r="V4" s="360" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="W4" s="357"/>
       <c r="X4" s="357"/>
@@ -34426,7 +34396,7 @@
       <c r="AE4" s="357"/>
       <c r="AF4" s="358"/>
       <c r="AG4" s="359" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AH4" s="357"/>
       <c r="AI4" s="357"/>
@@ -34434,7 +34404,7 @@
       <c r="AK4" s="357"/>
       <c r="AL4" s="358"/>
       <c r="AM4" s="359" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AN4" s="357"/>
       <c r="AO4" s="357"/>
@@ -34456,85 +34426,85 @@
         <v>7</v>
       </c>
       <c r="D5" s="316" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E5" s="316" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F5" s="316" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="316" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H5" s="316" t="s">
         <v>0</v>
       </c>
       <c r="I5" s="316" t="s">
+        <v>581</v>
+      </c>
+      <c r="J5" s="316" t="s">
         <v>582</v>
       </c>
-      <c r="J5" s="316" t="s">
+      <c r="K5" s="316" t="s">
         <v>583</v>
       </c>
-      <c r="K5" s="316" t="s">
-        <v>584</v>
-      </c>
       <c r="L5" s="316" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="M5" s="317" t="s">
         <v>9</v>
       </c>
       <c r="N5" s="317" t="s">
+        <v>584</v>
+      </c>
+      <c r="O5" s="317" t="s">
         <v>585</v>
-      </c>
-      <c r="O5" s="317" t="s">
-        <v>586</v>
       </c>
       <c r="P5" s="334" t="s">
         <v>29</v>
       </c>
       <c r="Q5" s="333" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="R5" s="317" t="s">
         <v>30</v>
       </c>
       <c r="S5" s="332" t="s">
+        <v>587</v>
+      </c>
+      <c r="T5" s="327" t="s">
         <v>588</v>
       </c>
-      <c r="T5" s="327" t="s">
+      <c r="U5" s="331" t="s">
         <v>589</v>
       </c>
-      <c r="U5" s="331" t="s">
+      <c r="V5" s="324" t="s">
+        <v>587</v>
+      </c>
+      <c r="W5" s="330" t="s">
         <v>590</v>
       </c>
-      <c r="V5" s="324" t="s">
+      <c r="X5" s="329" t="s">
+        <v>591</v>
+      </c>
+      <c r="Y5" s="328" t="s">
+        <v>592</v>
+      </c>
+      <c r="Z5" s="327" t="s">
         <v>588</v>
       </c>
-      <c r="W5" s="330" t="s">
-        <v>591</v>
-      </c>
-      <c r="X5" s="329" t="s">
-        <v>592</v>
-      </c>
-      <c r="Y5" s="328" t="s">
+      <c r="AA5" s="327" t="s">
         <v>593</v>
       </c>
-      <c r="Z5" s="327" t="s">
-        <v>589</v>
-      </c>
-      <c r="AA5" s="327" t="s">
+      <c r="AB5" s="327" t="s">
         <v>594</v>
       </c>
-      <c r="AB5" s="327" t="s">
+      <c r="AC5" s="327" t="s">
         <v>595</v>
       </c>
-      <c r="AC5" s="327" t="s">
+      <c r="AD5" s="326" t="s">
         <v>596</v>
-      </c>
-      <c r="AD5" s="326" t="s">
-        <v>597</v>
       </c>
       <c r="AE5" s="321" t="str">
         <f>AE3&amp;"x Valuation"</f>
@@ -34545,16 +34515,16 @@
         <v>8x Valuation</v>
       </c>
       <c r="AG5" s="325" t="s">
+        <v>597</v>
+      </c>
+      <c r="AH5" s="323" t="s">
         <v>598</v>
       </c>
-      <c r="AH5" s="323" t="s">
+      <c r="AI5" s="323" t="s">
         <v>599</v>
       </c>
-      <c r="AI5" s="323" t="s">
+      <c r="AJ5" s="322" t="s">
         <v>600</v>
-      </c>
-      <c r="AJ5" s="322" t="s">
-        <v>601</v>
       </c>
       <c r="AK5" s="321" t="str">
         <f>AK3&amp;"x Valuation"</f>
@@ -34565,16 +34535,16 @@
         <v>6x Valuation</v>
       </c>
       <c r="AM5" s="324" t="s">
+        <v>601</v>
+      </c>
+      <c r="AN5" s="323" t="s">
         <v>602</v>
       </c>
-      <c r="AN5" s="323" t="s">
+      <c r="AO5" s="323" t="s">
         <v>603</v>
       </c>
-      <c r="AO5" s="323" t="s">
+      <c r="AP5" s="322" t="s">
         <v>604</v>
-      </c>
-      <c r="AP5" s="322" t="s">
-        <v>605</v>
       </c>
       <c r="AQ5" s="321" t="str">
         <f>AQ3&amp;"x Valuation"</f>
@@ -34585,38 +34555,38 @@
         <v>6x Valuation</v>
       </c>
       <c r="AS5" s="320" t="s">
+        <v>605</v>
+      </c>
+      <c r="AT5" s="320" t="s">
         <v>606</v>
       </c>
-      <c r="AT5" s="320" t="s">
+      <c r="AU5" s="320" t="s">
         <v>607</v>
-      </c>
-      <c r="AU5" s="320" t="s">
-        <v>608</v>
       </c>
       <c r="AV5" s="320" t="str">
         <f>+AF3&amp;"x Trend"</f>
         <v>8x Trend</v>
       </c>
       <c r="AW5" s="320" t="s">
+        <v>608</v>
+      </c>
+      <c r="AX5" s="320" t="s">
         <v>609</v>
       </c>
-      <c r="AX5" s="320" t="s">
+      <c r="AZ5" s="319" t="s">
         <v>610</v>
       </c>
-      <c r="AZ5" s="319" t="s">
+      <c r="BA5" s="318" t="s">
         <v>611</v>
       </c>
-      <c r="BA5" s="318" t="s">
+      <c r="BB5" s="318" t="s">
         <v>612</v>
       </c>
-      <c r="BB5" s="318" t="s">
+      <c r="BC5" s="317" t="s">
         <v>613</v>
       </c>
-      <c r="BC5" s="317" t="s">
+      <c r="BD5" s="317" t="s">
         <v>614</v>
-      </c>
-      <c r="BD5" s="317" t="s">
-        <v>615</v>
       </c>
       <c r="BE5" s="303"/>
     </row>
@@ -34655,7 +34625,7 @@
         <v>60</v>
       </c>
       <c r="L6" s="274" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="M6" s="272">
         <v>26</v>
@@ -34832,7 +34802,7 @@
         <v>108</v>
       </c>
       <c r="L7" s="73" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M7" s="65">
         <v>31</v>
@@ -35008,7 +34978,7 @@
         <v>64</v>
       </c>
       <c r="L8" s="73" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="M8" s="65">
         <v>22</v>
@@ -35134,7 +35104,7 @@
         <v>18.267673277109282</v>
       </c>
       <c r="AZ8" s="73" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="BA8" s="305">
         <v>74.063204999999996</v>
@@ -35185,7 +35155,7 @@
         <v>110</v>
       </c>
       <c r="L9" s="73" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="M9" s="65">
         <v>25</v>
@@ -35356,7 +35326,7 @@
         <v>147</v>
       </c>
       <c r="L10" s="212" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="M10" s="210">
         <v>29</v>
@@ -35506,7 +35476,7 @@
         <v>79</v>
       </c>
       <c r="E11" s="274" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F11" s="274">
         <v>2024</v>
@@ -35527,7 +35497,7 @@
         <v>78</v>
       </c>
       <c r="L11" s="274" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="M11" s="272">
         <v>32</v>
@@ -35682,7 +35652,7 @@
         <v>104</v>
       </c>
       <c r="E12" s="73" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F12" s="73">
         <v>2024</v>
@@ -35703,7 +35673,7 @@
         <v>80</v>
       </c>
       <c r="L12" s="73" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="M12" s="65">
         <v>29</v>
@@ -35856,7 +35826,7 @@
         <v>140</v>
       </c>
       <c r="E13" s="73" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F13" s="73">
         <v>2024</v>
@@ -35877,7 +35847,7 @@
         <v>122</v>
       </c>
       <c r="L13" s="73" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="M13" s="65">
         <v>34</v>
@@ -36029,7 +35999,7 @@
         <v>193</v>
       </c>
       <c r="E14" s="212" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F14" s="212">
         <v>2024</v>
@@ -36050,7 +36020,7 @@
         <v>59</v>
       </c>
       <c r="L14" s="212" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="M14" s="210">
         <v>29</v>
@@ -36176,7 +36146,7 @@
         <v>-288.16316749999953</v>
       </c>
       <c r="AZ14" s="73" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="BA14" s="305">
         <v>78.014042916666654</v>
@@ -36227,7 +36197,7 @@
         <v>77</v>
       </c>
       <c r="L15" s="274" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="M15" s="272">
         <v>41</v>
@@ -36392,7 +36362,7 @@
         <v>92</v>
       </c>
       <c r="L16" s="73" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="M16" s="65">
         <v>30</v>
@@ -36552,7 +36522,7 @@
         <v>128</v>
       </c>
       <c r="L17" s="73" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="M17" s="65">
         <v>37</v>
@@ -36712,7 +36682,7 @@
         <v>97</v>
       </c>
       <c r="L18" s="56" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="M18" s="59">
         <v>30</v>
@@ -36879,7 +36849,7 @@
         <v>27</v>
       </c>
       <c r="L19" s="73" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="M19" s="65">
         <v>43</v>
@@ -37039,7 +37009,7 @@
         <v>98</v>
       </c>
       <c r="L20" s="274" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="M20" s="272">
         <v>32</v>
@@ -37202,7 +37172,7 @@
         <v>134</v>
       </c>
       <c r="L21" s="56" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="M21" s="59">
         <v>29</v>
@@ -37370,7 +37340,7 @@
         <v>108</v>
       </c>
       <c r="L22" s="73" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="M22" s="65">
         <v>22</v>
@@ -37530,7 +37500,7 @@
         <v>192</v>
       </c>
       <c r="L23" s="73" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="M23" s="65">
         <v>31</v>
@@ -37687,7 +37657,7 @@
         <v>80</v>
       </c>
       <c r="L24" s="73" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="M24" s="65">
         <v>31</v>
@@ -37847,7 +37817,7 @@
         <v>78</v>
       </c>
       <c r="L25" s="73" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="M25" s="65">
         <v>23</v>
@@ -38004,7 +37974,7 @@
         <v>63</v>
       </c>
       <c r="L26" s="73" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="M26" s="65">
         <v>27</v>
@@ -38162,7 +38132,7 @@
         <v>175</v>
       </c>
       <c r="L27" s="73" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="M27" s="65">
         <v>39</v>
@@ -38319,7 +38289,7 @@
         <v>119</v>
       </c>
       <c r="L28" s="254" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="M28" s="253">
         <v>33</v>
@@ -38485,7 +38455,7 @@
         <v>247</v>
       </c>
       <c r="L29" s="300" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="M29" s="299">
         <v>44</v>
@@ -38649,7 +38619,7 @@
         <v>178</v>
       </c>
       <c r="L30" s="56" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="M30" s="59">
         <v>30</v>
@@ -38809,7 +38779,7 @@
         <v>230</v>
       </c>
       <c r="L31" s="56" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="M31" s="59">
         <v>18</v>
@@ -38969,7 +38939,7 @@
         <v>83</v>
       </c>
       <c r="L32" s="56" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="M32" s="59">
         <v>38</v>
@@ -39105,7 +39075,7 @@
         <v>45</v>
       </c>
       <c r="D33" s="56" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E33" s="56" t="s">
         <v>44</v>
@@ -39129,7 +39099,7 @@
         <v>176</v>
       </c>
       <c r="L33" s="56" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="M33" s="59">
         <v>33</v>
@@ -39271,7 +39241,7 @@
         <v>45</v>
       </c>
       <c r="D34" s="56" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E34" s="56" t="s">
         <v>44</v>
@@ -39295,7 +39265,7 @@
         <v>182</v>
       </c>
       <c r="L34" s="56" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="M34" s="59">
         <v>29</v>
@@ -39461,7 +39431,7 @@
         <v>165</v>
       </c>
       <c r="L35" s="73" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="M35" s="65">
         <v>62</v>
@@ -39618,7 +39588,7 @@
         <v>275</v>
       </c>
       <c r="L36" s="212" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="M36" s="210">
         <v>42</v>
@@ -39779,7 +39749,7 @@
         <v>105</v>
       </c>
       <c r="L37" s="73" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="M37" s="65">
         <v>30</v>
@@ -39936,7 +39906,7 @@
         <v>123</v>
       </c>
       <c r="L38" s="73" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="M38" s="65">
         <v>41</v>
@@ -40093,7 +40063,7 @@
         <v>82</v>
       </c>
       <c r="L39" s="73" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="M39" s="65">
         <v>62</v>
@@ -40250,7 +40220,7 @@
         <v>127</v>
       </c>
       <c r="L40" s="73" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="M40" s="65">
         <v>45</v>
@@ -40407,7 +40377,7 @@
         <v>79</v>
       </c>
       <c r="L41" s="73" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="M41" s="65">
         <v>41</v>
@@ -40564,7 +40534,7 @@
         <v>26</v>
       </c>
       <c r="L42" s="73" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="M42" s="65">
         <v>43</v>
@@ -40721,7 +40691,7 @@
         <v>59</v>
       </c>
       <c r="L43" s="73" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="M43" s="65">
         <v>46</v>
@@ -40880,7 +40850,7 @@
         <v>136</v>
       </c>
       <c r="L44" s="274" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="M44" s="272">
         <v>33</v>
@@ -41010,7 +40980,7 @@
         <v>7</v>
       </c>
       <c r="B45" s="230" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C45" s="56" t="s">
         <v>45</v>
@@ -41040,7 +41010,7 @@
         <v>355</v>
       </c>
       <c r="L45" s="56" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="M45" s="59">
         <v>41</v>
@@ -41174,13 +41144,13 @@
         <v>7</v>
       </c>
       <c r="B46" s="230" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C46" s="73" t="s">
         <v>45</v>
       </c>
       <c r="D46" s="73" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E46" s="73" t="s">
         <v>65</v>
@@ -41204,7 +41174,7 @@
         <v>342</v>
       </c>
       <c r="L46" s="73" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="M46" s="65">
         <v>24</v>
@@ -41332,7 +41302,7 @@
         <v>7</v>
       </c>
       <c r="B47" s="230" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C47" s="73" t="s">
         <v>45</v>
@@ -41362,7 +41332,7 @@
         <v>507</v>
       </c>
       <c r="L47" s="73" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="M47" s="65">
         <v>27</v>
@@ -41519,7 +41489,7 @@
         <v>133</v>
       </c>
       <c r="L48" s="254" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="M48" s="253">
         <v>27</v>
@@ -41683,7 +41653,7 @@
         <v>74</v>
       </c>
       <c r="L49" s="56" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="M49" s="59">
         <v>22</v>
@@ -41813,7 +41783,7 @@
         <v>7</v>
       </c>
       <c r="B50" s="230" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C50" s="73" t="s">
         <v>66</v>
@@ -41843,7 +41813,7 @@
         <v>62</v>
       </c>
       <c r="L50" s="73" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="M50" s="65">
         <v>24</v>
@@ -41995,7 +41965,7 @@
         <v>194</v>
       </c>
       <c r="L51" s="73" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="M51" s="65">
         <v>48</v>
@@ -42147,7 +42117,7 @@
         <v>427</v>
       </c>
       <c r="L52" s="73" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="M52" s="65">
         <v>56</v>
@@ -42269,13 +42239,13 @@
         <v>7</v>
       </c>
       <c r="B53" s="213" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C53" s="212" t="s">
         <v>66</v>
       </c>
       <c r="D53" s="212" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E53" s="212" t="s">
         <v>65</v>
@@ -42299,7 +42269,7 @@
         <v>368</v>
       </c>
       <c r="L53" s="212" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="M53" s="210">
         <v>46</v>

--- a/data/CIM_Master_Data.xlsx
+++ b/data/CIM_Master_Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\calvi\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\calvi\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\S9NNQ3WT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DED93E4-16A6-440C-8B3E-CF2216E43593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77C5C63-DDBF-4828-B2DB-CAC597C8E962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6888,10 +6888,12 @@
         <v>0.30594115554713192</v>
       </c>
       <c r="AC3" s="346">
-        <v>469.63326323670242</v>
+        <f>+V3*6</f>
+        <v>338.89260562499976</v>
       </c>
       <c r="AD3" s="346">
-        <v>471.24628636111072</v>
+        <f>5.5*AA3</f>
+        <v>450.75731738888857</v>
       </c>
       <c r="AE3" s="346">
         <v>450</v>
@@ -7019,7 +7021,8 @@
         <v>0</v>
       </c>
       <c r="AD4" s="346">
-        <v>576.24858646400037</v>
+        <f t="shared" ref="AD4:AD10" si="0">5.5*AA4</f>
+        <v>551.19430009600057</v>
       </c>
       <c r="AE4" s="346">
         <v>550</v>
@@ -7144,10 +7147,12 @@
         <v>0.42872766971873799</v>
       </c>
       <c r="AC5" s="346">
-        <v>170.24970965871319</v>
+        <f t="shared" ref="AC4:AC10" si="1">+V5*6</f>
+        <v>407.95918936363648</v>
       </c>
       <c r="AD5" s="346">
-        <v>819.97792406206895</v>
+        <f t="shared" si="0"/>
+        <v>784.32670997241394</v>
       </c>
       <c r="AE5" s="346">
         <v>500</v>
@@ -7272,10 +7277,12 @@
         <v>0.51151898774997184</v>
       </c>
       <c r="AC6" s="346">
-        <v>1688.968058054714</v>
+        <f t="shared" si="1"/>
+        <v>1738.3902879999994</v>
       </c>
       <c r="AD6" s="346">
-        <v>2324.022433783065</v>
+        <f t="shared" si="0"/>
+        <v>2222.9779801403229</v>
       </c>
       <c r="AE6" s="346">
         <v>2000</v>
@@ -7400,10 +7407,12 @@
         <v>0.50968537910264655</v>
       </c>
       <c r="AC7" s="346">
-        <v>1794.5280440925701</v>
+        <f t="shared" si="1"/>
+        <v>1738.6271756842098</v>
       </c>
       <c r="AD7" s="346">
-        <v>1848.1622785249999</v>
+        <f t="shared" si="0"/>
+        <v>1767.8073968499993</v>
       </c>
       <c r="AE7" s="346">
         <v>1800</v>
@@ -7528,10 +7537,12 @@
         <v>0.51234016982186248</v>
       </c>
       <c r="AC8" s="346">
-        <v>737.22160781922412</v>
+        <f t="shared" si="1"/>
+        <v>1513.3617644999997</v>
       </c>
       <c r="AD8" s="346">
-        <v>1461.3724300199999</v>
+        <f t="shared" si="0"/>
+        <v>1397.8344982799999</v>
       </c>
       <c r="AE8" s="346">
         <v>1300</v>
@@ -7656,10 +7667,12 @@
         <v>0.24219225301187319</v>
       </c>
       <c r="AC9" s="346">
-        <v>919.01705147200153</v>
+        <f t="shared" si="1"/>
+        <v>686.44320000000027</v>
       </c>
       <c r="AD9" s="346">
-        <v>492.05366642045442</v>
+        <f t="shared" si="0"/>
+        <v>470.66002874999981</v>
       </c>
       <c r="AE9" s="346">
         <v>800</v>
@@ -7784,10 +7797,12 @@
         <v>0.33500456066349488</v>
       </c>
       <c r="AC10" s="346">
-        <v>918.96599319567781</v>
+        <f t="shared" si="1"/>
+        <v>360.85607999999974</v>
       </c>
       <c r="AD10" s="346">
-        <v>820.82646962499985</v>
+        <f t="shared" si="0"/>
+        <v>785.13836225</v>
       </c>
       <c r="AE10" s="346">
         <v>600</v>
@@ -8053,7 +8068,8 @@
         <v>0</v>
       </c>
       <c r="AD13" s="346">
-        <v>349.04746426428602</v>
+        <f t="shared" ref="AD13:AD46" si="2">5.5*AA13</f>
+        <v>333.87148755714315</v>
       </c>
       <c r="AE13" s="346">
         <v>300</v>
@@ -8178,10 +8194,12 @@
         <v>0.14699943284444331</v>
       </c>
       <c r="AC14" s="346">
-        <v>166.3777916679511</v>
+        <f t="shared" ref="AC13:AC54" si="3">+V14*6</f>
+        <v>374.22923550000024</v>
       </c>
       <c r="AD14" s="346">
-        <v>217.32266628888891</v>
+        <f t="shared" si="2"/>
+        <v>207.87385471111108</v>
       </c>
       <c r="AE14" s="346">
         <v>220</v>
@@ -8306,10 +8324,12 @@
         <v>9.9504678412912259E-2</v>
       </c>
       <c r="AC15" s="346">
-        <v>215.88705495871821</v>
+        <f t="shared" si="3"/>
+        <v>438.5966983999997</v>
       </c>
       <c r="AD15" s="346">
-        <v>146.3400914947367</v>
+        <f t="shared" si="2"/>
+        <v>139.9774788210525</v>
       </c>
       <c r="AE15" s="346">
         <v>500</v>
@@ -8434,10 +8454,12 @@
         <v>0.22173483295966681</v>
       </c>
       <c r="AC16" s="346">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>224.41387894736826</v>
       </c>
       <c r="AD16" s="346">
-        <v>439.38320825000011</v>
+        <f t="shared" si="2"/>
+        <v>420.2795905000001</v>
       </c>
       <c r="AE16" s="346">
         <v>100</v>
@@ -8562,10 +8584,12 @@
         <v>0.27919892496068238</v>
       </c>
       <c r="AC17" s="346">
-        <v>482.58024980429849</v>
+        <f t="shared" si="3"/>
+        <v>743.95921429411715</v>
       </c>
       <c r="AD17" s="346">
-        <v>831.90107772500005</v>
+        <f t="shared" si="2"/>
+        <v>795.73146565000002</v>
       </c>
       <c r="AE17" s="346">
         <v>850</v>
@@ -8690,10 +8714,12 @@
         <v>0.2203560676840029</v>
       </c>
       <c r="AC18" s="346">
-        <v>464.15249615277401</v>
+        <f t="shared" si="3"/>
+        <v>641.80624549999982</v>
       </c>
       <c r="AD18" s="346">
-        <v>488.21870000000001</v>
+        <f t="shared" si="2"/>
+        <v>466.99180000000001</v>
       </c>
       <c r="AE18" s="346">
         <v>500</v>
@@ -8818,10 +8844,12 @@
         <v>0.30943002747757758</v>
       </c>
       <c r="AC19" s="346">
-        <v>864.73768992339683</v>
+        <f t="shared" si="3"/>
+        <v>628.73087261538444</v>
       </c>
       <c r="AD19" s="346">
-        <v>735.5804650499997</v>
+        <f t="shared" si="2"/>
+        <v>703.59870569999998</v>
       </c>
       <c r="AE19" s="346">
         <v>800</v>
@@ -8946,10 +8974,12 @@
         <v>0.19927201558117821</v>
       </c>
       <c r="AC20" s="346">
-        <v>259.60800321059281</v>
+        <f t="shared" si="3"/>
+        <v>425.88408666666669</v>
       </c>
       <c r="AD20" s="346">
-        <v>293.16702749999962</v>
+        <f t="shared" si="2"/>
+        <v>280.42063499999955</v>
       </c>
       <c r="AE20" s="346">
         <v>300</v>
@@ -9074,10 +9104,12 @@
         <v>0.1650208597436231</v>
       </c>
       <c r="AC21" s="346">
-        <v>172.39103280516201</v>
+        <f t="shared" si="3"/>
+        <v>380.8318057499996</v>
       </c>
       <c r="AD21" s="346">
-        <v>374.10071943653918</v>
+        <f t="shared" si="2"/>
+        <v>357.83547076538531</v>
       </c>
       <c r="AE21" s="346">
         <v>380</v>
@@ -9202,10 +9234,12 @@
         <v>0.23280457885716471</v>
       </c>
       <c r="AC22" s="346">
-        <v>404.08316388214462</v>
+        <f t="shared" si="3"/>
+        <v>217.52544417391312</v>
       </c>
       <c r="AD22" s="346">
-        <v>559.235243975</v>
+        <f t="shared" si="2"/>
+        <v>534.92066814999998</v>
       </c>
       <c r="AE22" s="346">
         <v>500</v>
@@ -9330,10 +9364,12 @@
         <v>0.38594869087105538</v>
       </c>
       <c r="AC23" s="346">
-        <v>757.15529903414654</v>
+        <f t="shared" si="3"/>
+        <v>602.04917250000005</v>
       </c>
       <c r="AD23" s="346">
-        <v>1003.47254992132</v>
+        <f t="shared" si="2"/>
+        <v>959.84330862039292</v>
       </c>
       <c r="AE23" s="346">
         <v>600</v>
@@ -9458,10 +9494,12 @@
         <v>0.44602164748573891</v>
       </c>
       <c r="AC24" s="346">
-        <v>2047.934851519921</v>
+        <f t="shared" si="3"/>
+        <v>2180.8214685789471</v>
       </c>
       <c r="AD24" s="346">
-        <v>2600.235656162386</v>
+        <f t="shared" si="2"/>
+        <v>2487.1819319814126</v>
       </c>
       <c r="AE24" s="346">
         <v>2100</v>
@@ -9586,10 +9624,12 @@
         <v>0.17728481584933689</v>
       </c>
       <c r="AC25" s="346">
-        <v>264.5208562208237</v>
+        <f t="shared" si="3"/>
+        <v>285.63546494117679</v>
       </c>
       <c r="AD25" s="346">
-        <v>408.07550130000038</v>
+        <f t="shared" si="2"/>
+        <v>390.33308820000042</v>
       </c>
       <c r="AE25" s="346">
         <v>400</v>
@@ -9714,10 +9754,12 @@
         <v>0.39232476927430321</v>
       </c>
       <c r="AC26" s="346">
-        <v>160.5501237357318</v>
+        <f t="shared" si="3"/>
+        <v>461.27238</v>
       </c>
       <c r="AD26" s="346">
-        <v>1413.222335980952</v>
+        <f t="shared" si="2"/>
+        <v>1351.7778865904759</v>
       </c>
       <c r="AE26" s="346">
         <v>1200</v>
@@ -9842,10 +9884,12 @@
         <v>4.2421967692307723E-2</v>
       </c>
       <c r="AC27" s="346">
-        <v>283.01176762842732</v>
+        <f t="shared" si="3"/>
+        <v>74.242727399999978</v>
       </c>
       <c r="AD27" s="346">
-        <v>126.84168340000009</v>
+        <f t="shared" si="2"/>
+        <v>121.32682760000004</v>
       </c>
       <c r="AE27" s="346">
         <v>250</v>
@@ -9970,10 +10014,12 @@
         <v>0.23575081369332929</v>
       </c>
       <c r="AC28" s="346">
-        <v>449.24090643537062</v>
+        <f t="shared" si="3"/>
+        <v>364.07591999999994</v>
       </c>
       <c r="AD28" s="346">
-        <v>449.24090643537062</v>
+        <f t="shared" si="2"/>
+        <v>429.70869311209356</v>
       </c>
       <c r="AE28" s="346">
         <v>425</v>
@@ -10098,10 +10144,12 @@
         <v>0.33810901982170533</v>
       </c>
       <c r="AC29" s="346">
-        <v>326.00352729645812</v>
+        <f t="shared" si="3"/>
+        <v>638.77518436363641</v>
       </c>
       <c r="AD29" s="346">
-        <v>812.6713108564818</v>
+        <f t="shared" si="2"/>
+        <v>777.3377756018524</v>
       </c>
       <c r="AE29" s="346">
         <v>500</v>
@@ -10226,10 +10274,12 @@
         <v>0.27239088074419338</v>
       </c>
       <c r="AC30" s="346">
-        <v>418.26767327710928</v>
+        <f t="shared" si="3"/>
+        <v>330.86310000000014</v>
       </c>
       <c r="AD30" s="346">
-        <v>418.26767327710928</v>
+        <f t="shared" si="2"/>
+        <v>400.08212226506106</v>
       </c>
       <c r="AE30" s="346">
         <v>400</v>
@@ -10357,10 +10407,12 @@
         <v>0.35290948209971362</v>
       </c>
       <c r="AC31" s="346">
-        <v>668.95620481144192</v>
+        <f t="shared" si="3"/>
+        <v>622.00154999999972</v>
       </c>
       <c r="AD31" s="346">
-        <v>914.43069952133806</v>
+        <f t="shared" si="2"/>
+        <v>874.67284302041048</v>
       </c>
       <c r="AE31" s="346">
         <v>800</v>
@@ -10485,10 +10537,12 @@
         <v>0.13194494515011199</v>
       </c>
       <c r="AC32" s="346">
-        <v>227.30499257848669</v>
+        <f t="shared" si="3"/>
+        <v>125.73911999999977</v>
       </c>
       <c r="AD32" s="346">
-        <v>227.30499257848669</v>
+        <f t="shared" si="2"/>
+        <v>217.4221668142047</v>
       </c>
       <c r="AE32" s="346">
         <v>250</v>
@@ -10613,10 +10667,12 @@
         <v>0.25151342209910588</v>
       </c>
       <c r="AC33" s="346">
-        <v>281.10155942086658</v>
+        <f t="shared" si="3"/>
+        <v>382.21701272727296</v>
       </c>
       <c r="AD33" s="346">
-        <v>569.09070017703698</v>
+        <f t="shared" si="2"/>
+        <v>591.83579295343077</v>
       </c>
       <c r="AE33" s="346">
         <v>500</v>
@@ -10741,10 +10797,12 @@
         <v>0.36915413037479683</v>
       </c>
       <c r="AC34" s="346">
-        <v>1028.2140009418849</v>
+        <f t="shared" si="3"/>
+        <v>957.49107000000026</v>
       </c>
       <c r="AD34" s="346">
-        <v>1095.325672021052</v>
+        <f t="shared" si="2"/>
+        <v>1264.3070950533606</v>
       </c>
       <c r="AE34" s="346">
         <v>900</v>
@@ -10869,10 +10927,12 @@
         <v>0.32819117948000565</v>
       </c>
       <c r="AC35" s="346">
-        <v>765.8663374539567</v>
+        <f t="shared" si="3"/>
+        <v>1283.3567736</v>
       </c>
       <c r="AD35" s="346">
-        <v>910.65550246617659</v>
+        <f t="shared" si="2"/>
+        <v>1273.412734</v>
       </c>
       <c r="AE35" s="346">
         <v>1100</v>
@@ -10997,10 +11057,12 @@
         <v>0.2382657128930348</v>
       </c>
       <c r="AC36" s="346">
-        <v>939.28725204093132</v>
+        <f t="shared" si="3"/>
+        <v>771.47838150000007</v>
       </c>
       <c r="AD36" s="346">
-        <v>490.93886500000002</v>
+        <f t="shared" si="2"/>
+        <v>779.54200271072727</v>
       </c>
       <c r="AE36" s="346">
         <v>700</v>
@@ -11125,10 +11187,12 @@
         <v>0.22181881154304761</v>
       </c>
       <c r="AC37" s="346">
-        <v>228.29665861829511</v>
+        <f t="shared" si="3"/>
+        <v>660.30399399999965</v>
       </c>
       <c r="AD37" s="346">
-        <v>412.21684728421019</v>
+        <f t="shared" si="2"/>
+        <v>778.78959546186604</v>
       </c>
       <c r="AE37" s="346">
         <v>700</v>
@@ -11253,10 +11317,12 @@
         <v>0.40847233699789431</v>
       </c>
       <c r="AC38" s="346">
-        <v>1483.649878721631</v>
+        <f t="shared" si="3"/>
+        <v>1597.8534239999994</v>
       </c>
       <c r="AD38" s="346">
-        <v>1931.658811686154</v>
+        <f t="shared" si="2"/>
+        <v>1847.6736459606682</v>
       </c>
       <c r="AE38" s="346">
         <v>1800</v>
@@ -11384,7 +11450,8 @@
         <v>0</v>
       </c>
       <c r="AD39" s="346">
-        <v>381.17729142857229</v>
+        <f t="shared" si="2"/>
+        <v>364.60436571428653</v>
       </c>
       <c r="AE39" s="346">
         <v>300</v>
@@ -11509,10 +11576,12 @@
         <v>0.36587994385922701</v>
       </c>
       <c r="AC40" s="346">
-        <v>1489.7020995367529</v>
+        <f t="shared" si="3"/>
+        <v>1944.5757293333327</v>
       </c>
       <c r="AD40" s="346">
-        <v>2010.200949312964</v>
+        <f t="shared" si="2"/>
+        <v>1922.8009080384868</v>
       </c>
       <c r="AE40" s="346">
         <v>1900</v>
@@ -11637,10 +11706,12 @@
         <v>0.20884870618509199</v>
       </c>
       <c r="AC41" s="346">
-        <v>526.78136109192258</v>
+        <f t="shared" si="3"/>
+        <v>727.88873999999998</v>
       </c>
       <c r="AD41" s="346">
-        <v>404.39991500000019</v>
+        <f t="shared" si="2"/>
+        <v>386.81731000000019</v>
       </c>
       <c r="AE41" s="346">
         <v>550</v>
@@ -11765,10 +11836,12 @@
         <v>0.19872951532291941</v>
       </c>
       <c r="AC42" s="346">
-        <v>464.77452669857041</v>
+        <f t="shared" si="3"/>
+        <v>364.11812099999941</v>
       </c>
       <c r="AD42" s="346">
-        <v>663.68959511182857</v>
+        <f t="shared" si="2"/>
+        <v>634.83352575914034</v>
       </c>
       <c r="AE42" s="346">
         <v>500</v>
@@ -11893,10 +11966,12 @@
         <v>0.27816010116524648</v>
       </c>
       <c r="AC43" s="346">
-        <v>779.72997564747368</v>
+        <f t="shared" si="3"/>
+        <v>837.1870087741936</v>
       </c>
       <c r="AD43" s="346">
-        <v>1112.8840753153161</v>
+        <f t="shared" si="2"/>
+        <v>1064.4978111711719</v>
       </c>
       <c r="AE43" s="346">
         <v>1000</v>
@@ -12024,10 +12099,12 @@
         <v>0.36606115661291833</v>
       </c>
       <c r="AC44" s="346">
-        <v>1337.046007008792</v>
+        <f t="shared" si="3"/>
+        <v>1206.8761921395344</v>
       </c>
       <c r="AD44" s="346">
-        <v>1490.609381266667</v>
+        <f t="shared" si="2"/>
+        <v>1425.8002777333338</v>
       </c>
       <c r="AE44" s="346">
         <v>1400</v>
@@ -12152,10 +12229,12 @@
         <v>0.29978580126908122</v>
       </c>
       <c r="AC45" s="346">
-        <v>1282.631710525992</v>
+        <f t="shared" si="3"/>
+        <v>889.90519938461489</v>
       </c>
       <c r="AD45" s="346">
-        <v>1218.287076666667</v>
+        <f t="shared" si="2"/>
+        <v>1165.3180733333331</v>
       </c>
       <c r="AE45" s="346">
         <v>1400</v>
@@ -12280,10 +12359,12 @@
         <v>0.51991454764453282</v>
       </c>
       <c r="AC46" s="346">
-        <v>656.14404192405846</v>
+        <f t="shared" si="3"/>
+        <v>362.06034664864831</v>
       </c>
       <c r="AD46" s="346">
-        <v>3057.5154266666691</v>
+        <f t="shared" si="2"/>
+        <v>2924.5799733333351</v>
       </c>
       <c r="AE46" s="346">
         <v>3000</v>
@@ -12480,10 +12561,12 @@
         <v>0.40732005815020078</v>
       </c>
       <c r="AC48" s="346">
-        <v>1234.3295877260889</v>
+        <f t="shared" si="3"/>
+        <v>1064.1299906341455</v>
       </c>
       <c r="AD48" s="346">
-        <v>1574.545174166667</v>
+        <f t="shared" ref="AD48:AD49" si="4">5.5*AA48</f>
+        <v>1506.0866883333333</v>
       </c>
       <c r="AE48" s="346">
         <v>1300</v>
@@ -12608,10 +12691,12 @@
         <v>0.26658730158730159</v>
       </c>
       <c r="AC49" s="346">
-        <v>282.613969916266</v>
+        <f t="shared" si="3"/>
+        <v>722.75461599999983</v>
       </c>
       <c r="AD49" s="346">
-        <v>502.1705</v>
+        <f t="shared" si="4"/>
+        <v>480.33699999999999</v>
       </c>
       <c r="AE49" s="346">
         <v>300</v>
@@ -12811,7 +12896,8 @@
         <v>0</v>
       </c>
       <c r="AD51" s="346">
-        <v>549.47276402500006</v>
+        <f t="shared" ref="AD51:AD54" si="5">5.5*AA51</f>
+        <v>525.58264384999995</v>
       </c>
       <c r="AE51" s="346">
         <v>100</v>
@@ -12936,10 +13022,12 @@
         <v>0.34685033992278969</v>
       </c>
       <c r="AC52" s="346">
-        <v>550.73944104309567</v>
+        <f t="shared" si="3"/>
+        <v>749.89095750000001</v>
       </c>
       <c r="AD52" s="346">
-        <v>712.51079000000027</v>
+        <f t="shared" si="5"/>
+        <v>681.53206000000057</v>
       </c>
       <c r="AE52" s="346">
         <v>700</v>
@@ -13064,10 +13152,12 @@
         <v>0.26936888354700861</v>
       </c>
       <c r="AC53" s="346">
-        <v>625.77696441188073</v>
+        <f t="shared" si="3"/>
+        <v>680.00452954838624</v>
       </c>
       <c r="AD53" s="346">
-        <v>579.89733249999995</v>
+        <f t="shared" si="5"/>
+        <v>554.68440499999997</v>
       </c>
       <c r="AE53" s="346">
         <v>650</v>
@@ -13192,10 +13282,12 @@
         <v>0.38943465624866708</v>
       </c>
       <c r="AC54" s="346">
-        <v>1039.194730798609</v>
+        <f t="shared" si="3"/>
+        <v>912.58466644444434</v>
       </c>
       <c r="AD54" s="346">
-        <v>711.83683250000036</v>
+        <f t="shared" si="5"/>
+        <v>680.88740500000051</v>
       </c>
       <c r="AE54" s="346">
         <v>1000</v>

--- a/data/CIM_Master_Data.xlsx
+++ b/data/CIM_Master_Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\calvi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23DEB04-C23B-4FE4-A844-05F2BECAF1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AAD9C610-09BC-4C65-B223-168A0EE5995A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,10 +31,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Selling Locations 6.9.26'!$A$5:$AX$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Site Info'!$B$3:$M$3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId11"/>
-    <pivotCache cacheId="7" r:id="rId12"/>
+    <pivotCache cacheId="1" r:id="rId11"/>
+    <pivotCache cacheId="2" r:id="rId12"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -2080,7 +2080,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="19">
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
@@ -2098,6 +2098,8 @@
     <numFmt numFmtId="174" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="175" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="0.00\x"/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.000_);_(&quot;$&quot;* \(#,##0.000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="23" x14ac:knownFonts="1">
     <font>
@@ -2629,7 +2631,7 @@
     <xf numFmtId="44" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="402">
+  <cellXfs count="405">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3659,6 +3661,9 @@
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -9193,7 +9198,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{427CD699-56F8-4E4F-AE38-516D87ACD995}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{427CD699-56F8-4E4F-AE38-516D87ACD995}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:R65" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="47">
     <pivotField showAll="0"/>
@@ -9993,7 +9998,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0800-000000000000}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0800-000000000000}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="AZ5:BD14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="40">
     <pivotField dataField="1" showAll="0">
@@ -10611,7 +10616,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AV54"/>
+  <dimension ref="A1:AV60"/>
   <sheetFormatPr defaultColWidth="7" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="345" bestFit="1" customWidth="1"/>
@@ -10625,11 +10630,13 @@
     <col min="20" max="20" width="7.42578125" style="337" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7.42578125" style="355" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="8.42578125" style="338" customWidth="1"/>
-    <col min="23" max="24" width="7.42578125" style="355" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.42578125" style="355" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9" style="355" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="7.42578125" style="337" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="7.42578125" style="355" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="7.42578125" style="337" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="7.42578125" style="355" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.5703125" style="355" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.140625" style="355" customWidth="1"/>
     <col min="30" max="30" width="7.7109375" style="337" customWidth="1"/>
     <col min="31" max="32" width="7.7109375" style="347" customWidth="1"/>
     <col min="33" max="33" width="9" style="378" customWidth="1"/>
@@ -10803,1179 +10810,1171 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:48" s="394" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="393">
+    <row r="3" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A3" s="345">
         <v>1001</v>
       </c>
-      <c r="B3" s="394" t="s">
+      <c r="B3" s="346" t="s">
         <v>111</v>
       </c>
-      <c r="C3" s="394" t="s">
+      <c r="C3" s="346" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="394" t="s">
+      <c r="D3" s="346" t="s">
         <v>113</v>
       </c>
-      <c r="E3" s="394" t="s">
+      <c r="E3" s="346" t="s">
         <v>112</v>
       </c>
-      <c r="F3" s="394" t="s">
+      <c r="F3" s="346" t="s">
         <v>89</v>
       </c>
-      <c r="G3" s="394" t="s">
+      <c r="G3" s="346" t="s">
         <v>90</v>
       </c>
-      <c r="H3" s="394" t="s">
+      <c r="H3" s="346" t="s">
         <v>90</v>
       </c>
-      <c r="I3" s="394" t="s">
+      <c r="I3" s="346" t="s">
         <v>91</v>
       </c>
-      <c r="J3" s="394" t="s">
+      <c r="J3" s="346" t="s">
         <v>83</v>
       </c>
-      <c r="K3" s="393">
+      <c r="K3" s="345">
         <v>2020</v>
       </c>
-      <c r="L3" s="395">
+      <c r="L3" s="347">
         <v>25</v>
       </c>
-      <c r="M3" s="395">
+      <c r="M3" s="347">
         <v>4510</v>
       </c>
-      <c r="N3" s="396">
+      <c r="N3" s="337">
         <v>0.96</v>
       </c>
-      <c r="O3" s="396">
+      <c r="O3" s="337">
         <v>1</v>
       </c>
-      <c r="P3" s="397">
+      <c r="P3" s="355">
         <v>312.63822000000005</v>
       </c>
-      <c r="Q3" s="397">
+      <c r="Q3" s="355">
         <v>60.784320000000037</v>
       </c>
-      <c r="R3" s="396">
-        <f>+Q3/P3</f>
+      <c r="R3" s="337">
+        <f t="shared" ref="R3:R4" si="0">+Q3/P3</f>
         <v>0.19442382956248927</v>
       </c>
-      <c r="S3" s="398">
+      <c r="S3" s="339">
         <v>0.96</v>
       </c>
-      <c r="T3" s="396">
+      <c r="T3" s="337">
         <v>0.99</v>
       </c>
-      <c r="U3" s="397">
+      <c r="U3" s="355">
         <v>273.57461587508465</v>
       </c>
-      <c r="V3" s="396">
+      <c r="V3" s="337">
         <v>0.96</v>
       </c>
-      <c r="W3" s="397">
+      <c r="W3" s="355">
         <v>335.87127050807959</v>
       </c>
-      <c r="X3" s="397">
+      <c r="X3" s="355">
         <v>81.654703143746673</v>
       </c>
-      <c r="Y3" s="396">
-        <f>+X3/W3</f>
+      <c r="Y3" s="337">
+        <f t="shared" ref="Y3:Y4" si="1">+X3/W3</f>
         <v>0.24311309216839497</v>
       </c>
-      <c r="Z3" s="397">
+      <c r="Z3" s="355">
         <v>286.85939922197878</v>
       </c>
-      <c r="AA3" s="396">
+      <c r="AA3" s="337">
         <v>0.96</v>
       </c>
-      <c r="AB3" s="397">
+      <c r="AB3" s="355">
         <v>358.00053022903001</v>
       </c>
-      <c r="AC3" s="397">
+      <c r="AC3" s="355">
         <v>105.996938716326</v>
       </c>
-      <c r="AD3" s="396">
-        <f>+AC3/AB3</f>
+      <c r="AD3" s="337">
+        <f t="shared" ref="AD3:AD4" si="2">+AC3/AB3</f>
         <v>0.29608039588241586</v>
       </c>
-      <c r="AE3" s="395">
-        <f>+MAX(0,X3*6)</f>
+      <c r="AE3" s="347">
+        <f t="shared" ref="AE3:AE4" si="3">+MAX(0,X3*6)</f>
         <v>489.92821886248004</v>
       </c>
-      <c r="AF3" s="395">
+      <c r="AF3" s="347">
         <v>500</v>
       </c>
-      <c r="AG3" s="395">
+      <c r="AG3" s="347">
         <v>500</v>
       </c>
-      <c r="AH3" s="399">
+      <c r="AH3" s="348">
         <v>43916</v>
       </c>
-      <c r="AI3" s="399" t="s">
+      <c r="AI3" s="348" t="s">
         <v>84</v>
       </c>
-      <c r="AJ3" s="400">
+      <c r="AJ3" s="349">
         <v>47938</v>
       </c>
-      <c r="AK3" s="400" t="s">
+      <c r="AK3" s="349" t="s">
         <v>56</v>
       </c>
-      <c r="AL3" s="400">
+      <c r="AL3" s="349">
         <v>49765</v>
       </c>
-      <c r="AM3" s="400">
+      <c r="AM3" s="349">
         <v>51591</v>
       </c>
-      <c r="AN3" s="395">
+      <c r="AN3" s="347">
         <v>110</v>
       </c>
-      <c r="AO3" s="395">
+      <c r="AO3" s="347">
         <v>74941</v>
       </c>
-      <c r="AP3" s="394" t="s">
+      <c r="AP3" s="346" t="s">
         <v>58</v>
       </c>
-      <c r="AQ3" s="394" t="s">
+      <c r="AQ3" s="346" t="s">
         <v>90</v>
       </c>
-      <c r="AR3" s="393" t="s">
+      <c r="AR3" s="345" t="s">
         <v>608</v>
       </c>
-      <c r="AS3" s="401"/>
-      <c r="AT3" s="401" t="s">
+      <c r="AT3" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="AU3" s="401" t="s">
+      <c r="AU3" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="AV3" s="401"/>
-    </row>
-    <row r="4" spans="1:48" s="394" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="393">
+      <c r="AV3" s="55"/>
+    </row>
+    <row r="4" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A4" s="345">
         <v>1002</v>
       </c>
-      <c r="B4" s="394" t="s">
+      <c r="B4" s="346" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="394" t="s">
+      <c r="C4" s="346" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="394" t="s">
+      <c r="D4" s="346" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="394" t="s">
+      <c r="E4" s="346" t="s">
         <v>87</v>
       </c>
-      <c r="F4" s="394" t="s">
+      <c r="F4" s="346" t="s">
         <v>89</v>
       </c>
-      <c r="G4" s="394" t="s">
+      <c r="G4" s="346" t="s">
         <v>90</v>
       </c>
-      <c r="H4" s="394" t="s">
+      <c r="H4" s="346" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="394" t="s">
+      <c r="I4" s="346" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="394" t="s">
+      <c r="J4" s="346" t="s">
         <v>83</v>
       </c>
-      <c r="K4" s="393">
+      <c r="K4" s="345">
         <v>2019</v>
       </c>
-      <c r="L4" s="395">
+      <c r="L4" s="347">
         <v>29</v>
       </c>
-      <c r="M4" s="395">
+      <c r="M4" s="347">
         <v>4980</v>
       </c>
-      <c r="N4" s="396">
+      <c r="N4" s="337">
         <v>0.93965517241379304</v>
       </c>
-      <c r="O4" s="396">
+      <c r="O4" s="337">
         <v>0.96551724137931039</v>
       </c>
-      <c r="P4" s="397">
+      <c r="P4" s="355">
         <v>354.17849999999999</v>
       </c>
-      <c r="Q4" s="397">
+      <c r="Q4" s="355">
         <v>94.131349999999969</v>
       </c>
-      <c r="R4" s="396">
-        <f>+Q4/P4</f>
+      <c r="R4" s="337">
+        <f t="shared" si="0"/>
         <v>0.26577375532393971</v>
       </c>
-      <c r="S4" s="398">
+      <c r="S4" s="339">
         <v>0.95689655172413801</v>
       </c>
-      <c r="T4" s="396">
+      <c r="T4" s="337">
         <v>0.96551724137931039</v>
       </c>
-      <c r="U4" s="397">
+      <c r="U4" s="355">
         <v>235.88473901286611</v>
       </c>
-      <c r="V4" s="396">
+      <c r="V4" s="337">
         <v>0.96551724137931039</v>
       </c>
-      <c r="W4" s="397">
+      <c r="W4" s="355">
         <v>350.05240563133901</v>
       </c>
-      <c r="X4" s="397">
+      <c r="X4" s="355">
         <v>84.017237257521231</v>
       </c>
-      <c r="Y4" s="396">
-        <f>+X4/W4</f>
+      <c r="Y4" s="337">
+        <f t="shared" si="1"/>
         <v>0.24001331202392814</v>
       </c>
-      <c r="Z4" s="397">
+      <c r="Z4" s="355">
         <v>251.70788730584917</v>
       </c>
-      <c r="AA4" s="396">
+      <c r="AA4" s="337">
         <v>0.96551724137931039</v>
       </c>
-      <c r="AB4" s="397">
+      <c r="AB4" s="355">
         <v>366.48668391731599</v>
       </c>
-      <c r="AC4" s="397">
+      <c r="AC4" s="355">
         <v>102.34813348945499</v>
       </c>
-      <c r="AD4" s="396">
-        <f>+AC4/AB4</f>
+      <c r="AD4" s="337">
+        <f t="shared" si="2"/>
         <v>0.27926835538872136</v>
       </c>
-      <c r="AE4" s="395">
-        <f>+MAX(0,X4*6)</f>
+      <c r="AE4" s="347">
+        <f t="shared" si="3"/>
         <v>504.10342354512738</v>
       </c>
-      <c r="AF4" s="395">
+      <c r="AF4" s="347">
         <v>550</v>
       </c>
-      <c r="AG4" s="395">
+      <c r="AG4" s="347">
         <v>500</v>
       </c>
-      <c r="AH4" s="399">
+      <c r="AH4" s="348">
         <v>43815</v>
       </c>
-      <c r="AI4" s="399" t="s">
+      <c r="AI4" s="348" t="s">
         <v>84</v>
       </c>
-      <c r="AJ4" s="400">
+      <c r="AJ4" s="349">
         <v>47938</v>
       </c>
-      <c r="AK4" s="400" t="s">
+      <c r="AK4" s="349" t="s">
         <v>92</v>
       </c>
-      <c r="AL4" s="400">
+      <c r="AL4" s="349">
         <v>49887</v>
       </c>
-      <c r="AM4" s="400">
+      <c r="AM4" s="349">
         <v>49887</v>
       </c>
-      <c r="AN4" s="395">
+      <c r="AN4" s="347">
         <v>147</v>
       </c>
-      <c r="AO4" s="395">
+      <c r="AO4" s="347">
         <v>73531</v>
       </c>
-      <c r="AP4" s="394" t="s">
+      <c r="AP4" s="346" t="s">
         <v>58</v>
       </c>
-      <c r="AQ4" s="394" t="s">
+      <c r="AQ4" s="346" t="s">
         <v>90</v>
       </c>
-      <c r="AR4" s="393" t="s">
+      <c r="AR4" s="345" t="s">
         <v>609</v>
       </c>
-      <c r="AS4" s="401"/>
-      <c r="AT4" s="401" t="s">
+      <c r="AT4" s="55" t="s">
         <v>93</v>
       </c>
-      <c r="AU4" s="401" t="s">
+      <c r="AU4" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="AV4" s="401"/>
-    </row>
-    <row r="5" spans="1:48" s="394" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="393">
+      <c r="AV4" s="55"/>
+    </row>
+    <row r="5" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A5" s="345">
+        <v>1502</v>
+      </c>
+      <c r="B5" s="346" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="346" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="346" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="346" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="346" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="346" t="s">
+        <v>457</v>
+      </c>
+      <c r="H5" s="346" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" s="346" t="s">
+        <v>70</v>
+      </c>
+      <c r="J5" s="346" t="s">
+        <v>71</v>
+      </c>
+      <c r="K5" s="345">
+        <v>2025</v>
+      </c>
+      <c r="L5" s="347">
+        <v>46</v>
+      </c>
+      <c r="M5" s="347">
+        <v>8170</v>
+      </c>
+      <c r="N5" s="337">
+        <v>0.96195652173913049</v>
+      </c>
+      <c r="O5" s="337">
+        <v>0.97826086956521741</v>
+      </c>
+      <c r="P5" s="355">
+        <v>644.61250999999993</v>
+      </c>
+      <c r="Q5" s="355">
+        <v>190.67070000000001</v>
+      </c>
+      <c r="R5" s="337">
+        <f t="shared" ref="R5:R11" si="4">+Q5/P5</f>
+        <v>0.2957911877943542</v>
+      </c>
+      <c r="S5" s="339">
+        <v>0.97282608695652173</v>
+      </c>
+      <c r="T5" s="337">
+        <v>0.97826086956521741</v>
+      </c>
+      <c r="U5" s="355">
+        <v>288.89277986946917</v>
+      </c>
+      <c r="V5" s="337">
+        <v>0.97826086956521741</v>
+      </c>
+      <c r="W5" s="355">
+        <v>658.17249816322953</v>
+      </c>
+      <c r="X5" s="355">
+        <v>225.0807381770706</v>
+      </c>
+      <c r="Y5" s="337">
+        <f t="shared" ref="Y5:Y11" si="5">+X5/W5</f>
+        <v>0.34197833972888009</v>
+      </c>
+      <c r="Z5" s="355">
+        <v>318.24428630420721</v>
+      </c>
+      <c r="AA5" s="337">
+        <v>0.97282608695652173</v>
+      </c>
+      <c r="AB5" s="355">
+        <v>744.69162995184502</v>
+      </c>
+      <c r="AC5" s="355">
+        <v>304.54606087606197</v>
+      </c>
+      <c r="AD5" s="337">
+        <f t="shared" ref="AD5:AD11" si="6">+AC5/AB5</f>
+        <v>0.40895593374099726</v>
+      </c>
+      <c r="AE5" s="347">
+        <f t="shared" ref="AE5:AE10" si="7">+MAX(0,X5*6)</f>
+        <v>1350.4844290624237</v>
+      </c>
+      <c r="AF5" s="347">
+        <f t="shared" ref="AF5:AF11" si="8">MAX(0,6.5*AC5)</f>
+        <v>1979.5493956944028</v>
+      </c>
+      <c r="AG5" s="347">
+        <v>1950</v>
+      </c>
+      <c r="AH5" s="348">
+        <v>44682</v>
+      </c>
+      <c r="AI5" s="348">
+        <v>45699</v>
+      </c>
+      <c r="AJ5" s="349">
+        <v>50282</v>
+      </c>
+      <c r="AK5" s="349" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL5" s="349" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM5" s="349" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN5" s="347">
+        <v>59</v>
+      </c>
+      <c r="AO5" s="347">
+        <v>115936</v>
+      </c>
+      <c r="AP5" s="346" t="s">
+        <v>58</v>
+      </c>
+      <c r="AQ5" s="346" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR5" s="345" t="s">
+        <v>610</v>
+      </c>
+      <c r="AT5" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU5" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV5" s="55"/>
+    </row>
+    <row r="6" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A6" s="345">
+        <v>1503</v>
+      </c>
+      <c r="B6" s="346" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="346" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="346" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="346" t="s">
+        <v>122</v>
+      </c>
+      <c r="F6" s="346" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="346" t="s">
+        <v>457</v>
+      </c>
+      <c r="H6" s="346" t="s">
+        <v>70</v>
+      </c>
+      <c r="I6" s="346" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" s="346" t="s">
+        <v>71</v>
+      </c>
+      <c r="K6" s="345">
+        <v>2025</v>
+      </c>
+      <c r="L6" s="347">
+        <v>43</v>
+      </c>
+      <c r="M6" s="347">
+        <v>10107</v>
+      </c>
+      <c r="N6" s="337">
+        <v>0.95930232558139528</v>
+      </c>
+      <c r="O6" s="337">
+        <v>0.97674418604651159</v>
+      </c>
+      <c r="P6" s="355">
+        <v>647.10768000000007</v>
+      </c>
+      <c r="Q6" s="355">
+        <v>136.72114000000002</v>
+      </c>
+      <c r="R6" s="337">
+        <f t="shared" si="4"/>
+        <v>0.21128035445352775</v>
+      </c>
+      <c r="S6" s="339">
+        <v>0.88372093023255816</v>
+      </c>
+      <c r="T6" s="337">
+        <v>0.95348837209302317</v>
+      </c>
+      <c r="U6" s="355">
+        <v>335.87021952038629</v>
+      </c>
+      <c r="V6" s="337">
+        <v>0.97674418604651159</v>
+      </c>
+      <c r="W6" s="355">
+        <v>686.01699365383888</v>
+      </c>
+      <c r="X6" s="355">
+        <v>177.39274865056595</v>
+      </c>
+      <c r="Y6" s="337">
+        <f t="shared" si="5"/>
+        <v>0.25858360695373317</v>
+      </c>
+      <c r="Z6" s="355">
+        <v>386.25075244844419</v>
+      </c>
+      <c r="AA6" s="337">
+        <v>0.97674418604651159</v>
+      </c>
+      <c r="AB6" s="355">
+        <v>843.57164334740196</v>
+      </c>
+      <c r="AC6" s="355">
+        <v>320.73852251134099</v>
+      </c>
+      <c r="AD6" s="337">
+        <f t="shared" si="6"/>
+        <v>0.38021491718072553</v>
+      </c>
+      <c r="AE6" s="347">
+        <f t="shared" si="7"/>
+        <v>1064.3564919033956</v>
+      </c>
+      <c r="AF6" s="347">
+        <f t="shared" si="8"/>
+        <v>2084.8003963237165</v>
+      </c>
+      <c r="AG6" s="347">
+        <v>2000</v>
+      </c>
+      <c r="AH6" s="348">
+        <v>45078</v>
+      </c>
+      <c r="AI6" s="348">
+        <v>45699</v>
+      </c>
+      <c r="AJ6" s="349">
+        <v>48699</v>
+      </c>
+      <c r="AK6" s="349" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL6" s="349">
+        <v>50525</v>
+      </c>
+      <c r="AM6" s="349">
+        <v>52351</v>
+      </c>
+      <c r="AN6" s="347">
+        <v>26</v>
+      </c>
+      <c r="AO6" s="347">
+        <v>30650</v>
+      </c>
+      <c r="AP6" s="346" t="s">
+        <v>58</v>
+      </c>
+      <c r="AQ6" s="346" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR6" s="345" t="s">
+        <v>611</v>
+      </c>
+      <c r="AT6" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU6" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV6" s="55"/>
+    </row>
+    <row r="7" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A7" s="345">
+        <v>1505</v>
+      </c>
+      <c r="B7" s="346" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="346" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" s="346" t="s">
+        <v>142</v>
+      </c>
+      <c r="E7" s="346" t="s">
+        <v>141</v>
+      </c>
+      <c r="F7" s="346" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="346" t="s">
+        <v>457</v>
+      </c>
+      <c r="H7" s="346" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" s="346" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" s="346" t="s">
+        <v>71</v>
+      </c>
+      <c r="K7" s="345">
+        <v>2025</v>
+      </c>
+      <c r="L7" s="347">
+        <v>45</v>
+      </c>
+      <c r="M7" s="347">
+        <v>9601</v>
+      </c>
+      <c r="N7" s="337">
+        <v>0.93902439024390238</v>
+      </c>
+      <c r="O7" s="337">
+        <v>0.96341463414634143</v>
+      </c>
+      <c r="P7" s="355">
+        <v>617.78498000000013</v>
+      </c>
+      <c r="Q7" s="355">
+        <v>166.82581000000022</v>
+      </c>
+      <c r="R7" s="337">
+        <f t="shared" si="4"/>
+        <v>0.27003863059279976</v>
+      </c>
+      <c r="S7" s="339">
+        <v>0.90853658536585369</v>
+      </c>
+      <c r="T7" s="337">
+        <v>0.92073170731707321</v>
+      </c>
+      <c r="U7" s="355">
+        <v>312.19319944501041</v>
+      </c>
+      <c r="V7" s="337">
+        <v>0.95121951219512191</v>
+      </c>
+      <c r="W7" s="355">
+        <v>634.51776189762973</v>
+      </c>
+      <c r="X7" s="355">
+        <v>174.45806888313868</v>
+      </c>
+      <c r="Y7" s="337">
+        <f t="shared" si="5"/>
+        <v>0.27494591855300177</v>
+      </c>
+      <c r="Z7" s="355">
+        <v>327.80285941726095</v>
+      </c>
+      <c r="AA7" s="337">
+        <v>0.97777777777777775</v>
+      </c>
+      <c r="AB7" s="355">
+        <v>750.01294234669297</v>
+      </c>
+      <c r="AC7" s="355">
+        <v>267.852012417803</v>
+      </c>
+      <c r="AD7" s="337">
+        <f t="shared" si="6"/>
+        <v>0.35712985375922829</v>
+      </c>
+      <c r="AE7" s="347">
+        <f t="shared" si="7"/>
+        <v>1046.748413298832</v>
+      </c>
+      <c r="AF7" s="347">
+        <f t="shared" si="8"/>
+        <v>1741.0380807157194</v>
+      </c>
+      <c r="AG7" s="347">
+        <v>1700</v>
+      </c>
+      <c r="AH7" s="348">
+        <v>45170</v>
+      </c>
+      <c r="AI7" s="348">
+        <v>45699</v>
+      </c>
+      <c r="AJ7" s="349">
+        <v>48791</v>
+      </c>
+      <c r="AK7" s="349" t="s">
+        <v>143</v>
+      </c>
+      <c r="AL7" s="349">
+        <v>52443</v>
+      </c>
+      <c r="AM7" s="349">
+        <v>56096</v>
+      </c>
+      <c r="AN7" s="347">
+        <v>79</v>
+      </c>
+      <c r="AO7" s="347">
+        <v>64654</v>
+      </c>
+      <c r="AP7" s="346" t="s">
+        <v>58</v>
+      </c>
+      <c r="AQ7" s="346" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR7" s="345" t="s">
+        <v>613</v>
+      </c>
+      <c r="AT7" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU7" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV7" s="55"/>
+    </row>
+    <row r="8" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A8" s="345">
+        <v>1504</v>
+      </c>
+      <c r="B8" s="346" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" s="346" t="s">
+        <v>182</v>
+      </c>
+      <c r="D8" s="346" t="s">
+        <v>183</v>
+      </c>
+      <c r="E8" s="346" t="s">
+        <v>182</v>
+      </c>
+      <c r="F8" s="346" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="346" t="s">
+        <v>457</v>
+      </c>
+      <c r="H8" s="346" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" s="346" t="s">
+        <v>70</v>
+      </c>
+      <c r="J8" s="346" t="s">
+        <v>71</v>
+      </c>
+      <c r="K8" s="345">
+        <v>2025</v>
+      </c>
+      <c r="L8" s="347">
+        <v>41</v>
+      </c>
+      <c r="M8" s="347">
+        <v>9000</v>
+      </c>
+      <c r="N8" s="337">
+        <v>0.82777777777777772</v>
+      </c>
+      <c r="O8" s="337">
+        <v>0.84444444444444444</v>
+      </c>
+      <c r="P8" s="355">
+        <v>596.33623999999998</v>
+      </c>
+      <c r="Q8" s="355">
+        <v>85.68689999999998</v>
+      </c>
+      <c r="R8" s="337">
+        <f t="shared" si="4"/>
+        <v>0.14368890275727664</v>
+      </c>
+      <c r="S8" s="339">
+        <v>0.85555555555555562</v>
+      </c>
+      <c r="T8" s="337">
+        <v>0.88888888888888895</v>
+      </c>
+      <c r="U8" s="355">
+        <v>296.37619984361851</v>
+      </c>
+      <c r="V8" s="337">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="W8" s="355">
+        <v>608.69598419173872</v>
+      </c>
+      <c r="X8" s="355">
+        <v>99.046665501800845</v>
+      </c>
+      <c r="Y8" s="337">
+        <f t="shared" si="5"/>
+        <v>0.16271943313922246</v>
+      </c>
+      <c r="Z8" s="355">
+        <v>326.0138198279804</v>
+      </c>
+      <c r="AA8" s="337">
+        <v>0.97560975609756095</v>
+      </c>
+      <c r="AB8" s="355">
+        <v>678.10874524219901</v>
+      </c>
+      <c r="AC8" s="355">
+        <v>154.34207003772701</v>
+      </c>
+      <c r="AD8" s="337">
+        <f t="shared" si="6"/>
+        <v>0.22760666503806981</v>
+      </c>
+      <c r="AE8" s="347">
+        <f t="shared" si="7"/>
+        <v>594.27999301080513</v>
+      </c>
+      <c r="AF8" s="347">
+        <f t="shared" si="8"/>
+        <v>1003.2234552452255</v>
+      </c>
+      <c r="AG8" s="347">
+        <v>1000</v>
+      </c>
+      <c r="AH8" s="348">
+        <v>45108</v>
+      </c>
+      <c r="AI8" s="348">
+        <v>45699</v>
+      </c>
+      <c r="AJ8" s="349">
+        <v>48822</v>
+      </c>
+      <c r="AK8" s="349" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL8" s="349">
+        <v>50648</v>
+      </c>
+      <c r="AM8" s="349">
+        <v>52474</v>
+      </c>
+      <c r="AN8" s="347">
+        <v>127</v>
+      </c>
+      <c r="AO8" s="347">
+        <v>92452</v>
+      </c>
+      <c r="AP8" s="346" t="s">
+        <v>58</v>
+      </c>
+      <c r="AQ8" s="346" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR8" s="345" t="s">
+        <v>612</v>
+      </c>
+      <c r="AT8" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU8" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV8" s="55"/>
+    </row>
+    <row r="9" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A9" s="345">
         <v>1003</v>
       </c>
-      <c r="B5" s="394" t="s">
+      <c r="B9" s="346" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="394" t="s">
+      <c r="C9" s="346" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="394" t="s">
+      <c r="D9" s="346" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="394" t="s">
+      <c r="E9" s="346" t="s">
         <v>96</v>
       </c>
-      <c r="F5" s="394" t="s">
+      <c r="F9" s="346" t="s">
         <v>69</v>
       </c>
-      <c r="G5" s="394" t="s">
+      <c r="G9" s="346" t="s">
         <v>457</v>
       </c>
-      <c r="H5" s="394" t="s">
+      <c r="H9" s="346" t="s">
         <v>70</v>
       </c>
-      <c r="I5" s="394" t="s">
+      <c r="I9" s="346" t="s">
         <v>70</v>
       </c>
-      <c r="J5" s="394" t="s">
+      <c r="J9" s="346" t="s">
         <v>55</v>
       </c>
-      <c r="K5" s="393">
+      <c r="K9" s="345">
         <v>2024</v>
       </c>
-      <c r="L5" s="395">
+      <c r="L9" s="347">
         <v>30</v>
       </c>
-      <c r="M5" s="395">
+      <c r="M9" s="347">
         <v>4952</v>
       </c>
-      <c r="N5" s="396">
+      <c r="N9" s="337">
         <v>0.91666666666666663</v>
       </c>
-      <c r="O5" s="396">
+      <c r="O9" s="337">
         <v>0.95000000000000007</v>
       </c>
-      <c r="P5" s="397">
+      <c r="P9" s="355">
         <v>332.07556999999997</v>
       </c>
-      <c r="Q5" s="397">
+      <c r="Q9" s="355">
         <v>76.200720000000018</v>
       </c>
-      <c r="R5" s="396">
-        <f>+Q5/P5</f>
+      <c r="R9" s="337">
+        <f t="shared" si="4"/>
         <v>0.22946800934498141</v>
       </c>
-      <c r="S5" s="398">
+      <c r="S9" s="339">
         <v>0.91666666666666663</v>
       </c>
-      <c r="T5" s="396">
+      <c r="T9" s="337">
         <v>0.93333333333333335</v>
       </c>
-      <c r="U5" s="397">
+      <c r="U9" s="355">
         <v>282.03532313346881</v>
       </c>
-      <c r="V5" s="396">
+      <c r="V9" s="337">
         <v>0.8</v>
       </c>
-      <c r="W5" s="397">
+      <c r="W9" s="355">
         <v>347.10960299200826</v>
       </c>
-      <c r="X5" s="397">
+      <c r="X9" s="355">
         <v>37.834514278302748</v>
       </c>
-      <c r="Y5" s="396">
-        <f>+X5/W5</f>
+      <c r="Y9" s="337">
+        <f t="shared" si="5"/>
         <v>0.10899875414617624</v>
       </c>
-      <c r="Z5" s="397">
+      <c r="Z9" s="355">
         <v>299.18307077998372</v>
       </c>
-      <c r="AA5" s="396">
+      <c r="AA9" s="337">
         <v>0.96666666666666667</v>
       </c>
-      <c r="AB5" s="397">
+      <c r="AB9" s="355">
         <v>451.16807073621499</v>
       </c>
-      <c r="AC5" s="397">
+      <c r="AC9" s="355">
         <v>131.560685302682</v>
       </c>
-      <c r="AD5" s="396">
-        <f>+AC5/AB5</f>
+      <c r="AD9" s="337">
+        <f t="shared" si="6"/>
         <v>0.29160016817679846</v>
       </c>
-      <c r="AE5" s="395">
-        <f>+MAX(0,X5*6)</f>
+      <c r="AE9" s="347">
+        <f t="shared" si="7"/>
         <v>227.00708566981649</v>
       </c>
-      <c r="AF5" s="395">
-        <f>MAX(0,6.5*AC5)</f>
+      <c r="AF9" s="347">
+        <f t="shared" si="8"/>
         <v>855.14445446743298</v>
       </c>
-      <c r="AG5" s="395">
+      <c r="AG9" s="347">
         <v>850</v>
       </c>
-      <c r="AH5" s="399">
+      <c r="AH9" s="348">
         <v>41153</v>
       </c>
-      <c r="AI5" s="399">
+      <c r="AI9" s="348">
         <v>45581</v>
       </c>
-      <c r="AJ5" s="400">
+      <c r="AJ9" s="349">
         <v>46752</v>
       </c>
-      <c r="AK5" s="400" t="s">
+      <c r="AK9" s="349" t="s">
         <v>56</v>
       </c>
-      <c r="AL5" s="400">
+      <c r="AL9" s="349">
         <v>48579</v>
       </c>
-      <c r="AM5" s="400">
+      <c r="AM9" s="349">
         <v>50405</v>
       </c>
-      <c r="AN5" s="395">
+      <c r="AN9" s="347">
         <v>105</v>
       </c>
-      <c r="AO5" s="395">
+      <c r="AO9" s="347">
         <v>86703</v>
       </c>
-      <c r="AP5" s="394" t="s">
+      <c r="AP9" s="346" t="s">
         <v>58</v>
       </c>
-      <c r="AQ5" s="394" t="s">
+      <c r="AQ9" s="346" t="s">
         <v>70</v>
       </c>
-      <c r="AR5" s="393" t="s">
+      <c r="AR9" s="345" t="s">
         <v>598</v>
       </c>
-      <c r="AS5" s="401"/>
-      <c r="AT5" s="401" t="s">
+      <c r="AT9" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="AU5" s="401" t="s">
+      <c r="AU9" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="AV5" s="401"/>
-    </row>
-    <row r="6" spans="1:48" s="394" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="393">
+      <c r="AV9" s="55"/>
+    </row>
+    <row r="10" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A10" s="345">
         <v>1501</v>
       </c>
-      <c r="B6" s="394" t="s">
+      <c r="B10" s="346" t="s">
         <v>162</v>
       </c>
-      <c r="C6" s="394" t="s">
+      <c r="C10" s="346" t="s">
         <v>163</v>
       </c>
-      <c r="D6" s="394" t="s">
+      <c r="D10" s="346" t="s">
         <v>164</v>
       </c>
-      <c r="E6" s="394" t="s">
+      <c r="E10" s="346" t="s">
         <v>163</v>
       </c>
-      <c r="F6" s="394" t="s">
+      <c r="F10" s="346" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="394" t="s">
+      <c r="G10" s="346" t="s">
         <v>457</v>
       </c>
-      <c r="H6" s="394" t="s">
+      <c r="H10" s="346" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="394" t="s">
+      <c r="I10" s="346" t="s">
         <v>70</v>
       </c>
-      <c r="J6" s="394" t="s">
+      <c r="J10" s="346" t="s">
         <v>71</v>
       </c>
-      <c r="K6" s="393">
+      <c r="K10" s="345">
         <v>2025</v>
       </c>
-      <c r="L6" s="395">
+      <c r="L10" s="347">
         <v>41</v>
       </c>
-      <c r="M6" s="395">
+      <c r="M10" s="347">
         <v>8000</v>
       </c>
-      <c r="N6" s="396">
+      <c r="N10" s="337">
         <v>0.82317073170731714</v>
       </c>
-      <c r="O6" s="396">
+      <c r="O10" s="337">
         <v>0.85365853658536583</v>
       </c>
-      <c r="P6" s="397">
+      <c r="P10" s="355">
         <v>493.80358999999993</v>
       </c>
-      <c r="Q6" s="397">
+      <c r="Q10" s="355">
         <v>30.45507999999991</v>
       </c>
-      <c r="R6" s="396">
-        <f>+Q6/P6</f>
+      <c r="R10" s="337">
+        <f t="shared" si="4"/>
         <v>6.1674480738384087E-2</v>
       </c>
-      <c r="S6" s="398">
+      <c r="S10" s="339">
         <v>0.76219512195121952</v>
       </c>
-      <c r="T6" s="396">
+      <c r="T10" s="337">
         <v>0.76219512195121952</v>
       </c>
-      <c r="U6" s="397">
+      <c r="U10" s="355">
         <v>264.71284136880638</v>
       </c>
-      <c r="V6" s="396">
+      <c r="V10" s="337">
         <v>0.90243902439024393</v>
       </c>
-      <c r="W6" s="397">
+      <c r="W10" s="355">
         <v>501.46945744489074</v>
       </c>
-      <c r="X6" s="397">
+      <c r="X10" s="355">
         <v>32.270722799909535</v>
       </c>
-      <c r="Y6" s="396">
-        <f>+X6/W6</f>
+      <c r="Y10" s="337">
+        <f t="shared" si="5"/>
         <v>6.4352319609526656E-2</v>
       </c>
-      <c r="Z6" s="397">
+      <c r="Z10" s="355">
         <v>304.41976757412732</v>
       </c>
-      <c r="AA6" s="396">
+      <c r="AA10" s="337">
         <v>0.97560975609756095</v>
       </c>
-      <c r="AB6" s="397">
+      <c r="AB10" s="355">
         <v>633.19311655418505</v>
       </c>
-      <c r="AC6" s="397">
+      <c r="AC10" s="355">
         <v>156.36892636546901</v>
       </c>
-      <c r="AD6" s="396">
-        <f>+AC6/AB6</f>
+      <c r="AD10" s="337">
+        <f t="shared" si="6"/>
         <v>0.24695297892122275</v>
       </c>
-      <c r="AE6" s="395">
-        <f>+MAX(0,X6*6)</f>
+      <c r="AE10" s="347">
+        <f t="shared" si="7"/>
         <v>193.62433679945721</v>
       </c>
-      <c r="AF6" s="395">
-        <f>MAX(0,6.5*AC6)</f>
+      <c r="AF10" s="347">
+        <f t="shared" si="8"/>
         <v>1016.3980213755485</v>
       </c>
-      <c r="AG6" s="395">
+      <c r="AG10" s="347">
         <v>1000</v>
       </c>
-      <c r="AH6" s="399">
+      <c r="AH10" s="348">
         <v>44228</v>
       </c>
-      <c r="AI6" s="399">
+      <c r="AI10" s="348">
         <v>45699</v>
       </c>
-      <c r="AJ6" s="400">
+      <c r="AJ10" s="349">
         <v>47299</v>
       </c>
-      <c r="AK6" s="400" t="s">
+      <c r="AK10" s="349" t="s">
         <v>56</v>
       </c>
-      <c r="AL6" s="400">
+      <c r="AL10" s="349">
         <v>49125</v>
       </c>
-      <c r="AM6" s="400">
+      <c r="AM10" s="349">
         <v>50951</v>
       </c>
-      <c r="AN6" s="395">
+      <c r="AN10" s="347">
         <v>123</v>
       </c>
-      <c r="AO6" s="395">
+      <c r="AO10" s="347">
         <v>75936</v>
       </c>
-      <c r="AP6" s="394" t="s">
+      <c r="AP10" s="346" t="s">
         <v>58</v>
       </c>
-      <c r="AQ6" s="394" t="s">
+      <c r="AQ10" s="346" t="s">
         <v>70</v>
       </c>
-      <c r="AR6" s="393" t="s">
+      <c r="AR10" s="345" t="s">
         <v>646</v>
       </c>
-      <c r="AS6" s="401"/>
-      <c r="AT6" s="401" t="s">
+      <c r="AT10" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="AU6" s="401" t="s">
+      <c r="AU10" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="AV6" s="401"/>
-    </row>
-    <row r="7" spans="1:48" s="394" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="393">
-        <v>1502</v>
-      </c>
-      <c r="B7" s="394" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="394" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="394" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="394" t="s">
-        <v>67</v>
-      </c>
-      <c r="F7" s="394" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="394" t="s">
-        <v>457</v>
-      </c>
-      <c r="H7" s="394" t="s">
-        <v>70</v>
-      </c>
-      <c r="I7" s="394" t="s">
-        <v>70</v>
-      </c>
-      <c r="J7" s="394" t="s">
-        <v>71</v>
-      </c>
-      <c r="K7" s="393">
-        <v>2025</v>
-      </c>
-      <c r="L7" s="395">
-        <v>46</v>
-      </c>
-      <c r="M7" s="395">
-        <v>8170</v>
-      </c>
-      <c r="N7" s="396">
-        <v>0.96195652173913049</v>
-      </c>
-      <c r="O7" s="396">
-        <v>0.97826086956521741</v>
-      </c>
-      <c r="P7" s="397">
-        <v>644.61250999999993</v>
-      </c>
-      <c r="Q7" s="397">
-        <v>190.67070000000001</v>
-      </c>
-      <c r="R7" s="396">
-        <f>+Q7/P7</f>
-        <v>0.2957911877943542</v>
-      </c>
-      <c r="S7" s="398">
-        <v>0.97282608695652173</v>
-      </c>
-      <c r="T7" s="396">
-        <v>0.97826086956521741</v>
-      </c>
-      <c r="U7" s="397">
-        <v>288.89277986946917</v>
-      </c>
-      <c r="V7" s="396">
-        <v>0.97826086956521741</v>
-      </c>
-      <c r="W7" s="397">
-        <v>658.17249816322953</v>
-      </c>
-      <c r="X7" s="397">
-        <v>225.0807381770706</v>
-      </c>
-      <c r="Y7" s="396">
-        <f>+X7/W7</f>
-        <v>0.34197833972888009</v>
-      </c>
-      <c r="Z7" s="397">
-        <v>318.24428630420721</v>
-      </c>
-      <c r="AA7" s="396">
-        <v>0.97282608695652173</v>
-      </c>
-      <c r="AB7" s="397">
-        <v>744.69162995184502</v>
-      </c>
-      <c r="AC7" s="397">
-        <v>304.54606087606197</v>
-      </c>
-      <c r="AD7" s="396">
-        <f>+AC7/AB7</f>
-        <v>0.40895593374099726</v>
-      </c>
-      <c r="AE7" s="395">
-        <f>+MAX(0,X7*6)</f>
-        <v>1350.4844290624237</v>
-      </c>
-      <c r="AF7" s="395">
-        <f>MAX(0,6.5*AC7)</f>
-        <v>1979.5493956944028</v>
-      </c>
-      <c r="AG7" s="395">
-        <v>1950</v>
-      </c>
-      <c r="AH7" s="399">
-        <v>44682</v>
-      </c>
-      <c r="AI7" s="399">
-        <v>45699</v>
-      </c>
-      <c r="AJ7" s="400">
-        <v>50282</v>
-      </c>
-      <c r="AK7" s="400" t="s">
-        <v>57</v>
-      </c>
-      <c r="AL7" s="400" t="s">
-        <v>57</v>
-      </c>
-      <c r="AM7" s="400" t="s">
-        <v>57</v>
-      </c>
-      <c r="AN7" s="395">
-        <v>59</v>
-      </c>
-      <c r="AO7" s="395">
-        <v>115936</v>
-      </c>
-      <c r="AP7" s="394" t="s">
-        <v>58</v>
-      </c>
-      <c r="AQ7" s="394" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR7" s="393" t="s">
-        <v>610</v>
-      </c>
-      <c r="AS7" s="401"/>
-      <c r="AT7" s="401" t="s">
-        <v>72</v>
-      </c>
-      <c r="AU7" s="401" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV7" s="401"/>
-    </row>
-    <row r="8" spans="1:48" s="394" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="393">
-        <v>1503</v>
-      </c>
-      <c r="B8" s="394" t="s">
-        <v>121</v>
-      </c>
-      <c r="C8" s="394" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" s="394" t="s">
-        <v>123</v>
-      </c>
-      <c r="E8" s="394" t="s">
-        <v>122</v>
-      </c>
-      <c r="F8" s="394" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="394" t="s">
-        <v>457</v>
-      </c>
-      <c r="H8" s="394" t="s">
-        <v>70</v>
-      </c>
-      <c r="I8" s="394" t="s">
-        <v>70</v>
-      </c>
-      <c r="J8" s="394" t="s">
-        <v>71</v>
-      </c>
-      <c r="K8" s="393">
-        <v>2025</v>
-      </c>
-      <c r="L8" s="395">
-        <v>43</v>
-      </c>
-      <c r="M8" s="395">
-        <v>10107</v>
-      </c>
-      <c r="N8" s="396">
-        <v>0.95930232558139528</v>
-      </c>
-      <c r="O8" s="396">
-        <v>0.97674418604651159</v>
-      </c>
-      <c r="P8" s="397">
-        <v>647.10768000000007</v>
-      </c>
-      <c r="Q8" s="397">
-        <v>136.72114000000002</v>
-      </c>
-      <c r="R8" s="396">
-        <f>+Q8/P8</f>
-        <v>0.21128035445352775</v>
-      </c>
-      <c r="S8" s="398">
-        <v>0.88372093023255816</v>
-      </c>
-      <c r="T8" s="396">
-        <v>0.95348837209302317</v>
-      </c>
-      <c r="U8" s="397">
-        <v>335.87021952038629</v>
-      </c>
-      <c r="V8" s="396">
-        <v>0.97674418604651159</v>
-      </c>
-      <c r="W8" s="397">
-        <v>686.01699365383888</v>
-      </c>
-      <c r="X8" s="397">
-        <v>177.39274865056595</v>
-      </c>
-      <c r="Y8" s="396">
-        <f>+X8/W8</f>
-        <v>0.25858360695373317</v>
-      </c>
-      <c r="Z8" s="397">
-        <v>386.25075244844419</v>
-      </c>
-      <c r="AA8" s="396">
-        <v>0.97674418604651159</v>
-      </c>
-      <c r="AB8" s="397">
-        <v>843.57164334740196</v>
-      </c>
-      <c r="AC8" s="397">
-        <v>320.73852251134099</v>
-      </c>
-      <c r="AD8" s="396">
-        <f>+AC8/AB8</f>
-        <v>0.38021491718072553</v>
-      </c>
-      <c r="AE8" s="395">
-        <f>+MAX(0,X8*6)</f>
-        <v>1064.3564919033956</v>
-      </c>
-      <c r="AF8" s="395">
-        <f>MAX(0,6.5*AC8)</f>
-        <v>2084.8003963237165</v>
-      </c>
-      <c r="AG8" s="395">
-        <v>2000</v>
-      </c>
-      <c r="AH8" s="399">
-        <v>45078</v>
-      </c>
-      <c r="AI8" s="399">
-        <v>45699</v>
-      </c>
-      <c r="AJ8" s="400">
-        <v>48699</v>
-      </c>
-      <c r="AK8" s="400" t="s">
-        <v>56</v>
-      </c>
-      <c r="AL8" s="400">
-        <v>50525</v>
-      </c>
-      <c r="AM8" s="400">
-        <v>52351</v>
-      </c>
-      <c r="AN8" s="395">
-        <v>26</v>
-      </c>
-      <c r="AO8" s="395">
-        <v>30650</v>
-      </c>
-      <c r="AP8" s="394" t="s">
-        <v>58</v>
-      </c>
-      <c r="AQ8" s="394" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR8" s="393" t="s">
-        <v>611</v>
-      </c>
-      <c r="AS8" s="401"/>
-      <c r="AT8" s="401" t="s">
-        <v>72</v>
-      </c>
-      <c r="AU8" s="401" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV8" s="401"/>
-    </row>
-    <row r="9" spans="1:48" s="394" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="393">
-        <v>1504</v>
-      </c>
-      <c r="B9" s="394" t="s">
-        <v>181</v>
-      </c>
-      <c r="C9" s="394" t="s">
-        <v>182</v>
-      </c>
-      <c r="D9" s="394" t="s">
-        <v>183</v>
-      </c>
-      <c r="E9" s="394" t="s">
-        <v>182</v>
-      </c>
-      <c r="F9" s="394" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="394" t="s">
-        <v>457</v>
-      </c>
-      <c r="H9" s="394" t="s">
-        <v>70</v>
-      </c>
-      <c r="I9" s="394" t="s">
-        <v>70</v>
-      </c>
-      <c r="J9" s="394" t="s">
-        <v>71</v>
-      </c>
-      <c r="K9" s="393">
-        <v>2025</v>
-      </c>
-      <c r="L9" s="395">
-        <v>41</v>
-      </c>
-      <c r="M9" s="395">
-        <v>9000</v>
-      </c>
-      <c r="N9" s="396">
-        <v>0.82777777777777772</v>
-      </c>
-      <c r="O9" s="396">
-        <v>0.84444444444444444</v>
-      </c>
-      <c r="P9" s="397">
-        <v>596.33623999999998</v>
-      </c>
-      <c r="Q9" s="397">
-        <v>85.68689999999998</v>
-      </c>
-      <c r="R9" s="396">
-        <f>+Q9/P9</f>
-        <v>0.14368890275727664</v>
-      </c>
-      <c r="S9" s="398">
-        <v>0.85555555555555562</v>
-      </c>
-      <c r="T9" s="396">
-        <v>0.88888888888888895</v>
-      </c>
-      <c r="U9" s="397">
-        <v>296.37619984361851</v>
-      </c>
-      <c r="V9" s="396">
-        <v>0.93333333333333335</v>
-      </c>
-      <c r="W9" s="397">
-        <v>608.69598419173872</v>
-      </c>
-      <c r="X9" s="397">
-        <v>99.046665501800845</v>
-      </c>
-      <c r="Y9" s="396">
-        <f>+X9/W9</f>
-        <v>0.16271943313922246</v>
-      </c>
-      <c r="Z9" s="397">
-        <v>326.0138198279804</v>
-      </c>
-      <c r="AA9" s="396">
-        <v>0.97560975609756095</v>
-      </c>
-      <c r="AB9" s="397">
-        <v>678.10874524219901</v>
-      </c>
-      <c r="AC9" s="397">
-        <v>154.34207003772701</v>
-      </c>
-      <c r="AD9" s="396">
-        <f>+AC9/AB9</f>
-        <v>0.22760666503806981</v>
-      </c>
-      <c r="AE9" s="395">
-        <f>+MAX(0,X9*6)</f>
-        <v>594.27999301080513</v>
-      </c>
-      <c r="AF9" s="395">
-        <f>MAX(0,6.5*AC9)</f>
-        <v>1003.2234552452255</v>
-      </c>
-      <c r="AG9" s="395">
-        <v>1000</v>
-      </c>
-      <c r="AH9" s="399">
-        <v>45108</v>
-      </c>
-      <c r="AI9" s="399">
-        <v>45699</v>
-      </c>
-      <c r="AJ9" s="400">
-        <v>48822</v>
-      </c>
-      <c r="AK9" s="400" t="s">
-        <v>56</v>
-      </c>
-      <c r="AL9" s="400">
-        <v>50648</v>
-      </c>
-      <c r="AM9" s="400">
-        <v>52474</v>
-      </c>
-      <c r="AN9" s="395">
-        <v>127</v>
-      </c>
-      <c r="AO9" s="395">
-        <v>92452</v>
-      </c>
-      <c r="AP9" s="394" t="s">
-        <v>58</v>
-      </c>
-      <c r="AQ9" s="394" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR9" s="393" t="s">
-        <v>612</v>
-      </c>
-      <c r="AS9" s="401"/>
-      <c r="AT9" s="401" t="s">
-        <v>72</v>
-      </c>
-      <c r="AU9" s="401" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV9" s="401"/>
-    </row>
-    <row r="10" spans="1:48" s="394" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="393">
-        <v>1505</v>
-      </c>
-      <c r="B10" s="394" t="s">
-        <v>140</v>
-      </c>
-      <c r="C10" s="394" t="s">
-        <v>141</v>
-      </c>
-      <c r="D10" s="394" t="s">
-        <v>142</v>
-      </c>
-      <c r="E10" s="394" t="s">
-        <v>141</v>
-      </c>
-      <c r="F10" s="394" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="394" t="s">
-        <v>457</v>
-      </c>
-      <c r="H10" s="394" t="s">
-        <v>70</v>
-      </c>
-      <c r="I10" s="394" t="s">
-        <v>70</v>
-      </c>
-      <c r="J10" s="394" t="s">
-        <v>71</v>
-      </c>
-      <c r="K10" s="393">
-        <v>2025</v>
-      </c>
-      <c r="L10" s="395">
-        <v>45</v>
-      </c>
-      <c r="M10" s="395">
-        <v>9601</v>
-      </c>
-      <c r="N10" s="396">
-        <v>0.93902439024390238</v>
-      </c>
-      <c r="O10" s="396">
-        <v>0.96341463414634143</v>
-      </c>
-      <c r="P10" s="397">
-        <v>617.78498000000013</v>
-      </c>
-      <c r="Q10" s="397">
-        <v>166.82581000000022</v>
-      </c>
-      <c r="R10" s="396">
-        <f>+Q10/P10</f>
-        <v>0.27003863059279976</v>
-      </c>
-      <c r="S10" s="398">
-        <v>0.90853658536585369</v>
-      </c>
-      <c r="T10" s="396">
-        <v>0.92073170731707321</v>
-      </c>
-      <c r="U10" s="397">
-        <v>312.19319944501041</v>
-      </c>
-      <c r="V10" s="396">
-        <v>0.95121951219512191</v>
-      </c>
-      <c r="W10" s="397">
-        <v>634.51776189762973</v>
-      </c>
-      <c r="X10" s="397">
-        <v>174.45806888313868</v>
-      </c>
-      <c r="Y10" s="396">
-        <f>+X10/W10</f>
-        <v>0.27494591855300177</v>
-      </c>
-      <c r="Z10" s="397">
-        <v>327.80285941726095</v>
-      </c>
-      <c r="AA10" s="396">
-        <v>0.97777777777777775</v>
-      </c>
-      <c r="AB10" s="397">
-        <v>750.01294234669297</v>
-      </c>
-      <c r="AC10" s="397">
-        <v>267.852012417803</v>
-      </c>
-      <c r="AD10" s="396">
-        <f>+AC10/AB10</f>
-        <v>0.35712985375922829</v>
-      </c>
-      <c r="AE10" s="395">
-        <f>+MAX(0,X10*6)</f>
-        <v>1046.748413298832</v>
-      </c>
-      <c r="AF10" s="395">
-        <f>MAX(0,6.5*AC10)</f>
-        <v>1741.0380807157194</v>
-      </c>
-      <c r="AG10" s="395">
-        <v>1700</v>
-      </c>
-      <c r="AH10" s="399">
-        <v>45170</v>
-      </c>
-      <c r="AI10" s="399">
-        <v>45699</v>
-      </c>
-      <c r="AJ10" s="400">
-        <v>48791</v>
-      </c>
-      <c r="AK10" s="400" t="s">
-        <v>143</v>
-      </c>
-      <c r="AL10" s="400">
-        <v>52443</v>
-      </c>
-      <c r="AM10" s="400">
-        <v>56096</v>
-      </c>
-      <c r="AN10" s="395">
-        <v>79</v>
-      </c>
-      <c r="AO10" s="395">
-        <v>64654</v>
-      </c>
-      <c r="AP10" s="394" t="s">
-        <v>58</v>
-      </c>
-      <c r="AQ10" s="394" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR10" s="393" t="s">
-        <v>613</v>
-      </c>
-      <c r="AS10" s="401"/>
-      <c r="AT10" s="401" t="s">
-        <v>72</v>
-      </c>
-      <c r="AU10" s="401" t="s">
-        <v>73</v>
-      </c>
-      <c r="AV10" s="401"/>
+      <c r="AV10" s="55"/>
     </row>
     <row r="11" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A11" s="345">
@@ -12030,7 +12029,7 @@
         <v>-41.192910000000069</v>
       </c>
       <c r="R11" s="337">
-        <f>+Q11/P11</f>
+        <f t="shared" si="4"/>
         <v>-8.4413442711820039E-2</v>
       </c>
       <c r="S11" s="339">
@@ -12052,27 +12051,27 @@
         <v>-16.589398666065577</v>
       </c>
       <c r="Y11" s="337">
-        <f>+X11/W11</f>
+        <f t="shared" si="5"/>
         <v>-3.2413478477515328E-2</v>
       </c>
-      <c r="Z11" s="397">
+      <c r="Z11" s="355">
         <v>292.81597390526167</v>
       </c>
-      <c r="AA11" s="396">
+      <c r="AA11" s="337">
         <v>0.967741935483871</v>
       </c>
       <c r="AB11" s="355">
         <v>913.58583858441602</v>
       </c>
-      <c r="AC11" s="397">
+      <c r="AC11" s="355">
         <v>387.61361013850001</v>
       </c>
-      <c r="AD11" s="396">
-        <f>+AC11/AB11</f>
+      <c r="AD11" s="337">
+        <f t="shared" si="6"/>
         <v>0.42427716561270257</v>
       </c>
       <c r="AF11" s="347">
-        <f>MAX(0,6.5*AC11)</f>
+        <f t="shared" si="8"/>
         <v>2519.48846590025</v>
       </c>
       <c r="AG11" s="347">
@@ -12271,7 +12270,7 @@
         <v>110.91195999999994</v>
       </c>
       <c r="R13" s="337">
-        <f>+Q13/P13</f>
+        <f t="shared" ref="R13:R22" si="9">+Q13/P13</f>
         <v>0.30667424283271177</v>
       </c>
       <c r="S13" s="339">
@@ -12293,10 +12292,10 @@
         <v>117.90195292262541</v>
       </c>
       <c r="Y13" s="337">
-        <f>+X13/W13</f>
+        <f t="shared" ref="Y13:Y22" si="10">+X13/W13</f>
         <v>0.32215815281108906</v>
       </c>
-      <c r="Z13" s="397">
+      <c r="Z13" s="355">
         <v>305.28650274629427</v>
       </c>
       <c r="AA13" s="337">
@@ -12309,7 +12308,7 @@
         <v>136.21564506956</v>
       </c>
       <c r="AD13" s="337">
-        <f>+AC13/AB13</f>
+        <f t="shared" ref="AD13:AD22" si="11">+AC13/AB13</f>
         <v>0.35752367207911168</v>
       </c>
       <c r="AE13" s="347">
@@ -12317,7 +12316,7 @@
         <v>707.41171753575247</v>
       </c>
       <c r="AF13" s="347">
-        <f>MAX(0,5.5*AC13)</f>
+        <f t="shared" ref="AF13:AF22" si="12">MAX(0,5.5*AC13)</f>
         <v>749.18604788257994</v>
       </c>
       <c r="AG13" s="347">
@@ -12415,7 +12414,7 @@
         <v>274.48518999999993</v>
       </c>
       <c r="R14" s="337">
-        <f>+Q14/P14</f>
+        <f t="shared" si="9"/>
         <v>0.33831503734946861</v>
       </c>
       <c r="S14" s="339">
@@ -12437,10 +12436,10 @@
         <v>288.75588666069871</v>
       </c>
       <c r="Y14" s="337">
-        <f>+X14/W14</f>
+        <f t="shared" si="10"/>
         <v>0.34590566340281104</v>
       </c>
-      <c r="Z14" s="397">
+      <c r="Z14" s="355">
         <v>333.69583971622819</v>
       </c>
       <c r="AA14" s="337">
@@ -12453,7 +12452,7 @@
         <v>370.04035999950798</v>
       </c>
       <c r="AD14" s="337">
-        <f>+AC14/AB14</f>
+        <f t="shared" si="11"/>
         <v>0.39491278973584104</v>
       </c>
       <c r="AE14" s="347">
@@ -12461,7 +12460,7 @@
         <v>1732.5353199641922</v>
       </c>
       <c r="AF14" s="347">
-        <f>MAX(0,5.5*AC14)</f>
+        <f t="shared" si="12"/>
         <v>2035.2219799972938</v>
       </c>
       <c r="AG14" s="347">
@@ -12559,7 +12558,7 @@
         <v>317.63765999999998</v>
       </c>
       <c r="R15" s="337">
-        <f>+Q15/P15</f>
+        <f t="shared" si="9"/>
         <v>0.38260285590009591</v>
       </c>
       <c r="S15" s="339">
@@ -12581,10 +12580,10 @@
         <v>337.24507485279298</v>
       </c>
       <c r="Y15" s="337">
-        <f>+X15/W15</f>
+        <f t="shared" si="10"/>
         <v>0.40455805506740522</v>
       </c>
-      <c r="Z15" s="397">
+      <c r="Z15" s="355">
         <v>389.78352605886118</v>
       </c>
       <c r="AA15" s="337">
@@ -12597,7 +12596,7 @@
         <v>388.55719385056801</v>
       </c>
       <c r="AD15" s="337">
-        <f>+AC15/AB15</f>
+        <f t="shared" si="11"/>
         <v>0.43568785494443191</v>
       </c>
       <c r="AE15" s="347">
@@ -12605,7 +12604,7 @@
         <v>2023.4704491167579</v>
       </c>
       <c r="AF15" s="347">
-        <f>MAX(0,5.5*AC15)</f>
+        <f t="shared" si="12"/>
         <v>2137.0645661781241</v>
       </c>
       <c r="AG15" s="347">
@@ -12703,7 +12702,7 @@
         <v>244.96443000000008</v>
       </c>
       <c r="R16" s="337">
-        <f>+Q16/P16</f>
+        <f t="shared" si="9"/>
         <v>0.36754171701594063</v>
       </c>
       <c r="S16" s="339">
@@ -12725,10 +12724,10 @@
         <v>291.8654406179374</v>
       </c>
       <c r="Y16" s="337">
-        <f>+X16/W16</f>
+        <f t="shared" si="10"/>
         <v>0.40090425903146326</v>
       </c>
-      <c r="Z16" s="397">
+      <c r="Z16" s="355">
         <v>318.29706364962749</v>
       </c>
       <c r="AA16" s="337">
@@ -12741,7 +12740,7 @@
         <v>351.86244945815702</v>
       </c>
       <c r="AD16" s="337">
-        <f>+AC16/AB16</f>
+        <f t="shared" si="11"/>
         <v>0.44288983071064719</v>
       </c>
       <c r="AE16" s="347">
@@ -12749,7 +12748,7 @@
         <v>1751.1926437076245</v>
       </c>
       <c r="AF16" s="347">
-        <f>MAX(0,5.5*AC16)</f>
+        <f t="shared" si="12"/>
         <v>1935.2434720198635</v>
       </c>
       <c r="AG16" s="347">
@@ -12847,7 +12846,7 @@
         <v>-43.469950000000061</v>
       </c>
       <c r="R17" s="337">
-        <f>+Q17/P17</f>
+        <f t="shared" si="9"/>
         <v>-0.15092500084715327</v>
       </c>
       <c r="S17" s="339">
@@ -12869,10 +12868,10 @@
         <v>-32.035423850441298</v>
       </c>
       <c r="Y17" s="337">
-        <f>+X17/W17</f>
+        <f t="shared" si="10"/>
         <v>-0.10093837295189111</v>
       </c>
-      <c r="Z17" s="397">
+      <c r="Z17" s="355">
         <v>282.22238843741468</v>
       </c>
       <c r="AA17" s="337">
@@ -12885,11 +12884,11 @@
         <v>115.134232303164</v>
       </c>
       <c r="AD17" s="337">
-        <f>+AC17/AB17</f>
+        <f t="shared" si="11"/>
         <v>0.24516568567642669</v>
       </c>
       <c r="AF17" s="347">
-        <f>MAX(0,5.5*AC17)</f>
+        <f t="shared" si="12"/>
         <v>633.23827766740203</v>
       </c>
       <c r="AG17" s="347">
@@ -12987,7 +12986,7 @@
         <v>-38.580869999999955</v>
       </c>
       <c r="R18" s="337">
-        <f>+Q18/P18</f>
+        <f t="shared" si="9"/>
         <v>-7.78637627999548E-2</v>
       </c>
       <c r="S18" s="339">
@@ -13009,10 +13008,10 @@
         <v>27.80742962143561</v>
       </c>
       <c r="Y18" s="337">
-        <f>+X18/W18</f>
+        <f t="shared" si="10"/>
         <v>4.9946360655553378E-2</v>
       </c>
-      <c r="Z18" s="397">
+      <c r="Z18" s="355">
         <v>513.96870135263202</v>
       </c>
       <c r="AA18" s="337">
@@ -13025,7 +13024,7 @@
         <v>155.52832997267501</v>
       </c>
       <c r="AD18" s="337">
-        <f>+AC18/AB18</f>
+        <f t="shared" si="11"/>
         <v>0.22381858412480221</v>
       </c>
       <c r="AE18" s="347">
@@ -13033,7 +13032,7 @@
         <v>166.84457772861367</v>
       </c>
       <c r="AF18" s="347">
-        <f>MAX(0,5.5*AC18)</f>
+        <f t="shared" si="12"/>
         <v>855.40581484971256</v>
       </c>
       <c r="AG18" s="347">
@@ -13131,7 +13130,7 @@
         <v>123.31277000000006</v>
       </c>
       <c r="R19" s="337">
-        <f>+Q19/P19</f>
+        <f t="shared" si="9"/>
         <v>0.33846752505731542</v>
       </c>
       <c r="S19" s="339">
@@ -13153,10 +13152,10 @@
         <v>108.67469226890299</v>
       </c>
       <c r="Y19" s="337">
-        <f>+X19/W19</f>
+        <f t="shared" si="10"/>
         <v>0.27648346407118712</v>
       </c>
-      <c r="Z19" s="397">
+      <c r="Z19" s="355">
         <v>373.54720206051189</v>
       </c>
       <c r="AA19" s="337">
@@ -13169,7 +13168,7 @@
         <v>139.41491039294101</v>
       </c>
       <c r="AD19" s="337">
-        <f>+AC19/AB19</f>
+        <f t="shared" si="11"/>
         <v>0.32624037803305089</v>
       </c>
       <c r="AE19" s="347">
@@ -13177,7 +13176,7 @@
         <v>652.04815361341798</v>
       </c>
       <c r="AF19" s="347">
-        <f>MAX(0,5.5*AC19)</f>
+        <f t="shared" si="12"/>
         <v>766.78200716117556</v>
       </c>
       <c r="AG19" s="347">
@@ -13275,7 +13274,7 @@
         <v>-1.6121900000000444</v>
       </c>
       <c r="R20" s="337">
-        <f>+Q20/P20</f>
+        <f t="shared" si="9"/>
         <v>-4.0445262910140372E-3</v>
       </c>
       <c r="S20" s="339">
@@ -13297,10 +13296,10 @@
         <v>2.8121415514645385</v>
       </c>
       <c r="Y20" s="337">
-        <f>+X20/W20</f>
+        <f t="shared" si="10"/>
         <v>6.828754602201067E-3</v>
       </c>
-      <c r="Z20" s="397">
+      <c r="Z20" s="355">
         <v>481.22802571208746</v>
       </c>
       <c r="AA20" s="337">
@@ -13313,11 +13312,11 @@
         <v>170.62360064231501</v>
       </c>
       <c r="AD20" s="337">
-        <f>+AC20/AB20</f>
+        <f t="shared" si="11"/>
         <v>0.29645379284726936</v>
       </c>
       <c r="AF20" s="347">
-        <f>MAX(0,5.5*AC20)</f>
+        <f t="shared" si="12"/>
         <v>938.42980353273254</v>
       </c>
       <c r="AG20" s="347">
@@ -13415,7 +13414,7 @@
         <v>15.257129999999933</v>
       </c>
       <c r="R21" s="337">
-        <f>+Q21/P21</f>
+        <f t="shared" si="9"/>
         <v>5.0722374610052197E-2</v>
       </c>
       <c r="S21" s="339">
@@ -13437,10 +13436,10 @@
         <v>53.26854273936771</v>
       </c>
       <c r="Y21" s="337">
-        <f>+X21/W21</f>
+        <f t="shared" si="10"/>
         <v>0.12664284481674562</v>
       </c>
-      <c r="Z21" s="397">
+      <c r="Z21" s="355">
         <v>355.58447723194053</v>
       </c>
       <c r="AA21" s="337">
@@ -13453,7 +13452,7 @@
         <v>113.440906057628</v>
       </c>
       <c r="AD21" s="337">
-        <f>+AC21/AB21</f>
+        <f t="shared" si="11"/>
         <v>0.23596641860725598</v>
       </c>
       <c r="AE21" s="347">
@@ -13461,7 +13460,7 @@
         <v>319.61125643620625</v>
       </c>
       <c r="AF21" s="347">
-        <f>MAX(0,5.5*AC21)</f>
+        <f t="shared" si="12"/>
         <v>623.92498331695401</v>
       </c>
       <c r="AG21" s="347">
@@ -13559,7 +13558,7 @@
         <v>-64.473790000000037</v>
       </c>
       <c r="R22" s="337">
-        <f>+Q22/P22</f>
+        <f t="shared" si="9"/>
         <v>-0.27237847119026637</v>
       </c>
       <c r="S22" s="339">
@@ -13581,10 +13580,10 @@
         <v>-73.93430905202149</v>
       </c>
       <c r="Y22" s="337">
-        <f>+X22/W22</f>
+        <f t="shared" si="10"/>
         <v>-0.21070168046912072</v>
       </c>
-      <c r="Z22" s="397">
+      <c r="Z22" s="355">
         <v>294.42000197784353</v>
       </c>
       <c r="AA22" s="337">
@@ -13597,11 +13596,11 @@
         <v>220.74620919195701</v>
       </c>
       <c r="AD22" s="337">
-        <f>+AC22/AB22</f>
+        <f t="shared" si="11"/>
         <v>0.36046458961856609</v>
       </c>
       <c r="AF22" s="347">
-        <f>MAX(0,5.5*AC22)</f>
+        <f t="shared" si="12"/>
         <v>1214.1041505557635</v>
       </c>
       <c r="AG22" s="347">
@@ -13794,7 +13793,7 @@
         <v>64.232309999999984</v>
       </c>
       <c r="R24" s="337">
-        <f>+Q24/P24</f>
+        <f t="shared" ref="R24:R31" si="13">+Q24/P24</f>
         <v>0.34636902326639313</v>
       </c>
       <c r="S24" s="339">
@@ -13816,10 +13815,10 @@
         <v>135.76963411367473</v>
       </c>
       <c r="Y24" s="337">
-        <f>+X24/W24</f>
+        <f t="shared" ref="Y24:Y32" si="14">+X24/W24</f>
         <v>0.4253627686670462</v>
       </c>
-      <c r="Z24" s="397">
+      <c r="Z24" s="355">
         <v>235.02619591540713</v>
       </c>
       <c r="AA24" s="337">
@@ -13832,15 +13831,15 @@
         <v>161.550871401065</v>
       </c>
       <c r="AD24" s="337">
-        <f>+AC24/AB24</f>
+        <f t="shared" ref="AD24:AD33" si="15">+AC24/AB24</f>
         <v>0.45581823187734433</v>
       </c>
       <c r="AE24" s="347">
-        <f>+MAX(0,X24*6)</f>
+        <f t="shared" ref="AE24:AE32" si="16">+MAX(0,X24*6)</f>
         <v>814.61780468204836</v>
       </c>
       <c r="AF24" s="347">
-        <f>MAX(0,5.5*AC24)</f>
+        <f t="shared" ref="AF24:AF33" si="17">MAX(0,5.5*AC24)</f>
         <v>888.52979270585752</v>
       </c>
       <c r="AG24" s="347">
@@ -13887,446 +13886,443 @@
       </c>
       <c r="AV24" s="55"/>
     </row>
-    <row r="25" spans="1:48" s="394" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="393">
+    <row r="25" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A25" s="345">
         <v>4000</v>
       </c>
-      <c r="B25" s="394" t="s">
+      <c r="B25" s="346" t="s">
         <v>153</v>
       </c>
-      <c r="C25" s="394" t="s">
+      <c r="C25" s="346" t="s">
         <v>154</v>
       </c>
-      <c r="D25" s="394" t="s">
+      <c r="D25" s="346" t="s">
         <v>155</v>
       </c>
-      <c r="E25" s="394" t="s">
+      <c r="E25" s="346" t="s">
         <v>154</v>
       </c>
-      <c r="F25" s="394" t="s">
+      <c r="F25" s="346" t="s">
         <v>156</v>
       </c>
-      <c r="G25" s="394" t="s">
+      <c r="G25" s="346" t="s">
         <v>457</v>
       </c>
-      <c r="H25" s="394" t="s">
+      <c r="H25" s="346" t="s">
         <v>90</v>
       </c>
-      <c r="I25" s="394" t="s">
+      <c r="I25" s="346" t="s">
         <v>91</v>
       </c>
-      <c r="J25" s="394" t="s">
+      <c r="J25" s="346" t="s">
         <v>55</v>
       </c>
-      <c r="K25" s="393">
+      <c r="K25" s="345">
         <v>2018</v>
       </c>
-      <c r="L25" s="395">
+      <c r="L25" s="347">
         <v>22</v>
       </c>
-      <c r="M25" s="395">
+      <c r="M25" s="347">
         <v>4108</v>
       </c>
-      <c r="N25" s="396">
+      <c r="N25" s="337">
         <v>0.97727272727272729</v>
       </c>
-      <c r="O25" s="396">
+      <c r="O25" s="337">
         <v>1</v>
       </c>
-      <c r="P25" s="397">
+      <c r="P25" s="355">
         <v>258.66017999999997</v>
       </c>
-      <c r="Q25" s="397">
+      <c r="Q25" s="355">
         <v>55.143849999999965</v>
       </c>
-      <c r="R25" s="396">
-        <f>+Q25/P25</f>
+      <c r="R25" s="337">
+        <f t="shared" si="13"/>
         <v>0.21319033335552451</v>
       </c>
-      <c r="S25" s="398">
+      <c r="S25" s="339">
         <v>0.88636363636363635</v>
       </c>
-      <c r="T25" s="396">
+      <c r="T25" s="337">
         <v>0.92045454545454541</v>
       </c>
-      <c r="U25" s="397">
+      <c r="U25" s="355">
         <v>237.4486589214556</v>
       </c>
-      <c r="V25" s="396">
+      <c r="V25" s="337">
         <v>1</v>
       </c>
-      <c r="W25" s="397">
+      <c r="W25" s="355">
         <v>269.9030158749643</v>
       </c>
-      <c r="X25" s="397">
+      <c r="X25" s="355">
         <v>74.625232722755669</v>
       </c>
-      <c r="Y25" s="396">
-        <f>+X25/W25</f>
+      <c r="Y25" s="337">
+        <f t="shared" si="14"/>
         <v>0.27648906582550625</v>
       </c>
-      <c r="Z25" s="397">
+      <c r="Z25" s="355">
         <v>249.32109186752839</v>
       </c>
-      <c r="AA25" s="396">
+      <c r="AA25" s="337">
         <v>1</v>
       </c>
-      <c r="AB25" s="397">
+      <c r="AB25" s="355">
         <v>285.22332909645201</v>
       </c>
-      <c r="AC25" s="397">
+      <c r="AC25" s="355">
         <v>93.670337440229403</v>
       </c>
-      <c r="AD25" s="396">
-        <f>+AC25/AB25</f>
+      <c r="AD25" s="337">
+        <f t="shared" si="15"/>
         <v>0.32841050462794913</v>
       </c>
-      <c r="AE25" s="395">
-        <f>+MAX(0,X25*6)</f>
+      <c r="AE25" s="347">
+        <f t="shared" si="16"/>
         <v>447.75139633653401</v>
       </c>
-      <c r="AF25" s="395">
-        <f>MAX(0,5.5*AC25)</f>
+      <c r="AF25" s="347">
+        <f t="shared" si="17"/>
         <v>515.18685592126167</v>
       </c>
-      <c r="AG25" s="395">
+      <c r="AG25" s="347">
         <v>500</v>
       </c>
-      <c r="AH25" s="399">
+      <c r="AH25" s="348">
         <v>42675</v>
       </c>
-      <c r="AI25" s="399">
+      <c r="AI25" s="348">
         <v>43405</v>
       </c>
-      <c r="AJ25" s="400">
+      <c r="AJ25" s="349">
         <v>48152</v>
       </c>
-      <c r="AK25" s="400" t="s">
+      <c r="AK25" s="349" t="s">
         <v>56</v>
       </c>
-      <c r="AL25" s="400">
+      <c r="AL25" s="349">
         <v>48152</v>
       </c>
-      <c r="AM25" s="400">
+      <c r="AM25" s="349">
         <v>51805</v>
       </c>
-      <c r="AN25" s="395">
+      <c r="AN25" s="347">
         <v>64</v>
       </c>
-      <c r="AO25" s="395">
+      <c r="AO25" s="347">
         <v>62899</v>
       </c>
-      <c r="AP25" s="394" t="s">
+      <c r="AP25" s="346" t="s">
         <v>58</v>
       </c>
-      <c r="AQ25" s="394" t="s">
+      <c r="AQ25" s="346" t="s">
         <v>90</v>
       </c>
-      <c r="AR25" s="393" t="s">
+      <c r="AR25" s="345" t="s">
         <v>623</v>
       </c>
-      <c r="AS25" s="401"/>
-      <c r="AT25" s="401" t="s">
+      <c r="AT25" s="55" t="s">
         <v>157</v>
       </c>
-      <c r="AU25" s="401" t="s">
+      <c r="AU25" s="55" t="s">
         <v>158</v>
       </c>
-      <c r="AV25" s="401"/>
-    </row>
-    <row r="26" spans="1:48" s="394" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="393">
+      <c r="AV25" s="55"/>
+    </row>
+    <row r="26" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A26" s="345">
         <v>5000</v>
       </c>
-      <c r="B26" s="394" t="s">
+      <c r="B26" s="346" t="s">
         <v>197</v>
       </c>
-      <c r="C26" s="394" t="s">
+      <c r="C26" s="346" t="s">
         <v>198</v>
       </c>
-      <c r="D26" s="394" t="s">
+      <c r="D26" s="346" t="s">
         <v>199</v>
       </c>
-      <c r="E26" s="394" t="s">
+      <c r="E26" s="346" t="s">
         <v>198</v>
       </c>
-      <c r="F26" s="394" t="s">
+      <c r="F26" s="346" t="s">
         <v>177</v>
       </c>
-      <c r="G26" s="394" t="s">
+      <c r="G26" s="346" t="s">
         <v>90</v>
       </c>
-      <c r="H26" s="394" t="s">
+      <c r="H26" s="346" t="s">
         <v>90</v>
       </c>
-      <c r="I26" s="394" t="s">
+      <c r="I26" s="346" t="s">
         <v>91</v>
       </c>
-      <c r="J26" s="394" t="s">
+      <c r="J26" s="346" t="s">
         <v>55</v>
       </c>
-      <c r="K26" s="393">
+      <c r="K26" s="345">
         <v>2018</v>
       </c>
-      <c r="L26" s="395">
+      <c r="L26" s="347">
         <v>26</v>
       </c>
-      <c r="M26" s="395">
+      <c r="M26" s="347">
         <v>4500</v>
       </c>
-      <c r="N26" s="396">
+      <c r="N26" s="337">
         <v>0.95192307692307698</v>
       </c>
-      <c r="O26" s="396">
+      <c r="O26" s="337">
         <v>0.98076923076923084</v>
       </c>
-      <c r="P26" s="397">
+      <c r="P26" s="355">
         <v>280.72868</v>
       </c>
-      <c r="Q26" s="397">
+      <c r="Q26" s="355">
         <v>20.956520000000019</v>
       </c>
-      <c r="R26" s="396">
-        <f>+Q26/P26</f>
+      <c r="R26" s="337">
+        <f t="shared" si="13"/>
         <v>7.4650441842992382E-2</v>
       </c>
-      <c r="S26" s="398">
+      <c r="S26" s="339">
+        <v>0.98076923076923095</v>
+      </c>
+      <c r="T26" s="337">
+        <v>1</v>
+      </c>
+      <c r="U26" s="355">
+        <v>250.16844216729828</v>
+      </c>
+      <c r="V26" s="337">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="W26" s="355">
+        <v>309.64521060777554</v>
+      </c>
+      <c r="X26" s="355">
+        <v>49.10866911318125</v>
+      </c>
+      <c r="Y26" s="337">
+        <f t="shared" si="14"/>
+        <v>0.1585965725637743</v>
+      </c>
+      <c r="Z26" s="355">
+        <v>262.82696534096362</v>
+      </c>
+      <c r="AA26" s="337">
         <v>0.98076923076923084</v>
       </c>
-      <c r="T26" s="396">
-        <v>1</v>
-      </c>
-      <c r="U26" s="397">
-        <v>250.16844216729828</v>
-      </c>
-      <c r="V26" s="396">
-        <v>0.92307692307692313</v>
-      </c>
-      <c r="W26" s="397">
-        <v>309.64521060777554</v>
-      </c>
-      <c r="X26" s="397">
-        <v>49.10866911318125</v>
-      </c>
-      <c r="Y26" s="396">
-        <f>+X26/W26</f>
-        <v>0.1585965725637743</v>
-      </c>
-      <c r="Z26" s="397">
-        <v>262.82696534096362</v>
-      </c>
-      <c r="AA26" s="396">
-        <v>0.98076923076923084</v>
-      </c>
-      <c r="AB26" s="397">
+      <c r="AB26" s="355">
         <v>355.342057140983</v>
       </c>
-      <c r="AC26" s="397">
+      <c r="AC26" s="355">
         <v>91.516802147155801</v>
       </c>
-      <c r="AD26" s="396">
-        <f>+AC26/AB26</f>
+      <c r="AD26" s="337">
+        <f t="shared" si="15"/>
         <v>0.25754565300680476</v>
       </c>
-      <c r="AE26" s="395">
-        <f>+MAX(0,X26*6)</f>
+      <c r="AE26" s="347">
+        <f t="shared" si="16"/>
         <v>294.65201467908753</v>
       </c>
-      <c r="AF26" s="395">
-        <f>MAX(0,5.5*AC26)</f>
+      <c r="AF26" s="347">
+        <f t="shared" si="17"/>
         <v>503.34241180935692</v>
       </c>
-      <c r="AG26" s="395">
+      <c r="AG26" s="347">
         <v>500</v>
       </c>
-      <c r="AH26" s="399">
+      <c r="AH26" s="348">
         <v>42884</v>
       </c>
-      <c r="AI26" s="399">
+      <c r="AI26" s="348">
         <v>43405</v>
       </c>
-      <c r="AJ26" s="400">
+      <c r="AJ26" s="349">
         <v>46507</v>
       </c>
-      <c r="AK26" s="400" t="s">
+      <c r="AK26" s="349" t="s">
         <v>56</v>
       </c>
-      <c r="AL26" s="400">
+      <c r="AL26" s="349">
         <v>48334</v>
       </c>
-      <c r="AM26" s="400">
+      <c r="AM26" s="349">
         <v>51986</v>
       </c>
-      <c r="AN26" s="395">
+      <c r="AN26" s="347">
         <v>60</v>
       </c>
-      <c r="AO26" s="395">
+      <c r="AO26" s="347">
         <v>66435</v>
       </c>
-      <c r="AP26" s="394" t="s">
+      <c r="AP26" s="346" t="s">
         <v>58</v>
       </c>
-      <c r="AQ26" s="394" t="s">
+      <c r="AQ26" s="346" t="s">
         <v>90</v>
       </c>
-      <c r="AR26" s="393" t="s">
+      <c r="AR26" s="345" t="s">
         <v>624</v>
       </c>
-      <c r="AS26" s="401"/>
-      <c r="AT26" s="401" t="s">
+      <c r="AT26" s="55" t="s">
         <v>157</v>
       </c>
-      <c r="AU26" s="401" t="s">
+      <c r="AU26" s="55" t="s">
         <v>158</v>
       </c>
-      <c r="AV26" s="401"/>
-    </row>
-    <row r="27" spans="1:48" s="394" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="393">
+      <c r="AV26" s="55"/>
+    </row>
+    <row r="27" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A27" s="345">
         <v>5001</v>
       </c>
-      <c r="B27" s="394" t="s">
+      <c r="B27" s="346" t="s">
         <v>174</v>
       </c>
-      <c r="C27" s="394" t="s">
+      <c r="C27" s="346" t="s">
         <v>175</v>
       </c>
-      <c r="D27" s="394" t="s">
+      <c r="D27" s="346" t="s">
         <v>176</v>
       </c>
-      <c r="E27" s="394" t="s">
+      <c r="E27" s="346" t="s">
         <v>175</v>
       </c>
-      <c r="F27" s="394" t="s">
+      <c r="F27" s="346" t="s">
         <v>177</v>
       </c>
-      <c r="G27" s="394" t="s">
+      <c r="G27" s="346" t="s">
         <v>90</v>
       </c>
-      <c r="H27" s="394" t="s">
+      <c r="H27" s="346" t="s">
         <v>90</v>
       </c>
-      <c r="I27" s="394" t="s">
+      <c r="I27" s="346" t="s">
         <v>91</v>
       </c>
-      <c r="J27" s="394" t="s">
+      <c r="J27" s="346" t="s">
         <v>55</v>
       </c>
-      <c r="K27" s="393">
+      <c r="K27" s="345">
         <v>2025</v>
       </c>
-      <c r="L27" s="395">
+      <c r="L27" s="347">
         <v>31</v>
       </c>
-      <c r="M27" s="395">
+      <c r="M27" s="347">
         <v>5604</v>
       </c>
-      <c r="N27" s="396">
+      <c r="N27" s="337">
         <v>0.79032258064516125</v>
       </c>
-      <c r="O27" s="396">
+      <c r="O27" s="337">
         <v>0.83870967741935487</v>
       </c>
-      <c r="P27" s="397">
+      <c r="P27" s="355">
         <v>351.19897000000003</v>
       </c>
-      <c r="Q27" s="397">
+      <c r="Q27" s="355">
         <v>61.764479999999949</v>
       </c>
-      <c r="R27" s="396">
-        <f>+Q27/P27</f>
+      <c r="R27" s="337">
+        <f t="shared" si="13"/>
         <v>0.17586748617172751</v>
       </c>
-      <c r="S27" s="398">
+      <c r="S27" s="339">
         <v>0.86290322580645162</v>
       </c>
-      <c r="T27" s="396">
+      <c r="T27" s="337">
         <v>0.89516129032258063</v>
       </c>
-      <c r="U27" s="397">
+      <c r="U27" s="355">
         <v>270.95533728376842</v>
       </c>
-      <c r="V27" s="396">
+      <c r="V27" s="337">
         <v>0.93548387096774188</v>
       </c>
-      <c r="W27" s="397">
+      <c r="W27" s="355">
         <v>359.83845476073049</v>
       </c>
-      <c r="X27" s="397">
+      <c r="X27" s="355">
         <v>62.96472001124306</v>
       </c>
-      <c r="Y27" s="396">
-        <f>+X27/W27</f>
+      <c r="Y27" s="337">
+        <f t="shared" si="14"/>
         <v>0.17498052022569563</v>
       </c>
-      <c r="Z27" s="397">
+      <c r="Z27" s="355">
         <v>281.90193291003266</v>
       </c>
-      <c r="AA27" s="396">
+      <c r="AA27" s="337">
         <v>0.967741935483871</v>
       </c>
-      <c r="AB27" s="397">
+      <c r="AB27" s="355">
         <v>439.76701533965098</v>
       </c>
-      <c r="AC27" s="397">
+      <c r="AC27" s="355">
         <v>144.42687141307599</v>
       </c>
-      <c r="AD27" s="396">
-        <f>+AC27/AB27</f>
+      <c r="AD27" s="337">
+        <f t="shared" si="15"/>
         <v>0.32841678974383492</v>
       </c>
-      <c r="AE27" s="395">
-        <f>+MAX(0,X27*6)</f>
+      <c r="AE27" s="347">
+        <f t="shared" si="16"/>
         <v>377.78832006745836</v>
       </c>
-      <c r="AF27" s="395">
-        <f>MAX(0,5.5*AC27)</f>
+      <c r="AF27" s="347">
+        <f t="shared" si="17"/>
         <v>794.34779277191797</v>
       </c>
-      <c r="AG27" s="395">
+      <c r="AG27" s="347">
         <v>600</v>
       </c>
-      <c r="AH27" s="399">
+      <c r="AH27" s="348">
         <v>43327</v>
       </c>
-      <c r="AI27" s="399">
+      <c r="AI27" s="348">
         <v>45700</v>
       </c>
-      <c r="AJ27" s="400">
+      <c r="AJ27" s="349">
         <v>46691</v>
       </c>
-      <c r="AK27" s="400" t="s">
+      <c r="AK27" s="349" t="s">
         <v>56</v>
       </c>
-      <c r="AL27" s="400">
+      <c r="AL27" s="349">
         <v>48518</v>
       </c>
-      <c r="AM27" s="400">
+      <c r="AM27" s="349">
         <v>50344</v>
       </c>
-      <c r="AN27" s="395">
+      <c r="AN27" s="347">
         <v>108</v>
       </c>
-      <c r="AO27" s="395">
+      <c r="AO27" s="347">
         <v>83058</v>
       </c>
-      <c r="AP27" s="394" t="s">
+      <c r="AP27" s="346" t="s">
         <v>58</v>
       </c>
-      <c r="AQ27" s="394" t="s">
+      <c r="AQ27" s="346" t="s">
         <v>90</v>
       </c>
-      <c r="AR27" s="393" t="s">
+      <c r="AR27" s="345" t="s">
         <v>625</v>
       </c>
-      <c r="AS27" s="401"/>
-      <c r="AT27" s="401" t="s">
+      <c r="AT27" s="55" t="s">
         <v>157</v>
       </c>
-      <c r="AU27" s="401" t="s">
+      <c r="AU27" s="55" t="s">
         <v>158</v>
       </c>
-      <c r="AV27" s="401"/>
+      <c r="AV27" s="55"/>
     </row>
     <row r="28" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A28" s="345">
@@ -14381,7 +14377,7 @@
         <v>27.428519999999949</v>
       </c>
       <c r="R28" s="337">
-        <f>+Q28/P28</f>
+        <f t="shared" si="13"/>
         <v>7.7460927071784091E-2</v>
       </c>
       <c r="S28" s="339">
@@ -14403,10 +14399,10 @@
         <v>40.789040361518069</v>
       </c>
       <c r="Y28" s="337">
-        <f>+X28/W28</f>
+        <f t="shared" si="14"/>
         <v>9.0659970823864691E-2</v>
       </c>
-      <c r="Z28" s="397">
+      <c r="Z28" s="355">
         <v>309.16529291363275</v>
       </c>
       <c r="AA28" s="337">
@@ -14419,15 +14415,15 @@
         <v>200.596862201721</v>
       </c>
       <c r="AD28" s="337">
-        <f>+AC28/AB28</f>
+        <f t="shared" si="15"/>
         <v>0.3199377239493304</v>
       </c>
       <c r="AE28" s="347">
-        <f>+MAX(0,X28*6)</f>
+        <f t="shared" si="16"/>
         <v>244.73424216910843</v>
       </c>
       <c r="AF28" s="347">
-        <f>MAX(0,5.5*AC28)</f>
+        <f t="shared" si="17"/>
         <v>1103.2827421094655</v>
       </c>
       <c r="AG28" s="347">
@@ -14530,7 +14526,7 @@
         <v>173.36428000000001</v>
       </c>
       <c r="R29" s="337">
-        <f>+Q29/P29</f>
+        <f t="shared" si="13"/>
         <v>0.29489083287049406</v>
       </c>
       <c r="S29" s="339">
@@ -14552,10 +14548,10 @@
         <v>159.1814976375918</v>
       </c>
       <c r="Y29" s="337">
-        <f>+X29/W29</f>
+        <f t="shared" si="14"/>
         <v>0.26917790045619083</v>
       </c>
-      <c r="Z29" s="397">
+      <c r="Z29" s="355">
         <v>336.75350682898971</v>
       </c>
       <c r="AA29" s="337">
@@ -14568,15 +14564,15 @@
         <v>191.42299232019101</v>
       </c>
       <c r="AD29" s="337">
-        <f>+AC29/AB29</f>
+        <f t="shared" si="15"/>
         <v>0.30365198844934843</v>
       </c>
       <c r="AE29" s="347">
-        <f>+MAX(0,X29*6)</f>
+        <f t="shared" si="16"/>
         <v>955.08898582555082</v>
       </c>
       <c r="AF29" s="347">
-        <f>MAX(0,5.5*AC29)</f>
+        <f t="shared" si="17"/>
         <v>1052.8264577610505</v>
       </c>
       <c r="AG29" s="347">
@@ -14676,7 +14672,7 @@
         <v>27.733659999999997</v>
       </c>
       <c r="R30" s="337">
-        <f>+Q30/P30</f>
+        <f t="shared" si="13"/>
         <v>9.8132317487096846E-2</v>
       </c>
       <c r="S30" s="339">
@@ -14698,10 +14694,10 @@
         <v>41.639574351433055</v>
       </c>
       <c r="Y30" s="337">
-        <f>+X30/W30</f>
+        <f t="shared" si="14"/>
         <v>0.13623980316305873</v>
       </c>
-      <c r="Z30" s="397">
+      <c r="Z30" s="355">
         <v>240.16969786837666</v>
       </c>
       <c r="AA30" s="337">
@@ -14714,15 +14710,15 @@
         <v>101.280623812933</v>
       </c>
       <c r="AD30" s="337">
-        <f>+AC30/AB30</f>
+        <f t="shared" si="15"/>
         <v>0.27964484270363432</v>
       </c>
       <c r="AE30" s="347">
-        <f>+MAX(0,X30*6)</f>
+        <f t="shared" si="16"/>
         <v>249.83744610859833</v>
       </c>
       <c r="AF30" s="347">
-        <f>MAX(0,5.5*AC30)</f>
+        <f t="shared" si="17"/>
         <v>557.04343097113156</v>
       </c>
       <c r="AG30" s="347">
@@ -14822,7 +14818,7 @@
         <v>94.197850000000045</v>
       </c>
       <c r="R31" s="337">
-        <f>+Q31/P31</f>
+        <f t="shared" si="13"/>
         <v>0.21610300043611599</v>
       </c>
       <c r="S31" s="339">
@@ -14844,10 +14840,10 @@
         <v>138.55175399217552</v>
       </c>
       <c r="Y31" s="337">
-        <f>+X31/W31</f>
+        <f t="shared" si="14"/>
         <v>0.28608335726645728</v>
       </c>
-      <c r="Z31" s="397">
+      <c r="Z31" s="355">
         <v>281.66412488285738</v>
       </c>
       <c r="AA31" s="337">
@@ -14860,15 +14856,15 @@
         <v>245.55179361774799</v>
       </c>
       <c r="AD31" s="337">
-        <f>+AC31/AB31</f>
+        <f t="shared" si="15"/>
         <v>0.4089068400111347</v>
       </c>
       <c r="AE31" s="347">
-        <f>+MAX(0,X31*6)</f>
+        <f t="shared" si="16"/>
         <v>831.31052395305312</v>
       </c>
       <c r="AF31" s="347">
-        <f>MAX(0,5.5*AC31)</f>
+        <f t="shared" si="17"/>
         <v>1350.5348648976139</v>
       </c>
       <c r="AG31" s="347">
@@ -14915,195 +14911,253 @@
       </c>
       <c r="AV31" s="55"/>
     </row>
-    <row r="32" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A32" s="350">
+    <row r="32" spans="1:48" s="397" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="396">
         <v>6501</v>
       </c>
-      <c r="B32" s="351" t="s">
+      <c r="B32" s="397" t="s">
         <v>247</v>
       </c>
-      <c r="C32" s="351" t="s">
+      <c r="C32" s="397" t="s">
         <v>248</v>
       </c>
-      <c r="D32" s="351" t="s">
+      <c r="D32" s="397" t="s">
         <v>249</v>
       </c>
-      <c r="E32" s="351" t="s">
+      <c r="E32" s="397" t="s">
         <v>248</v>
       </c>
-      <c r="F32" s="351" t="s">
+      <c r="F32" s="397" t="s">
         <v>250</v>
       </c>
-      <c r="G32" s="351" t="s">
+      <c r="G32" s="397" t="s">
         <v>457</v>
       </c>
-      <c r="H32" s="351" t="s">
+      <c r="H32" s="397" t="s">
         <v>251</v>
       </c>
-      <c r="I32" s="351" t="s">
+      <c r="I32" s="397" t="s">
         <v>252</v>
       </c>
-      <c r="J32" s="351" t="s">
+      <c r="J32" s="397" t="s">
         <v>55</v>
       </c>
-      <c r="K32" s="350">
+      <c r="K32" s="396">
         <v>2026</v>
       </c>
-      <c r="L32" s="352">
+      <c r="L32" s="398">
         <v>32</v>
       </c>
-      <c r="M32" s="352">
+      <c r="M32" s="398">
         <v>5906</v>
       </c>
-      <c r="N32" s="340"/>
-      <c r="O32" s="340"/>
-      <c r="P32" s="361"/>
-      <c r="Q32" s="361"/>
-      <c r="R32" s="340"/>
-      <c r="S32" s="341"/>
-      <c r="T32" s="340"/>
-      <c r="U32" s="361"/>
-      <c r="V32" s="340"/>
-      <c r="W32" s="361"/>
-      <c r="X32" s="361"/>
-      <c r="Y32" s="340"/>
-      <c r="Z32" s="361"/>
-      <c r="AA32" s="340"/>
-      <c r="AB32" s="361"/>
-      <c r="AC32" s="361"/>
-      <c r="AD32" s="340"/>
-      <c r="AE32" s="352"/>
-      <c r="AF32" s="352"/>
-      <c r="AG32" s="352"/>
-      <c r="AH32" s="353">
+      <c r="N32" s="399"/>
+      <c r="O32" s="399"/>
+      <c r="P32" s="400"/>
+      <c r="Q32" s="400"/>
+      <c r="R32" s="399"/>
+      <c r="S32" s="401">
+        <v>0.59375</v>
+      </c>
+      <c r="T32" s="399">
+        <v>0.65625</v>
+      </c>
+      <c r="U32" s="400">
+        <v>280</v>
+      </c>
+      <c r="V32" s="399"/>
+      <c r="W32" s="400"/>
+      <c r="X32" s="400"/>
+      <c r="Y32" s="399"/>
+      <c r="Z32" s="400">
+        <f>+U32*1.05</f>
+        <v>294</v>
+      </c>
+      <c r="AA32" s="399">
+        <f>31/L32</f>
+        <v>0.96875</v>
+      </c>
+      <c r="AB32" s="400">
+        <f>+ROUND(AA32*L32,0)*Z32*52/1000</f>
+        <v>473.928</v>
+      </c>
+      <c r="AC32" s="400">
+        <v>110.86499999999999</v>
+      </c>
+      <c r="AD32" s="399">
+        <f t="shared" si="15"/>
+        <v>0.23392793842102597</v>
+      </c>
+      <c r="AE32" s="398"/>
+      <c r="AF32" s="398">
+        <f t="shared" si="17"/>
+        <v>609.75749999999994</v>
+      </c>
+      <c r="AG32" s="398">
+        <v>250</v>
+      </c>
+      <c r="AH32" s="402">
         <v>42856</v>
       </c>
-      <c r="AI32" s="353">
+      <c r="AI32" s="402">
         <v>46085</v>
       </c>
-      <c r="AJ32" s="354">
+      <c r="AJ32" s="403">
         <v>49738</v>
       </c>
-      <c r="AK32" s="354" t="s">
+      <c r="AK32" s="403" t="s">
         <v>92</v>
       </c>
-      <c r="AL32" s="354">
+      <c r="AL32" s="403">
         <v>51564</v>
       </c>
-      <c r="AM32" s="354" t="s">
+      <c r="AM32" s="403" t="s">
         <v>57</v>
       </c>
-      <c r="AN32" s="352"/>
-      <c r="AO32" s="352"/>
-      <c r="AP32" s="351" t="s">
+      <c r="AN32" s="398">
+        <v>153</v>
+      </c>
+      <c r="AO32" s="398">
+        <v>86000</v>
+      </c>
+      <c r="AP32" s="397" t="s">
         <v>58</v>
       </c>
-      <c r="AQ32" s="351" t="s">
+      <c r="AQ32" s="397" t="s">
         <v>253</v>
       </c>
-      <c r="AR32" s="350" t="s">
+      <c r="AR32" s="396" t="s">
         <v>603</v>
       </c>
-      <c r="AT32" s="55" t="s">
+      <c r="AS32" s="404"/>
+      <c r="AT32" s="404" t="s">
         <v>372</v>
       </c>
-      <c r="AU32" s="55"/>
-      <c r="AV32" s="55"/>
-    </row>
-    <row r="33" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A33" s="350">
+      <c r="AU32" s="404"/>
+      <c r="AV32" s="404"/>
+    </row>
+    <row r="33" spans="1:48" s="397" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="396">
         <v>6502</v>
       </c>
-      <c r="B33" s="351" t="s">
+      <c r="B33" s="397" t="s">
         <v>254</v>
       </c>
-      <c r="C33" s="351" t="s">
+      <c r="C33" s="397" t="s">
         <v>255</v>
       </c>
-      <c r="D33" s="351" t="s">
+      <c r="D33" s="397" t="s">
         <v>256</v>
       </c>
-      <c r="E33" s="351" t="s">
+      <c r="E33" s="397" t="s">
         <v>255</v>
       </c>
-      <c r="F33" s="351" t="s">
+      <c r="F33" s="397" t="s">
         <v>250</v>
       </c>
-      <c r="G33" s="351" t="s">
+      <c r="G33" s="397" t="s">
         <v>457</v>
       </c>
-      <c r="H33" s="351" t="s">
+      <c r="H33" s="397" t="s">
         <v>251</v>
       </c>
-      <c r="I33" s="351" t="s">
+      <c r="I33" s="397" t="s">
         <v>252</v>
       </c>
-      <c r="J33" s="351" t="s">
+      <c r="J33" s="397" t="s">
         <v>55</v>
       </c>
-      <c r="K33" s="350">
+      <c r="K33" s="396">
         <v>2026</v>
       </c>
-      <c r="L33" s="352">
+      <c r="L33" s="398">
         <v>29</v>
       </c>
-      <c r="M33" s="352">
+      <c r="M33" s="398">
         <v>4845</v>
       </c>
-      <c r="N33" s="340"/>
-      <c r="O33" s="340"/>
-      <c r="P33" s="361"/>
-      <c r="Q33" s="361"/>
-      <c r="R33" s="340"/>
-      <c r="S33" s="341"/>
-      <c r="T33" s="340"/>
-      <c r="U33" s="361"/>
-      <c r="V33" s="340"/>
-      <c r="W33" s="361"/>
-      <c r="X33" s="361"/>
-      <c r="Y33" s="340"/>
-      <c r="Z33" s="361"/>
-      <c r="AA33" s="340"/>
-      <c r="AB33" s="361"/>
-      <c r="AC33" s="361"/>
-      <c r="AD33" s="340"/>
-      <c r="AE33" s="352"/>
-      <c r="AF33" s="352"/>
-      <c r="AG33" s="352"/>
-      <c r="AH33" s="353">
+      <c r="N33" s="399"/>
+      <c r="O33" s="399"/>
+      <c r="P33" s="400"/>
+      <c r="Q33" s="400"/>
+      <c r="R33" s="399"/>
+      <c r="S33" s="401">
+        <v>0.55172413793103448</v>
+      </c>
+      <c r="T33" s="399">
+        <v>0.62068965517241381</v>
+      </c>
+      <c r="U33" s="400">
+        <v>218</v>
+      </c>
+      <c r="V33" s="399"/>
+      <c r="W33" s="400"/>
+      <c r="X33" s="400"/>
+      <c r="Y33" s="399"/>
+      <c r="Z33" s="400">
+        <v>239.55175455507697</v>
+      </c>
+      <c r="AA33" s="399">
+        <v>0.96551724137931039</v>
+      </c>
+      <c r="AB33" s="400">
+        <f>+ROUND(AA33*L33,0)*Z33*52/1000</f>
+        <v>348.78735463219203</v>
+      </c>
+      <c r="AC33" s="400">
+        <v>111.65</v>
+      </c>
+      <c r="AD33" s="399">
+        <f t="shared" si="15"/>
+        <v>0.32010908227375007</v>
+      </c>
+      <c r="AE33" s="398"/>
+      <c r="AF33" s="398">
+        <f t="shared" si="17"/>
+        <v>614.07500000000005</v>
+      </c>
+      <c r="AG33" s="398">
+        <v>250</v>
+      </c>
+      <c r="AH33" s="402">
         <v>42795</v>
       </c>
-      <c r="AI33" s="353">
+      <c r="AI33" s="402">
         <v>46174</v>
       </c>
-      <c r="AJ33" s="354">
+      <c r="AJ33" s="403">
         <v>49979</v>
       </c>
-      <c r="AK33" s="354" t="s">
+      <c r="AK33" s="403" t="s">
         <v>92</v>
       </c>
-      <c r="AL33" s="354">
+      <c r="AL33" s="403">
         <v>51805</v>
       </c>
-      <c r="AM33" s="354" t="s">
+      <c r="AM33" s="403" t="s">
         <v>57</v>
       </c>
-      <c r="AN33" s="352"/>
-      <c r="AO33" s="352"/>
-      <c r="AP33" s="351" t="s">
+      <c r="AN33" s="398">
+        <v>192</v>
+      </c>
+      <c r="AO33" s="398">
+        <v>93000</v>
+      </c>
+      <c r="AP33" s="397" t="s">
         <v>58</v>
       </c>
-      <c r="AQ33" s="351" t="s">
+      <c r="AQ33" s="397" t="s">
         <v>253</v>
       </c>
-      <c r="AR33" s="350" t="s">
+      <c r="AR33" s="396" t="s">
         <v>604</v>
       </c>
-      <c r="AT33" s="55" t="s">
+      <c r="AS33" s="404"/>
+      <c r="AT33" s="404" t="s">
         <v>372</v>
       </c>
-      <c r="AU33" s="55"/>
-      <c r="AV33" s="55"/>
+      <c r="AU33" s="404"/>
+      <c r="AV33" s="404"/>
     </row>
     <row r="34" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A34" s="345">
@@ -15158,7 +15212,7 @@
         <v>31.259739999999965</v>
       </c>
       <c r="R34" s="337">
-        <f>+Q34/P34</f>
+        <f t="shared" ref="R34:R54" si="18">+Q34/P34</f>
         <v>8.3614826888451538E-2</v>
       </c>
       <c r="S34" s="339">
@@ -15180,10 +15234,10 @@
         <v>51.370832415500047</v>
       </c>
       <c r="Y34" s="337">
-        <f>+X34/W34</f>
+        <f t="shared" ref="Y34:Y54" si="19">+X34/W34</f>
         <v>0.13190527019811712</v>
       </c>
-      <c r="Z34" s="397">
+      <c r="Z34" s="355">
         <v>312.19455131322053</v>
       </c>
       <c r="AA34" s="337">
@@ -15196,7 +15250,7 @@
         <v>141.38163792655601</v>
       </c>
       <c r="AD34" s="337">
-        <f>+AC34/AB34</f>
+        <f t="shared" ref="AD34:AD54" si="20">+AC34/AB34</f>
         <v>0.29029736329446237</v>
       </c>
       <c r="AE34" s="347">
@@ -15204,7 +15258,7 @@
         <v>308.22499449300028</v>
       </c>
       <c r="AF34" s="347">
-        <f>MAX(0,5.5*AC34)</f>
+        <f t="shared" ref="AF34:AF54" si="21">MAX(0,5.5*AC34)</f>
         <v>777.59900859605807</v>
       </c>
       <c r="AG34" s="347">
@@ -15304,7 +15358,7 @@
         <v>37.655499999999975</v>
       </c>
       <c r="R35" s="337">
-        <f>+Q35/P35</f>
+        <f t="shared" si="18"/>
         <v>0.13330842440703755</v>
       </c>
       <c r="S35" s="339">
@@ -15326,10 +15380,10 @@
         <v>47.174123064419788</v>
       </c>
       <c r="Y35" s="337">
-        <f>+X35/W35</f>
+        <f t="shared" si="19"/>
         <v>0.16594032882996435</v>
       </c>
-      <c r="Z35" s="397">
+      <c r="Z35" s="355">
         <v>324.02417240367981</v>
       </c>
       <c r="AA35" s="337">
@@ -15342,7 +15396,7 @@
         <v>114.467543913847</v>
       </c>
       <c r="AD35" s="337">
-        <f>+AC35/AB35</f>
+        <f t="shared" si="20"/>
         <v>0.32350598223971644</v>
       </c>
       <c r="AE35" s="347">
@@ -15350,7 +15404,7 @@
         <v>283.0447383865187</v>
       </c>
       <c r="AF35" s="347">
-        <f>MAX(0,5.5*AC35)</f>
+        <f t="shared" si="21"/>
         <v>629.57149152615852</v>
       </c>
       <c r="AG35" s="347">
@@ -15450,7 +15504,7 @@
         <v>50.747919999999993</v>
       </c>
       <c r="R36" s="337">
-        <f>+Q36/P36</f>
+        <f t="shared" si="18"/>
         <v>0.1950826396243496</v>
       </c>
       <c r="S36" s="339">
@@ -15472,10 +15526,10 @@
         <v>82.011166788030081</v>
       </c>
       <c r="Y36" s="337">
-        <f>+X36/W36</f>
+        <f t="shared" si="19"/>
         <v>0.28946701477419323</v>
       </c>
-      <c r="Z36" s="397">
+      <c r="Z36" s="355">
         <v>256.60560905783194</v>
       </c>
       <c r="AA36" s="337">
@@ -15488,7 +15542,7 @@
         <v>106.892104297985</v>
       </c>
       <c r="AD36" s="337">
-        <f>+AC36/AB36</f>
+        <f t="shared" si="20"/>
         <v>0.34829585165197918</v>
       </c>
       <c r="AE36" s="347">
@@ -15496,7 +15550,7 @@
         <v>492.06700072818046</v>
       </c>
       <c r="AF36" s="347">
-        <f>MAX(0,5.5*AC36)</f>
+        <f t="shared" si="21"/>
         <v>587.90657363891751</v>
       </c>
       <c r="AG36" s="347">
@@ -15596,7 +15650,7 @@
         <v>92.870090000000005</v>
       </c>
       <c r="R37" s="337">
-        <f>+Q37/P37</f>
+        <f t="shared" si="18"/>
         <v>0.18430334741746648</v>
       </c>
       <c r="S37" s="339">
@@ -15618,10 +15672,10 @@
         <v>131.87614428558945</v>
       </c>
       <c r="Y37" s="337">
-        <f>+X37/W37</f>
+        <f t="shared" si="19"/>
         <v>0.24036739734237125</v>
       </c>
-      <c r="Z37" s="397">
+      <c r="Z37" s="355">
         <v>305.69986737518838</v>
       </c>
       <c r="AA37" s="337">
@@ -15634,7 +15688,7 @@
         <v>189.79042491816199</v>
       </c>
       <c r="AD37" s="337">
-        <f>+AC37/AB37</f>
+        <f t="shared" si="20"/>
         <v>0.30613366944689341</v>
       </c>
       <c r="AE37" s="347">
@@ -15642,7 +15696,7 @@
         <v>791.25686571353663</v>
       </c>
       <c r="AF37" s="347">
-        <f>MAX(0,5.5*AC37)</f>
+        <f t="shared" si="21"/>
         <v>1043.8473370498909</v>
       </c>
       <c r="AG37" s="347">
@@ -15742,7 +15796,7 @@
         <v>-17.017700000000094</v>
       </c>
       <c r="R38" s="337">
-        <f>+Q38/P38</f>
+        <f t="shared" si="18"/>
         <v>-6.2496185271073985E-2</v>
       </c>
       <c r="S38" s="339">
@@ -15764,10 +15818,10 @@
         <v>-32.120104494220797</v>
       </c>
       <c r="Y38" s="337">
-        <f>+X38/W38</f>
+        <f t="shared" si="19"/>
         <v>-0.1156226986934047</v>
       </c>
-      <c r="Z38" s="397">
+      <c r="Z38" s="355">
         <v>276.66822933727912</v>
       </c>
       <c r="AA38" s="337">
@@ -15780,11 +15834,11 @@
         <v>132.80200445517099</v>
       </c>
       <c r="AD38" s="337">
-        <f>+AC38/AB38</f>
+        <f t="shared" si="20"/>
         <v>0.29776956194398652</v>
       </c>
       <c r="AF38" s="347">
-        <f>MAX(0,5.5*AC38)</f>
+        <f t="shared" si="21"/>
         <v>730.41102450344044</v>
       </c>
       <c r="AG38" s="347">
@@ -15884,7 +15938,7 @@
         <v>95.207420000000013</v>
       </c>
       <c r="R39" s="337">
-        <f>+Q39/P39</f>
+        <f t="shared" si="18"/>
         <v>0.23612373963275604</v>
       </c>
       <c r="S39" s="339">
@@ -15906,10 +15960,10 @@
         <v>111.20791799475032</v>
       </c>
       <c r="Y39" s="337">
-        <f>+X39/W39</f>
+        <f t="shared" si="19"/>
         <v>0.26479182854869476</v>
       </c>
-      <c r="Z39" s="397">
+      <c r="Z39" s="355">
         <v>329.16277080246704</v>
       </c>
       <c r="AA39" s="337">
@@ -15922,7 +15976,7 @@
         <v>135.40678326641</v>
       </c>
       <c r="AD39" s="337">
-        <f>+AC39/AB39</f>
+        <f t="shared" si="20"/>
         <v>0.30426571619506931</v>
       </c>
       <c r="AE39" s="347">
@@ -15930,7 +15984,7 @@
         <v>667.24750796850185</v>
       </c>
       <c r="AF39" s="347">
-        <f>MAX(0,5.5*AC39)</f>
+        <f t="shared" si="21"/>
         <v>744.73730796525501</v>
       </c>
       <c r="AG39" s="347">
@@ -16030,7 +16084,7 @@
         <v>15.099209999999943</v>
       </c>
       <c r="R40" s="337">
-        <f>+Q40/P40</f>
+        <f t="shared" si="18"/>
         <v>4.8594957761530728E-2</v>
       </c>
       <c r="S40" s="339">
@@ -16052,10 +16106,10 @@
         <v>48.018220732019003</v>
       </c>
       <c r="Y40" s="337">
-        <f>+X40/W40</f>
+        <f t="shared" si="19"/>
         <v>0.13991357785529493</v>
       </c>
-      <c r="Z40" s="397">
+      <c r="Z40" s="355">
         <v>308.7787016313539</v>
       </c>
       <c r="AA40" s="337">
@@ -16068,7 +16122,7 @@
         <v>179.010498476902</v>
       </c>
       <c r="AD40" s="337">
-        <f>+AC40/AB40</f>
+        <f t="shared" si="20"/>
         <v>0.37162640729500279</v>
       </c>
       <c r="AE40" s="347">
@@ -16076,7 +16130,7 @@
         <v>288.10932439211399</v>
       </c>
       <c r="AF40" s="347">
-        <f>MAX(0,5.5*AC40)</f>
+        <f t="shared" si="21"/>
         <v>984.55774162296098</v>
       </c>
       <c r="AG40" s="347">
@@ -16179,7 +16233,7 @@
         <v>-62.567749999999968</v>
       </c>
       <c r="R41" s="337">
-        <f>+Q41/P41</f>
+        <f t="shared" si="18"/>
         <v>-0.36406856745184418</v>
       </c>
       <c r="S41" s="339">
@@ -16201,10 +16255,10 @@
         <v>-53.906198041382233</v>
       </c>
       <c r="Y41" s="337">
-        <f>+X41/W41</f>
+        <f t="shared" si="19"/>
         <v>-0.27433474164986277</v>
       </c>
-      <c r="Z41" s="397">
+      <c r="Z41" s="355">
         <v>254.02700249647259</v>
       </c>
       <c r="AA41" s="337">
@@ -16217,11 +16271,11 @@
         <v>122.100315749871</v>
       </c>
       <c r="AD41" s="337">
-        <f>+AC41/AB41</f>
+        <f t="shared" si="20"/>
         <v>0.33012280642184777</v>
       </c>
       <c r="AF41" s="347">
-        <f>MAX(0,5.5*AC41)</f>
+        <f t="shared" si="21"/>
         <v>671.55173662429047</v>
       </c>
       <c r="AG41" s="347">
@@ -16321,7 +16375,7 @@
         <v>-3.426919999999992</v>
       </c>
       <c r="R42" s="337">
-        <f>+Q42/P42</f>
+        <f t="shared" si="18"/>
         <v>-3.8953303594608746E-2</v>
       </c>
       <c r="S42" s="339">
@@ -16343,10 +16397,10 @@
         <v>113.60964449587738</v>
       </c>
       <c r="Y42" s="337">
-        <f>+X42/W42</f>
+        <f t="shared" si="19"/>
         <v>0.29641153953334942</v>
       </c>
-      <c r="Z42" s="397">
+      <c r="Z42" s="355">
         <v>252.62094982003129</v>
       </c>
       <c r="AA42" s="337">
@@ -16359,15 +16413,15 @@
         <v>149.476004200532</v>
       </c>
       <c r="AD42" s="337">
-        <f>+AC42/AB42</f>
+        <f t="shared" si="20"/>
         <v>0.35558938999885037</v>
       </c>
       <c r="AE42" s="347">
-        <f>+MAX(0,X42*6)</f>
+        <f t="shared" ref="AE42:AE54" si="22">+MAX(0,X42*6)</f>
         <v>681.65786697526426</v>
       </c>
       <c r="AF42" s="347">
-        <f>MAX(0,5.5*AC42)</f>
+        <f t="shared" si="21"/>
         <v>822.11802310292603</v>
       </c>
       <c r="AG42" s="347">
@@ -16467,7 +16521,7 @@
         <v>267.93579999999997</v>
       </c>
       <c r="R43" s="337">
-        <f>+Q43/P43</f>
+        <f t="shared" si="18"/>
         <v>0.45107417488487567</v>
       </c>
       <c r="S43" s="339">
@@ -16489,10 +16543,10 @@
         <v>284.1982945005754</v>
       </c>
       <c r="Y43" s="337">
-        <f>+X43/W43</f>
+        <f t="shared" si="19"/>
         <v>0.46956169908031825</v>
       </c>
-      <c r="Z43" s="397">
+      <c r="Z43" s="355">
         <v>308.9661316980368</v>
       </c>
       <c r="AA43" s="337">
@@ -16505,15 +16559,15 @@
         <v>311.849941775795</v>
       </c>
       <c r="AD43" s="337">
-        <f>+AC43/AB43</f>
+        <f t="shared" si="20"/>
         <v>0.48525660660278419</v>
       </c>
       <c r="AE43" s="347">
-        <f>+MAX(0,X43*6)</f>
+        <f t="shared" si="22"/>
         <v>1705.1897670034523</v>
       </c>
       <c r="AF43" s="347">
-        <f>MAX(0,5.5*AC43)</f>
+        <f t="shared" si="21"/>
         <v>1715.1746797668725</v>
       </c>
       <c r="AG43" s="347">
@@ -16613,7 +16667,7 @@
         <v>230.59747999999993</v>
       </c>
       <c r="R44" s="337">
-        <f>+Q44/P44</f>
+        <f t="shared" si="18"/>
         <v>0.36386273388712287</v>
       </c>
       <c r="S44" s="339">
@@ -16635,10 +16689,10 @@
         <v>270.33823022689626</v>
       </c>
       <c r="Y44" s="337">
-        <f>+X44/W44</f>
+        <f t="shared" si="19"/>
         <v>0.39588953965712914</v>
       </c>
-      <c r="Z44" s="397">
+      <c r="Z44" s="355">
         <v>286.98905312121178</v>
       </c>
       <c r="AA44" s="337">
@@ -16651,15 +16705,15 @@
         <v>453.91468713371199</v>
       </c>
       <c r="AD44" s="337">
-        <f>+AC44/AB44</f>
+        <f t="shared" si="20"/>
         <v>0.51552953178076544</v>
       </c>
       <c r="AE44" s="347">
-        <f>+MAX(0,X44*6)</f>
+        <f t="shared" si="22"/>
         <v>1622.0293813613775</v>
       </c>
       <c r="AF44" s="347">
-        <f>MAX(0,5.5*AC44)</f>
+        <f t="shared" si="21"/>
         <v>2496.530779235416</v>
       </c>
       <c r="AG44" s="347">
@@ -16759,7 +16813,7 @@
         <v>41.057659999999984</v>
       </c>
       <c r="R45" s="337">
-        <f>+Q45/P45</f>
+        <f t="shared" si="18"/>
         <v>0.14456881302556843</v>
       </c>
       <c r="S45" s="339">
@@ -16781,10 +16835,10 @@
         <v>46.794310786418009</v>
       </c>
       <c r="Y45" s="337">
-        <f>+X45/W45</f>
+        <f t="shared" si="19"/>
         <v>0.15357168445191513</v>
       </c>
-      <c r="Z45" s="397">
+      <c r="Z45" s="355">
         <v>257.88774731071146</v>
       </c>
       <c r="AA45" s="337">
@@ -16797,15 +16851,15 @@
         <v>138.877416493179</v>
       </c>
       <c r="AD45" s="337">
-        <f>+AC45/AB45</f>
+        <f t="shared" si="20"/>
         <v>0.35710799941345456</v>
       </c>
       <c r="AE45" s="347">
-        <f>+MAX(0,X45*6)</f>
+        <f t="shared" si="22"/>
         <v>280.76586471850806</v>
       </c>
       <c r="AF45" s="347">
-        <f>MAX(0,5.5*AC45)</f>
+        <f t="shared" si="21"/>
         <v>763.82579071248449</v>
       </c>
       <c r="AG45" s="347">
@@ -16905,7 +16959,7 @@
         <v>45.67397000000004</v>
       </c>
       <c r="R46" s="337">
-        <f>+Q46/P46</f>
+        <f t="shared" si="18"/>
         <v>0.18461569865026423</v>
       </c>
       <c r="S46" s="339">
@@ -16927,10 +16981,10 @@
         <v>49.951395106499106</v>
       </c>
       <c r="Y46" s="337">
-        <f>+X46/W46</f>
+        <f t="shared" si="19"/>
         <v>0.20002937318698549</v>
       </c>
-      <c r="Z46" s="397">
+      <c r="Z46" s="355">
         <v>297.24981688916569</v>
       </c>
       <c r="AA46" s="337">
@@ -16943,15 +16997,15 @@
         <v>74.937911334006003</v>
       </c>
       <c r="AD46" s="337">
-        <f>+AC46/AB46</f>
+        <f t="shared" si="20"/>
         <v>0.28518568589524146</v>
       </c>
       <c r="AE46" s="347">
-        <f>+MAX(0,X46*6)</f>
+        <f t="shared" si="22"/>
         <v>299.70837063899467</v>
       </c>
       <c r="AF46" s="347">
-        <f>MAX(0,5.5*AC46)</f>
+        <f t="shared" si="21"/>
         <v>412.15851233703302</v>
       </c>
       <c r="AG46" s="347">
@@ -17051,7 +17105,7 @@
         <v>173.83041999999995</v>
       </c>
       <c r="R47" s="337">
-        <f>+Q47/P47</f>
+        <f t="shared" si="18"/>
         <v>0.38529978159010031</v>
       </c>
       <c r="S47" s="339">
@@ -17073,10 +17127,10 @@
         <v>191.49187035736026</v>
       </c>
       <c r="Y47" s="337">
-        <f>+X47/W47</f>
+        <f t="shared" si="19"/>
         <v>0.42047565186300834</v>
       </c>
-      <c r="Z47" s="397">
+      <c r="Z47" s="355">
         <v>289.93596926666862</v>
       </c>
       <c r="AA47" s="337">
@@ -17089,15 +17143,15 @@
         <v>290.61254284207001</v>
       </c>
       <c r="AD47" s="337">
-        <f>+AC47/AB47</f>
+        <f t="shared" si="20"/>
         <v>0.52096337191354691</v>
       </c>
       <c r="AE47" s="347">
-        <f>+MAX(0,X47*6)</f>
+        <f t="shared" si="22"/>
         <v>1148.9512221441614</v>
       </c>
       <c r="AF47" s="347">
-        <f>MAX(0,5.5*AC47)</f>
+        <f t="shared" si="21"/>
         <v>1598.3689856313852</v>
       </c>
       <c r="AG47" s="347">
@@ -17197,7 +17251,7 @@
         <v>-177.37941000000001</v>
       </c>
       <c r="R48" s="337">
-        <f>+Q48/P48</f>
+        <f t="shared" si="18"/>
         <v>-0.52578999928562509</v>
       </c>
       <c r="S48" s="339">
@@ -17219,10 +17273,10 @@
         <v>3.1667764259846507</v>
       </c>
       <c r="Y48" s="337">
-        <f>+X48/W48</f>
+        <f t="shared" si="19"/>
         <v>6.0115356373093244E-3</v>
       </c>
-      <c r="Z48" s="397">
+      <c r="Z48" s="355">
         <v>315.52574537568717</v>
       </c>
       <c r="AA48" s="337">
@@ -17235,15 +17289,15 @@
         <v>152.05248159055199</v>
       </c>
       <c r="AD48" s="337">
-        <f>+AC48/AB48</f>
+        <f t="shared" si="20"/>
         <v>0.22065108996566293</v>
       </c>
       <c r="AE48" s="347">
-        <f>+MAX(0,X48*6)</f>
+        <f t="shared" si="22"/>
         <v>19.000658555907904</v>
       </c>
       <c r="AF48" s="347">
-        <f>MAX(0,5.5*AC48)</f>
+        <f t="shared" si="21"/>
         <v>836.28864874803594</v>
       </c>
       <c r="AG48" s="347">
@@ -17346,7 +17400,7 @@
         <v>25.853879999999997</v>
       </c>
       <c r="R49" s="337">
-        <f>+Q49/P49</f>
+        <f t="shared" si="18"/>
         <v>0.18578010328542144</v>
       </c>
       <c r="S49" s="339">
@@ -17368,10 +17422,10 @@
         <v>166.91249085464017</v>
       </c>
       <c r="Y49" s="337">
-        <f>+X49/W49</f>
+        <f t="shared" si="19"/>
         <v>0.43468617998689413</v>
       </c>
-      <c r="Z49" s="397">
+      <c r="Z49" s="355">
         <v>291.14016882436761</v>
       </c>
       <c r="AA49" s="337">
@@ -17384,15 +17438,15 @@
         <v>198.93621839008901</v>
       </c>
       <c r="AD49" s="337">
-        <f>+AC49/AB49</f>
+        <f t="shared" si="20"/>
         <v>0.46929978325143257</v>
       </c>
       <c r="AE49" s="347">
-        <f>+MAX(0,X49*6)</f>
+        <f t="shared" si="22"/>
         <v>1001.474945127841</v>
       </c>
       <c r="AF49" s="347">
-        <f>MAX(0,5.5*AC49)</f>
+        <f t="shared" si="21"/>
         <v>1094.1492011454895</v>
       </c>
       <c r="AG49" s="347">
@@ -17492,7 +17546,7 @@
         <v>8.1603099999999884</v>
       </c>
       <c r="R50" s="337">
-        <f>+Q50/P50</f>
+        <f t="shared" si="18"/>
         <v>5.5799593526344192E-2</v>
       </c>
       <c r="S50" s="339">
@@ -17514,10 +17568,10 @@
         <v>144.37783432125133</v>
       </c>
       <c r="Y50" s="337">
-        <f>+X50/W50</f>
+        <f t="shared" si="19"/>
         <v>0.34985033532630444</v>
       </c>
-      <c r="Z50" s="397">
+      <c r="Z50" s="355">
         <v>276.95040235794426</v>
       </c>
       <c r="AA50" s="337">
@@ -17530,15 +17584,15 @@
         <v>183.81207260211301</v>
       </c>
       <c r="AD50" s="337">
-        <f>+AC50/AB50</f>
+        <f t="shared" si="20"/>
         <v>0.3988583695791163</v>
       </c>
       <c r="AE50" s="347">
-        <f>+MAX(0,X50*6)</f>
+        <f t="shared" si="22"/>
         <v>866.26700592750797</v>
       </c>
       <c r="AF50" s="347">
-        <f>MAX(0,5.5*AC50)</f>
+        <f t="shared" si="21"/>
         <v>1010.9663993116216</v>
       </c>
       <c r="AG50" s="347">
@@ -17638,7 +17692,7 @@
         <v>143.32769999999999</v>
       </c>
       <c r="R51" s="337">
-        <f>+Q51/P51</f>
+        <f t="shared" si="18"/>
         <v>0.42371854420234611</v>
       </c>
       <c r="S51" s="339">
@@ -17660,10 +17714,10 @@
         <v>167.00296638454961</v>
       </c>
       <c r="Y51" s="337">
-        <f>+X51/W51</f>
+        <f t="shared" si="19"/>
         <v>0.47682314601853903</v>
       </c>
-      <c r="Z51" s="397">
+      <c r="Z51" s="355">
         <v>243.90338537847862</v>
       </c>
       <c r="AA51" s="337">
@@ -17676,15 +17730,15 @@
         <v>179.238509824674</v>
       </c>
       <c r="AD51" s="337">
-        <f>+AC51/AB51</f>
+        <f t="shared" si="20"/>
         <v>0.48731766507160013</v>
       </c>
       <c r="AE51" s="347">
-        <f>+MAX(0,X51*6)</f>
+        <f t="shared" si="22"/>
         <v>1002.0177983072977</v>
       </c>
       <c r="AF51" s="347">
-        <f>MAX(0,5.5*AC51)</f>
+        <f t="shared" si="21"/>
         <v>985.81180403570693</v>
       </c>
       <c r="AG51" s="347">
@@ -17782,7 +17836,7 @@
         <v>104.76482</v>
       </c>
       <c r="R52" s="337">
-        <f>+Q52/P52</f>
+        <f t="shared" si="18"/>
         <v>0.30228418051098277</v>
       </c>
       <c r="S52" s="339">
@@ -17804,10 +17858,10 @@
         <v>113.92080222141213</v>
       </c>
       <c r="Y52" s="337">
-        <f>+X52/W52</f>
+        <f t="shared" si="19"/>
         <v>0.31966817284153531</v>
       </c>
-      <c r="Z52" s="397">
+      <c r="Z52" s="355">
         <v>285.85846679748363</v>
       </c>
       <c r="AA52" s="337">
@@ -17820,15 +17874,15 @@
         <v>171.97485403460601</v>
       </c>
       <c r="AD52" s="337">
-        <f>+AC52/AB52</f>
+        <f t="shared" si="20"/>
         <v>0.4131925804909557</v>
       </c>
       <c r="AE52" s="347">
-        <f>+MAX(0,X52*6)</f>
+        <f t="shared" si="22"/>
         <v>683.52481332847276</v>
       </c>
       <c r="AF52" s="347">
-        <f>MAX(0,5.5*AC52)</f>
+        <f t="shared" si="21"/>
         <v>945.86169719033308</v>
       </c>
       <c r="AG52" s="347">
@@ -17926,7 +17980,7 @@
         <v>105.00200000000004</v>
       </c>
       <c r="R53" s="337">
-        <f>+Q53/P53</f>
+        <f t="shared" si="18"/>
         <v>0.28456406482863833</v>
       </c>
       <c r="S53" s="339">
@@ -17948,10 +18002,10 @@
         <v>117.38464279767985</v>
       </c>
       <c r="Y53" s="337">
-        <f>+X53/W53</f>
+        <f t="shared" si="19"/>
         <v>0.30625909357143</v>
       </c>
-      <c r="Z53" s="397">
+      <c r="Z53" s="355">
         <v>246.65537194663574</v>
       </c>
       <c r="AA53" s="337">
@@ -17964,15 +18018,15 @@
         <v>152.661781862325</v>
       </c>
       <c r="AD53" s="337">
-        <f>+AC53/AB53</f>
+        <f t="shared" si="20"/>
         <v>0.3606803356517192</v>
       </c>
       <c r="AE53" s="347">
-        <f>+MAX(0,X53*6)</f>
+        <f t="shared" si="22"/>
         <v>704.30785678607913</v>
       </c>
       <c r="AF53" s="347">
-        <f>MAX(0,5.5*AC53)</f>
+        <f t="shared" si="21"/>
         <v>839.63980024278749</v>
       </c>
       <c r="AG53" s="347">
@@ -18070,7 +18124,7 @@
         <v>-56.841699999999996</v>
       </c>
       <c r="R54" s="337">
-        <f>+Q54/P54</f>
+        <f t="shared" si="18"/>
         <v>-0.29928753374123812</v>
       </c>
       <c r="S54" s="339">
@@ -18092,10 +18146,10 @@
         <v>-26.328126006069155</v>
       </c>
       <c r="Y54" s="337">
-        <f>+X54/W54</f>
+        <f t="shared" si="19"/>
         <v>-0.12054589572609067</v>
       </c>
-      <c r="Z54" s="397">
+      <c r="Z54" s="355">
         <v>225.40461481009612</v>
       </c>
       <c r="AA54" s="337">
@@ -18108,15 +18162,15 @@
         <v>118.16849534737899</v>
       </c>
       <c r="AD54" s="337">
-        <f>+AC54/AB54</f>
+        <f t="shared" si="20"/>
         <v>0.32521746845036931</v>
       </c>
       <c r="AE54" s="347">
-        <f>+MAX(0,X54*6)</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AF54" s="347">
-        <f>MAX(0,5.5*AC54)</f>
+        <f t="shared" si="21"/>
         <v>649.92672441058448</v>
       </c>
       <c r="AG54" s="347">
@@ -18160,6 +18214,34 @@
       </c>
       <c r="AU54" s="55"/>
       <c r="AV54" s="55"/>
+    </row>
+    <row r="56" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="W56" s="378"/>
+      <c r="X56" s="378"/>
+      <c r="AB56" s="378"/>
+      <c r="AC56" s="378"/>
+    </row>
+    <row r="57" spans="1:48" ht="15" x14ac:dyDescent="0.25">
+      <c r="X57" s="385"/>
+      <c r="AC57" s="384"/>
+    </row>
+    <row r="58" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="X58" s="338"/>
+      <c r="AC58" s="338"/>
+    </row>
+    <row r="59" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="X59" s="338"/>
+      <c r="Y59" s="383"/>
+      <c r="Z59" s="338"/>
+      <c r="AA59" s="383"/>
+      <c r="AB59" s="338"/>
+      <c r="AC59" s="338"/>
+      <c r="AG59" s="338"/>
+      <c r="AH59" s="338"/>
+    </row>
+    <row r="60" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="X60" s="384"/>
+      <c r="AC60" s="338"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:AV54" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -18295,40 +18377,40 @@
       <c r="B4" s="328" t="s">
         <v>485</v>
       </c>
-      <c r="S4" s="388" t="s">
+      <c r="S4" s="391" t="s">
         <v>486</v>
       </c>
-      <c r="T4" s="389"/>
-      <c r="U4" s="390"/>
-      <c r="V4" s="392" t="s">
+      <c r="T4" s="392"/>
+      <c r="U4" s="393"/>
+      <c r="V4" s="395" t="s">
         <v>487</v>
       </c>
-      <c r="W4" s="389"/>
-      <c r="X4" s="389"/>
-      <c r="Y4" s="389"/>
-      <c r="Z4" s="389"/>
-      <c r="AA4" s="389"/>
-      <c r="AB4" s="389"/>
-      <c r="AC4" s="389"/>
-      <c r="AD4" s="389"/>
-      <c r="AE4" s="389"/>
-      <c r="AF4" s="390"/>
-      <c r="AG4" s="391" t="s">
+      <c r="W4" s="392"/>
+      <c r="X4" s="392"/>
+      <c r="Y4" s="392"/>
+      <c r="Z4" s="392"/>
+      <c r="AA4" s="392"/>
+      <c r="AB4" s="392"/>
+      <c r="AC4" s="392"/>
+      <c r="AD4" s="392"/>
+      <c r="AE4" s="392"/>
+      <c r="AF4" s="393"/>
+      <c r="AG4" s="394" t="s">
         <v>488</v>
       </c>
-      <c r="AH4" s="389"/>
-      <c r="AI4" s="389"/>
-      <c r="AJ4" s="389"/>
-      <c r="AK4" s="389"/>
-      <c r="AL4" s="390"/>
-      <c r="AM4" s="391" t="s">
+      <c r="AH4" s="392"/>
+      <c r="AI4" s="392"/>
+      <c r="AJ4" s="392"/>
+      <c r="AK4" s="392"/>
+      <c r="AL4" s="393"/>
+      <c r="AM4" s="394" t="s">
         <v>489</v>
       </c>
-      <c r="AN4" s="389"/>
-      <c r="AO4" s="389"/>
-      <c r="AP4" s="389"/>
-      <c r="AQ4" s="389"/>
-      <c r="AR4" s="390"/>
+      <c r="AN4" s="392"/>
+      <c r="AO4" s="392"/>
+      <c r="AP4" s="392"/>
+      <c r="AQ4" s="392"/>
+      <c r="AR4" s="393"/>
       <c r="AS4" s="327"/>
       <c r="AT4" s="327"/>
       <c r="AU4" s="327"/>
@@ -26358,17 +26440,17 @@
   <sheetData>
     <row r="1" spans="2:3" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="386"/>
-      <c r="C2" s="384"/>
+      <c r="B2" s="389"/>
+      <c r="C2" s="387"/>
     </row>
     <row r="3" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="383"/>
-      <c r="C3" s="384"/>
+      <c r="B3" s="386"/>
+      <c r="C3" s="387"/>
     </row>
     <row r="4" spans="2:3" ht="8.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="385"/>
-      <c r="C5" s="384"/>
+      <c r="B5" s="388"/>
+      <c r="C5" s="387"/>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1"/>
@@ -26546,15 +26628,15 @@
     <row r="1" spans="2:10" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:10" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="387"/>
-      <c r="C3" s="384"/>
-      <c r="D3" s="384"/>
-      <c r="E3" s="384"/>
-      <c r="F3" s="384"/>
-      <c r="G3" s="384"/>
-      <c r="H3" s="384"/>
-      <c r="I3" s="384"/>
-      <c r="J3" s="384"/>
+      <c r="B3" s="390"/>
+      <c r="C3" s="387"/>
+      <c r="D3" s="387"/>
+      <c r="E3" s="387"/>
+      <c r="F3" s="387"/>
+      <c r="G3" s="387"/>
+      <c r="H3" s="387"/>
+      <c r="I3" s="387"/>
+      <c r="J3" s="387"/>
     </row>
     <row r="4" spans="2:10" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">

--- a/data/CIM_Master_Data.xlsx
+++ b/data/CIM_Master_Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\calvi\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Network Shares\Phenix Salon Suites\SELLING LOCATIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AAD9C610-09BC-4C65-B223-168A0EE5995A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D7E5C28-E342-43B0-B03A-4C6AFA84A5E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Locations" sheetId="1" r:id="rId1"/>
@@ -33,8 +33,8 @@
   </definedNames>
   <calcPr calcId="191029" iterate="1"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId11"/>
-    <pivotCache cacheId="2" r:id="rId12"/>
+    <pivotCache cacheId="0" r:id="rId11"/>
+    <pivotCache cacheId="1" r:id="rId12"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -2631,7 +2631,7 @@
     <xf numFmtId="44" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="405">
+  <cellXfs count="396">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3680,17 +3680,6 @@
     <xf numFmtId="166" fontId="11" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="175" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -9198,7 +9187,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{427CD699-56F8-4E4F-AE38-516D87ACD995}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{427CD699-56F8-4E4F-AE38-516D87ACD995}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:R65" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="47">
     <pivotField showAll="0"/>
@@ -9998,7 +9987,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0800-000000000000}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0800-000000000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="AZ5:BD14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="40">
     <pivotField dataField="1" showAll="0">
@@ -13815,7 +13804,7 @@
         <v>135.76963411367473</v>
       </c>
       <c r="Y24" s="337">
-        <f t="shared" ref="Y24:Y32" si="14">+X24/W24</f>
+        <f t="shared" ref="Y24:Y31" si="14">+X24/W24</f>
         <v>0.4253627686670462</v>
       </c>
       <c r="Z24" s="355">
@@ -13835,7 +13824,7 @@
         <v>0.45581823187734433</v>
       </c>
       <c r="AE24" s="347">
-        <f t="shared" ref="AE24:AE32" si="16">+MAX(0,X24*6)</f>
+        <f t="shared" ref="AE24:AE31" si="16">+MAX(0,X24*6)</f>
         <v>814.61780468204836</v>
       </c>
       <c r="AF24" s="347">
@@ -14911,253 +14900,233 @@
       </c>
       <c r="AV31" s="55"/>
     </row>
-    <row r="32" spans="1:48" s="397" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="396">
+    <row r="32" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A32" s="345">
         <v>6501</v>
       </c>
-      <c r="B32" s="397" t="s">
+      <c r="B32" s="346" t="s">
         <v>247</v>
       </c>
-      <c r="C32" s="397" t="s">
+      <c r="C32" s="346" t="s">
         <v>248</v>
       </c>
-      <c r="D32" s="397" t="s">
+      <c r="D32" s="346" t="s">
         <v>249</v>
       </c>
-      <c r="E32" s="397" t="s">
+      <c r="E32" s="346" t="s">
         <v>248</v>
       </c>
-      <c r="F32" s="397" t="s">
+      <c r="F32" s="346" t="s">
         <v>250</v>
       </c>
-      <c r="G32" s="397" t="s">
+      <c r="G32" s="346" t="s">
         <v>457</v>
       </c>
-      <c r="H32" s="397" t="s">
+      <c r="H32" s="346" t="s">
         <v>251</v>
       </c>
-      <c r="I32" s="397" t="s">
+      <c r="I32" s="346" t="s">
         <v>252</v>
       </c>
-      <c r="J32" s="397" t="s">
+      <c r="J32" s="346" t="s">
         <v>55</v>
       </c>
-      <c r="K32" s="396">
+      <c r="K32" s="345">
         <v>2026</v>
       </c>
-      <c r="L32" s="398">
+      <c r="L32" s="347">
         <v>32</v>
       </c>
-      <c r="M32" s="398">
+      <c r="M32" s="347">
         <v>5906</v>
       </c>
-      <c r="N32" s="399"/>
-      <c r="O32" s="399"/>
-      <c r="P32" s="400"/>
-      <c r="Q32" s="400"/>
-      <c r="R32" s="399"/>
-      <c r="S32" s="401">
+      <c r="S32" s="339">
         <v>0.59375</v>
       </c>
-      <c r="T32" s="399">
+      <c r="T32" s="337">
         <v>0.65625</v>
       </c>
-      <c r="U32" s="400">
+      <c r="U32" s="355">
         <v>280</v>
       </c>
-      <c r="V32" s="399"/>
-      <c r="W32" s="400"/>
-      <c r="X32" s="400"/>
-      <c r="Y32" s="399"/>
-      <c r="Z32" s="400">
+      <c r="V32" s="337"/>
+      <c r="Z32" s="355">
         <f>+U32*1.05</f>
         <v>294</v>
       </c>
-      <c r="AA32" s="399">
+      <c r="AA32" s="337">
         <f>31/L32</f>
         <v>0.96875</v>
       </c>
-      <c r="AB32" s="400">
+      <c r="AB32" s="355">
         <f>+ROUND(AA32*L32,0)*Z32*52/1000</f>
         <v>473.928</v>
       </c>
-      <c r="AC32" s="400">
-        <v>110.86499999999999</v>
-      </c>
-      <c r="AD32" s="399">
+      <c r="AC32" s="355">
+        <v>95.265000000000001</v>
+      </c>
+      <c r="AD32" s="337">
         <f t="shared" si="15"/>
-        <v>0.23392793842102597</v>
-      </c>
-      <c r="AE32" s="398"/>
-      <c r="AF32" s="398">
+        <v>0.201011546057629</v>
+      </c>
+      <c r="AF32" s="347">
         <f t="shared" si="17"/>
-        <v>609.75749999999994</v>
-      </c>
-      <c r="AG32" s="398">
+        <v>523.95749999999998</v>
+      </c>
+      <c r="AG32" s="347">
+        <v>200</v>
+      </c>
+      <c r="AH32" s="348">
+        <v>42856</v>
+      </c>
+      <c r="AI32" s="348">
+        <v>46085</v>
+      </c>
+      <c r="AJ32" s="349">
+        <v>49738</v>
+      </c>
+      <c r="AK32" s="349" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL32" s="349">
+        <v>51564</v>
+      </c>
+      <c r="AM32" s="349" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN32" s="347">
+        <v>153</v>
+      </c>
+      <c r="AO32" s="347">
+        <v>86000</v>
+      </c>
+      <c r="AP32" s="346" t="s">
+        <v>58</v>
+      </c>
+      <c r="AQ32" s="346" t="s">
+        <v>253</v>
+      </c>
+      <c r="AR32" s="345" t="s">
+        <v>603</v>
+      </c>
+      <c r="AT32" s="55" t="s">
+        <v>372</v>
+      </c>
+      <c r="AU32" s="55"/>
+      <c r="AV32" s="55"/>
+    </row>
+    <row r="33" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A33" s="345">
+        <v>6502</v>
+      </c>
+      <c r="B33" s="346" t="s">
+        <v>254</v>
+      </c>
+      <c r="C33" s="346" t="s">
+        <v>255</v>
+      </c>
+      <c r="D33" s="346" t="s">
+        <v>256</v>
+      </c>
+      <c r="E33" s="346" t="s">
+        <v>255</v>
+      </c>
+      <c r="F33" s="346" t="s">
         <v>250</v>
       </c>
-      <c r="AH32" s="402">
-        <v>42856</v>
-      </c>
-      <c r="AI32" s="402">
-        <v>46085</v>
-      </c>
-      <c r="AJ32" s="403">
-        <v>49738</v>
-      </c>
-      <c r="AK32" s="403" t="s">
-        <v>92</v>
-      </c>
-      <c r="AL32" s="403">
-        <v>51564</v>
-      </c>
-      <c r="AM32" s="403" t="s">
-        <v>57</v>
-      </c>
-      <c r="AN32" s="398">
-        <v>153</v>
-      </c>
-      <c r="AO32" s="398">
-        <v>86000</v>
-      </c>
-      <c r="AP32" s="397" t="s">
-        <v>58</v>
-      </c>
-      <c r="AQ32" s="397" t="s">
-        <v>253</v>
-      </c>
-      <c r="AR32" s="396" t="s">
-        <v>603</v>
-      </c>
-      <c r="AS32" s="404"/>
-      <c r="AT32" s="404" t="s">
-        <v>372</v>
-      </c>
-      <c r="AU32" s="404"/>
-      <c r="AV32" s="404"/>
-    </row>
-    <row r="33" spans="1:48" s="397" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="396">
-        <v>6502</v>
-      </c>
-      <c r="B33" s="397" t="s">
-        <v>254</v>
-      </c>
-      <c r="C33" s="397" t="s">
-        <v>255</v>
-      </c>
-      <c r="D33" s="397" t="s">
-        <v>256</v>
-      </c>
-      <c r="E33" s="397" t="s">
-        <v>255</v>
-      </c>
-      <c r="F33" s="397" t="s">
-        <v>250</v>
-      </c>
-      <c r="G33" s="397" t="s">
+      <c r="G33" s="346" t="s">
         <v>457</v>
       </c>
-      <c r="H33" s="397" t="s">
+      <c r="H33" s="346" t="s">
         <v>251</v>
       </c>
-      <c r="I33" s="397" t="s">
+      <c r="I33" s="346" t="s">
         <v>252</v>
       </c>
-      <c r="J33" s="397" t="s">
+      <c r="J33" s="346" t="s">
         <v>55</v>
       </c>
-      <c r="K33" s="396">
+      <c r="K33" s="345">
         <v>2026</v>
       </c>
-      <c r="L33" s="398">
+      <c r="L33" s="347">
         <v>29</v>
       </c>
-      <c r="M33" s="398">
+      <c r="M33" s="347">
         <v>4845</v>
       </c>
-      <c r="N33" s="399"/>
-      <c r="O33" s="399"/>
-      <c r="P33" s="400"/>
-      <c r="Q33" s="400"/>
-      <c r="R33" s="399"/>
-      <c r="S33" s="401">
+      <c r="S33" s="339">
         <v>0.55172413793103448</v>
       </c>
-      <c r="T33" s="399">
+      <c r="T33" s="337">
         <v>0.62068965517241381</v>
       </c>
-      <c r="U33" s="400">
+      <c r="U33" s="355">
         <v>218</v>
       </c>
-      <c r="V33" s="399"/>
-      <c r="W33" s="400"/>
-      <c r="X33" s="400"/>
-      <c r="Y33" s="399"/>
-      <c r="Z33" s="400">
+      <c r="V33" s="337"/>
+      <c r="Z33" s="355">
         <v>239.55175455507697</v>
       </c>
-      <c r="AA33" s="399">
+      <c r="AA33" s="337">
         <v>0.96551724137931039</v>
       </c>
-      <c r="AB33" s="400">
+      <c r="AB33" s="355">
         <f>+ROUND(AA33*L33,0)*Z33*52/1000</f>
         <v>348.78735463219203</v>
       </c>
-      <c r="AC33" s="400">
-        <v>111.65</v>
-      </c>
-      <c r="AD33" s="399">
+      <c r="AC33" s="355">
+        <v>99.853999999999999</v>
+      </c>
+      <c r="AD33" s="337">
         <f t="shared" si="15"/>
-        <v>0.32010908227375007</v>
-      </c>
-      <c r="AE33" s="398"/>
-      <c r="AF33" s="398">
+        <v>0.28628904882546385</v>
+      </c>
+      <c r="AF33" s="347">
         <f t="shared" si="17"/>
-        <v>614.07500000000005</v>
-      </c>
-      <c r="AG33" s="398">
-        <v>250</v>
-      </c>
-      <c r="AH33" s="402">
+        <v>549.197</v>
+      </c>
+      <c r="AG33" s="347">
+        <v>200</v>
+      </c>
+      <c r="AH33" s="348">
         <v>42795</v>
       </c>
-      <c r="AI33" s="402">
+      <c r="AI33" s="348">
         <v>46174</v>
       </c>
-      <c r="AJ33" s="403">
+      <c r="AJ33" s="349">
         <v>49979</v>
       </c>
-      <c r="AK33" s="403" t="s">
+      <c r="AK33" s="349" t="s">
         <v>92</v>
       </c>
-      <c r="AL33" s="403">
+      <c r="AL33" s="349">
         <v>51805</v>
       </c>
-      <c r="AM33" s="403" t="s">
+      <c r="AM33" s="349" t="s">
         <v>57</v>
       </c>
-      <c r="AN33" s="398">
+      <c r="AN33" s="347">
         <v>192</v>
       </c>
-      <c r="AO33" s="398">
+      <c r="AO33" s="347">
         <v>93000</v>
       </c>
-      <c r="AP33" s="397" t="s">
+      <c r="AP33" s="346" t="s">
         <v>58</v>
       </c>
-      <c r="AQ33" s="397" t="s">
+      <c r="AQ33" s="346" t="s">
         <v>253</v>
       </c>
-      <c r="AR33" s="396" t="s">
+      <c r="AR33" s="345" t="s">
         <v>604</v>
       </c>
-      <c r="AS33" s="404"/>
-      <c r="AT33" s="404" t="s">
+      <c r="AT33" s="55" t="s">
         <v>372</v>
       </c>
-      <c r="AU33" s="404"/>
-      <c r="AV33" s="404"/>
+      <c r="AU33" s="55"/>
+      <c r="AV33" s="55"/>
     </row>
     <row r="34" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A34" s="345">

--- a/data/CIM_Master_Data.xlsx
+++ b/data/CIM_Master_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Network Shares\Phenix Salon Suites\SELLING LOCATIONS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D7E5C28-E342-43B0-B03A-4C6AFA84A5E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB4794AC-8C23-4C69-A095-6DDF49AE97F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Locations" sheetId="1" r:id="rId1"/>
@@ -14974,7 +14974,7 @@
         <v>523.95749999999998</v>
       </c>
       <c r="AG32" s="347">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AH32" s="348">
         <v>42856</v>
@@ -15087,7 +15087,7 @@
         <v>549.197</v>
       </c>
       <c r="AG33" s="347">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AH33" s="348">
         <v>42795</v>
